--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2127,7 +2127,7 @@
         <v>2.6</v>
       </c>
       <c r="J22" t="n">
-        <v>19729.47</v>
+        <v>19729.46</v>
       </c>
       <c r="K22" t="n">
         <v>19630.93</v>
@@ -4919,7 +4919,7 @@
         <v>2.6</v>
       </c>
       <c r="J58" t="n">
-        <v>17132.25</v>
+        <v>17132.26</v>
       </c>
       <c r="K58" t="n">
         <v>18472.28</v>
@@ -7935,7 +7935,7 @@
         <v>2.6</v>
       </c>
       <c r="J98" t="n">
-        <v>19240.32</v>
+        <v>19240.31</v>
       </c>
       <c r="K98" t="n">
         <v>17918.44</v>
@@ -31591,6 +31591,83 @@
         <v>154.5</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>26018.5</v>
+      </c>
+      <c r="D413" t="n">
+        <v>26329.98</v>
+      </c>
+      <c r="E413" t="n">
+        <v>25992.54</v>
+      </c>
+      <c r="F413" t="n">
+        <v>26281.99</v>
+      </c>
+      <c r="G413" t="n">
+        <v>4029915000</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J413" t="n">
+        <v>26293.49</v>
+      </c>
+      <c r="K413" t="n">
+        <v>26018.36</v>
+      </c>
+      <c r="L413" t="n">
+        <v>25425.02</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24493.58</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="O413" t="n">
+        <v>31</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -2127,7 +2127,7 @@
         <v>2.6</v>
       </c>
       <c r="J22" t="n">
-        <v>19729.46</v>
+        <v>19729.47</v>
       </c>
       <c r="K22" t="n">
         <v>19630.93</v>
@@ -4919,7 +4919,7 @@
         <v>2.6</v>
       </c>
       <c r="J58" t="n">
-        <v>17132.26</v>
+        <v>17132.25</v>
       </c>
       <c r="K58" t="n">
         <v>18472.28</v>
@@ -7935,7 +7935,7 @@
         <v>2.6</v>
       </c>
       <c r="J98" t="n">
-        <v>19240.31</v>
+        <v>19240.32</v>
       </c>
       <c r="K98" t="n">
         <v>17918.44</v>
@@ -31612,31 +31612,31 @@
         <v>25992.54</v>
       </c>
       <c r="F413" t="n">
-        <v>26281.99</v>
+        <v>26186.41</v>
       </c>
       <c r="G413" t="n">
-        <v>4029915000</v>
+        <v>6240109000</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="I413" t="n">
         <v>2.6</v>
       </c>
       <c r="J413" t="n">
-        <v>26293.49</v>
+        <v>26288.71</v>
       </c>
       <c r="K413" t="n">
-        <v>26018.36</v>
+        <v>26016.77</v>
       </c>
       <c r="L413" t="n">
-        <v>25425.02</v>
+        <v>25424.22</v>
       </c>
       <c r="M413" t="n">
-        <v>24493.58</v>
+        <v>24493.11</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>56.47</v>
+        <v>54.24</v>
       </c>
       <c r="O413" t="n">
         <v>31</v>
@@ -31657,16 +31657,18 @@
         </is>
       </c>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>152.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31534,13 +31534,13 @@
         <v>26329.98</v>
       </c>
       <c r="E412" t="n">
-        <v>25992.54</v>
+        <v>25992.55</v>
       </c>
       <c r="F412" t="n">
         <v>26186.41</v>
       </c>
       <c r="G412" t="n">
-        <v>6240109000</v>
+        <v>7179780000</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-0.5600000000000001</v>
@@ -31564,7 +31564,7 @@
         <v>54.24</v>
       </c>
       <c r="O412" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31587,9 +31587,7 @@
       <c r="T412" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U412" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
         <v>152.1</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31564,7 +31564,7 @@
         <v>54.24</v>
       </c>
       <c r="O412" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31593,6 +31593,83 @@
         <v>152.1</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>26140.23</v>
+      </c>
+      <c r="D413" t="n">
+        <v>26172.12</v>
+      </c>
+      <c r="E413" t="n">
+        <v>25949.48</v>
+      </c>
+      <c r="F413" t="n">
+        <v>25981.08</v>
+      </c>
+      <c r="G413" t="n">
+        <v>4474114000</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J413" t="n">
+        <v>26255.52</v>
+      </c>
+      <c r="K413" t="n">
+        <v>26007.82</v>
+      </c>
+      <c r="L413" t="n">
+        <v>25459.38</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24507.88</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>46.55</v>
+      </c>
+      <c r="O413" t="n">
+        <v>29</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -645,9 +645,7 @@
       <c r="T2" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U2" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U2" s="2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" s="1" t="n">
         <v>173.2</v>
@@ -724,9 +722,7 @@
       <c r="T3" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U3" s="5" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U3" s="5" t="inlineStr"/>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" s="4" t="n">
         <v>168.6</v>
@@ -799,9 +795,7 @@
       <c r="T4" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U4" s="2" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U4" s="2" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="1" t="n">
         <v>163.6</v>
@@ -874,9 +868,7 @@
       <c r="T5" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U5" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U5" s="2" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="1" t="n">
         <v>157.4</v>
@@ -949,9 +941,7 @@
       <c r="T6" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U6" s="2" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U6" s="2" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="1" t="n">
         <v>156.7</v>
@@ -1024,9 +1014,7 @@
       <c r="T7" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U7" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U7" s="2" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="1" t="n">
         <v>158.5</v>
@@ -1103,9 +1091,7 @@
       <c r="T8" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U8" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U8" s="2" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="1" t="n">
         <v>155.4</v>
@@ -1178,9 +1164,7 @@
       <c r="T9" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U9" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="1" t="n">
         <v>159.4</v>
@@ -1253,9 +1237,7 @@
       <c r="T10" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U10" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="1" t="n">
         <v>162.6</v>
@@ -1328,9 +1310,7 @@
       <c r="T11" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U11" s="2" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="1" t="n">
         <v>163.6</v>
@@ -1407,9 +1387,7 @@
       <c r="T12" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U12" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="1" t="n">
         <v>166.5</v>
@@ -1482,9 +1460,7 @@
       <c r="T13" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U13" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="1" t="n">
         <v>166.9</v>
@@ -1557,9 +1533,7 @@
       <c r="T14" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U14" s="2" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="1" t="n">
         <v>168.8</v>
@@ -1636,9 +1610,7 @@
       <c r="T15" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U15" s="2" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="1" t="n">
         <v>166.1</v>
@@ -1711,9 +1683,7 @@
       <c r="T16" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U16" s="2" t="n">
-        <v>11</v>
-      </c>
+      <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="1" t="n">
         <v>163.4</v>
@@ -1786,9 +1756,7 @@
       <c r="T17" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U17" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="1" t="n">
         <v>168</v>
@@ -1861,9 +1829,7 @@
       <c r="T18" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U18" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="1" t="n">
         <v>183.1</v>
@@ -1936,9 +1902,7 @@
       <c r="T19" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U19" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="1" t="n">
         <v>175.8</v>
@@ -2011,9 +1975,7 @@
       <c r="T20" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U20" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="1" t="n">
         <v>178.6</v>
@@ -2090,9 +2052,7 @@
       <c r="T21" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U21" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="1" t="n">
         <v>165</v>
@@ -2165,9 +2125,7 @@
       <c r="T22" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U22" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="1" t="n">
         <v>156.9</v>
@@ -2240,9 +2198,7 @@
       <c r="T23" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U23" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="1" t="n">
         <v>157.6</v>
@@ -2315,9 +2271,7 @@
       <c r="T24" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U24" s="2" t="n">
-        <v>20.5</v>
-      </c>
+      <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" s="2" t="n">
         <v>153.4</v>
@@ -2394,9 +2348,7 @@
       <c r="T25" s="5" t="n">
         <v>21.1</v>
       </c>
-      <c r="U25" s="5" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U25" s="5" t="inlineStr"/>
       <c r="V25" s="3" t="inlineStr"/>
       <c r="W25" s="5" t="n">
         <v>149.3</v>
@@ -2469,9 +2421,7 @@
       <c r="T26" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U26" s="2" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="1" t="n">
         <v>157.9</v>
@@ -2548,9 +2498,7 @@
       <c r="T27" s="5" t="n">
         <v>22.8</v>
       </c>
-      <c r="U27" s="5" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U27" s="5" t="inlineStr"/>
       <c r="V27" s="3" t="inlineStr"/>
       <c r="W27" s="5" t="n">
         <v>154.3</v>
@@ -2627,9 +2575,7 @@
       <c r="T28" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U28" s="2" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="2" t="n">
         <v>151.4</v>
@@ -2702,9 +2648,7 @@
       <c r="T29" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U29" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="2" t="n">
         <v>138.9</v>
@@ -2781,9 +2725,7 @@
       <c r="T30" s="5" t="n">
         <v>24.9</v>
       </c>
-      <c r="U30" s="7" t="n">
-        <v>31.1</v>
-      </c>
+      <c r="U30" s="5" t="inlineStr"/>
       <c r="V30" s="3" t="inlineStr"/>
       <c r="W30" s="5" t="n">
         <v>137.6</v>
@@ -2860,9 +2802,7 @@
       <c r="T31" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U31" s="2" t="n">
-        <v>24.7</v>
-      </c>
+      <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" s="2" t="n">
         <v>139.9</v>
@@ -2939,14 +2879,8 @@
       <c r="T32" s="7" t="n">
         <v>27.9</v>
       </c>
-      <c r="U32" s="7" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="V32" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U32" s="5" t="inlineStr"/>
+      <c r="V32" s="3" t="inlineStr"/>
       <c r="W32" s="5" t="n">
         <v>146</v>
       </c>
@@ -3022,14 +2956,8 @@
       <c r="T33" s="6" t="n">
         <v>26.9</v>
       </c>
-      <c r="U33" s="6" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="V33" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" s="2" t="n">
         <v>132.8</v>
       </c>
@@ -3105,9 +3033,7 @@
       <c r="T34" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U34" s="2" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="2" t="n">
         <v>128.7</v>
@@ -3184,9 +3110,7 @@
       <c r="T35" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U35" s="2" t="n">
-        <v>23.4</v>
-      </c>
+      <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="2" t="n">
         <v>128.9</v>
@@ -3259,9 +3183,7 @@
       <c r="T36" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U36" s="2" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="2" t="n">
         <v>130.3</v>
@@ -3334,9 +3256,7 @@
       <c r="T37" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U37" s="2" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="2" t="n">
         <v>133.9</v>
@@ -3409,9 +3329,7 @@
       <c r="T38" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U38" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="2" t="n">
         <v>136.8</v>
@@ -3484,9 +3402,7 @@
       <c r="T39" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U39" s="2" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="n">
         <v>136.4</v>
@@ -3559,9 +3475,7 @@
       <c r="T40" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U40" s="2" t="n">
-        <v>18.6</v>
-      </c>
+      <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="2" t="n">
         <v>140.8</v>
@@ -3634,9 +3548,7 @@
       <c r="T41" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U41" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="2" t="n">
         <v>141.7</v>
@@ -3709,9 +3621,7 @@
       <c r="T42" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U42" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="2" t="n">
         <v>144</v>
@@ -3784,9 +3694,7 @@
       <c r="T43" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U43" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="2" t="n">
         <v>148.7</v>
@@ -3863,9 +3771,7 @@
       <c r="T44" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U44" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="2" t="n">
         <v>144.8</v>
@@ -3938,9 +3844,7 @@
       <c r="T45" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U45" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="2" t="n">
         <v>140.9</v>
@@ -4013,9 +3917,7 @@
       <c r="T46" s="5" t="n">
         <v>21.6</v>
       </c>
-      <c r="U46" s="7" t="n">
-        <v>25.4</v>
-      </c>
+      <c r="U46" s="5" t="inlineStr"/>
       <c r="V46" s="3" t="inlineStr"/>
       <c r="W46" s="5" t="n">
         <v>139</v>
@@ -4088,9 +3990,7 @@
       <c r="T47" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U47" s="2" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="2" t="n">
         <v>148.6</v>
@@ -4163,9 +4063,7 @@
       <c r="T48" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U48" s="2" t="n">
-        <v>20.1</v>
-      </c>
+      <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="2" t="n">
         <v>143</v>
@@ -4238,9 +4136,7 @@
       <c r="T49" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="U49" s="6" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" s="2" t="n">
         <v>144.3</v>
@@ -4313,14 +4209,8 @@
       <c r="T50" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="U50" s="7" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="V50" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U50" s="5" t="inlineStr"/>
+      <c r="V50" s="3" t="inlineStr"/>
       <c r="W50" s="5" t="n">
         <v>139.2</v>
       </c>
@@ -4396,14 +4286,8 @@
       <c r="T51" s="7" t="n">
         <v>45.3</v>
       </c>
-      <c r="U51" s="7" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="V51" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U51" s="5" t="inlineStr"/>
+      <c r="V51" s="3" t="inlineStr"/>
       <c r="W51" s="5" t="n">
         <v>136.5</v>
       </c>
@@ -4479,14 +4363,8 @@
       <c r="T52" s="6" t="n">
         <v>47</v>
       </c>
-      <c r="U52" s="6" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="V52" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" s="2" t="n">
         <v>133.8</v>
       </c>
@@ -4562,14 +4440,8 @@
       <c r="T53" s="6" t="n">
         <v>52.3</v>
       </c>
-      <c r="U53" s="6" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="V53" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" s="2" t="n">
         <v>135.7</v>
       </c>
@@ -4641,14 +4513,8 @@
       <c r="T54" s="6" t="n">
         <v>33.6</v>
       </c>
-      <c r="U54" s="6" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="V54" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" s="2" t="n">
         <v>142.2</v>
       </c>
@@ -4720,14 +4586,8 @@
       <c r="T55" s="7" t="n">
         <v>40.7</v>
       </c>
-      <c r="U55" s="7" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="V55" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U55" s="5" t="inlineStr"/>
+      <c r="V55" s="3" t="inlineStr"/>
       <c r="W55" s="5" t="n">
         <v>127.5</v>
       </c>
@@ -4799,14 +4659,8 @@
       <c r="T56" s="6" t="n">
         <v>37.6</v>
       </c>
-      <c r="U56" s="6" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="V56" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" s="2" t="n">
         <v>128.6</v>
       </c>
@@ -4878,9 +4732,7 @@
       <c r="T57" s="6" t="n">
         <v>30.9</v>
       </c>
-      <c r="U57" s="6" t="n">
-        <v>28.5</v>
-      </c>
+      <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="2" t="n">
         <v>135.7</v>
@@ -4953,9 +4805,7 @@
       <c r="T58" s="6" t="n">
         <v>30.1</v>
       </c>
-      <c r="U58" s="6" t="n">
-        <v>26</v>
-      </c>
+      <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" s="2" t="n">
         <v>135.8</v>
@@ -5028,14 +4878,8 @@
       <c r="T59" s="7" t="n">
         <v>32.6</v>
       </c>
-      <c r="U59" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="V59" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U59" s="5" t="inlineStr"/>
+      <c r="V59" s="3" t="inlineStr"/>
       <c r="W59" s="5" t="n">
         <v>131.3</v>
       </c>
@@ -5107,14 +4951,8 @@
       <c r="T60" s="6" t="n">
         <v>29.6</v>
       </c>
-      <c r="U60" s="6" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="V60" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" s="2" t="n">
         <v>130</v>
       </c>
@@ -5186,9 +5024,7 @@
       <c r="T61" s="6" t="n">
         <v>33.8</v>
       </c>
-      <c r="U61" s="6" t="n">
-        <v>30.6</v>
-      </c>
+      <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="6" t="n">
         <v>125.8</v>
@@ -5261,9 +5097,7 @@
       <c r="T62" s="6" t="n">
         <v>30.6</v>
       </c>
-      <c r="U62" s="6" t="n">
-        <v>29.1</v>
-      </c>
+      <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" s="6" t="n">
         <v>125.9</v>
@@ -5336,14 +5170,8 @@
       <c r="T63" s="6" t="n">
         <v>28.5</v>
       </c>
-      <c r="U63" s="6" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="V63" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" s="6" t="n">
         <v>126.7</v>
       </c>
@@ -5415,9 +5243,7 @@
       <c r="T64" s="6" t="n">
         <v>26.5</v>
       </c>
-      <c r="U64" s="6" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="2" t="n">
         <v>129</v>
@@ -5490,9 +5316,7 @@
       <c r="T65" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U65" s="2" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="2" t="n">
         <v>132.4</v>
@@ -5565,9 +5389,7 @@
       <c r="T66" s="6" t="n">
         <v>25.1</v>
       </c>
-      <c r="U66" s="2" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="2" t="n">
         <v>131.3</v>
@@ -5640,9 +5462,7 @@
       <c r="T67" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U67" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="2" t="n">
         <v>134.3</v>
@@ -5715,9 +5535,7 @@
       <c r="T68" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U68" s="2" t="n">
-        <v>22.9</v>
-      </c>
+      <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="2" t="n">
         <v>132.7</v>
@@ -5790,9 +5608,7 @@
       <c r="T69" s="2" t="n">
         <v>24.6</v>
       </c>
-      <c r="U69" s="6" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="2" t="n">
         <v>134.1</v>
@@ -5865,9 +5681,7 @@
       <c r="T70" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="U70" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="2" t="n">
         <v>134.8</v>
@@ -5944,9 +5758,7 @@
       <c r="T71" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U71" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="2" t="n">
         <v>134.1</v>
@@ -6019,9 +5831,7 @@
       <c r="T72" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U72" s="2" t="n">
-        <v>22.2</v>
-      </c>
+      <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="2" t="n">
         <v>133.2</v>
@@ -6094,9 +5904,7 @@
       <c r="T73" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U73" s="2" t="n">
-        <v>19.8</v>
-      </c>
+      <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="2" t="n">
         <v>132.2</v>
@@ -6169,9 +5977,7 @@
       <c r="T74" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="U74" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="2" t="n">
         <v>131.5</v>
@@ -6244,9 +6050,7 @@
       <c r="T75" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U75" s="6" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="2" t="n">
         <v>128.4</v>
@@ -6319,9 +6123,7 @@
       <c r="T76" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U76" s="2" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="2" t="n">
         <v>137.7</v>
@@ -6394,9 +6196,7 @@
       <c r="T77" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U77" s="2" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="2" t="n">
         <v>140.5</v>
@@ -6469,9 +6269,7 @@
       <c r="T78" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U78" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="2" t="n">
         <v>138.9</v>
@@ -6544,9 +6342,7 @@
       <c r="T79" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U79" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="2" t="n">
         <v>140.9</v>
@@ -6619,9 +6415,7 @@
       <c r="T80" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U80" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="2" t="n">
         <v>136</v>
@@ -6694,9 +6488,7 @@
       <c r="T81" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U81" s="2" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="2" t="n">
         <v>135.9</v>
@@ -6769,9 +6561,7 @@
       <c r="T82" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U82" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="2" t="n">
         <v>137.3</v>
@@ -6844,9 +6634,7 @@
       <c r="T83" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="U83" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="2" t="n">
         <v>137.3</v>
@@ -6919,9 +6707,7 @@
       <c r="T84" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U84" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="2" t="n">
         <v>139</v>
@@ -6994,9 +6780,7 @@
       <c r="T85" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U85" s="2" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="2" t="n">
         <v>139.3</v>
@@ -7069,9 +6853,7 @@
       <c r="T86" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U86" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="2" t="n">
         <v>140.9</v>
@@ -7144,9 +6926,7 @@
       <c r="T87" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U87" s="2" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="2" t="n">
         <v>137.6</v>
@@ -7219,9 +6999,7 @@
       <c r="T88" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U88" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="2" t="n">
         <v>137.3</v>
@@ -7294,9 +7072,7 @@
       <c r="T89" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U89" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="2" t="n">
         <v>138.2</v>
@@ -7369,9 +7145,7 @@
       <c r="T90" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U90" s="2" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
       <c r="W90" s="2" t="n">
         <v>141</v>
@@ -7444,9 +7218,7 @@
       <c r="T91" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U91" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="2" t="n">
         <v>141.6</v>
@@ -7519,9 +7291,7 @@
       <c r="T92" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U92" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="2" t="n">
         <v>137.5</v>
@@ -7594,9 +7364,7 @@
       <c r="T93" s="2" t="n">
         <v>18.5</v>
       </c>
-      <c r="U93" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="2" t="n">
         <v>140.1</v>
@@ -7669,9 +7437,7 @@
       <c r="T94" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U94" s="2" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="2" t="n">
         <v>138.9</v>
@@ -7744,9 +7510,7 @@
       <c r="T95" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U95" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="2" t="n">
         <v>139.2</v>
@@ -7819,9 +7583,7 @@
       <c r="T96" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U96" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="2" t="n">
         <v>141.2</v>
@@ -7860,7 +7622,7 @@
         <v>2.6</v>
       </c>
       <c r="J97" t="n">
-        <v>19240.32</v>
+        <v>19240.31</v>
       </c>
       <c r="K97" t="n">
         <v>17918.44</v>
@@ -7894,9 +7656,7 @@
       <c r="T97" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U97" s="2" t="n">
-        <v>13.9</v>
-      </c>
+      <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="2" t="n">
         <v>141.4</v>
@@ -7969,9 +7729,7 @@
       <c r="T98" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U98" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="2" t="n">
         <v>145.6</v>
@@ -8044,9 +7802,7 @@
       <c r="T99" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U99" s="2" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" s="2" t="n">
         <v>149.6</v>
@@ -8119,9 +7875,7 @@
       <c r="T100" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U100" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" t="inlineStr"/>
       <c r="W100" s="1" t="n">
         <v>156.6</v>
@@ -8194,9 +7948,7 @@
       <c r="T101" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U101" s="2" t="n">
-        <v>21</v>
-      </c>
+      <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="2" t="n">
         <v>154.4</v>
@@ -8269,9 +8021,7 @@
       <c r="T102" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U102" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="2" t="n">
         <v>148.4</v>
@@ -8344,9 +8094,7 @@
       <c r="T103" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U103" s="2" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="U103" s="2" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="2" t="n">
         <v>149.2</v>
@@ -8419,9 +8167,7 @@
       <c r="T104" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U104" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U104" s="2" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="2" t="n">
         <v>154.8</v>
@@ -8494,9 +8240,7 @@
       <c r="T105" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U105" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U105" s="2" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="1" t="n">
         <v>155</v>
@@ -8569,9 +8313,7 @@
       <c r="T106" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U106" s="2" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U106" s="2" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="2" t="n">
         <v>152.2</v>
@@ -8644,9 +8386,7 @@
       <c r="T107" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U107" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U107" s="2" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="2" t="n">
         <v>147.5</v>
@@ -8719,9 +8459,7 @@
       <c r="T108" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U108" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U108" s="2" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="2" t="n">
         <v>143.4</v>
@@ -8794,9 +8532,7 @@
       <c r="T109" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U109" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U109" s="2" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="2" t="n">
         <v>139.6</v>
@@ -8869,9 +8605,7 @@
       <c r="T110" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U110" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U110" s="2" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="2" t="n">
         <v>140.1</v>
@@ -8944,9 +8678,7 @@
       <c r="T111" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U111" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U111" s="2" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="2" t="n">
         <v>139.3</v>
@@ -9019,9 +8751,7 @@
       <c r="T112" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U112" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U112" s="2" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="2" t="n">
         <v>141.4</v>
@@ -9094,9 +8824,7 @@
       <c r="T113" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U113" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U113" s="2" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="2" t="n">
         <v>138</v>
@@ -9169,9 +8897,7 @@
       <c r="T114" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U114" s="2" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U114" s="2" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="2" t="n">
         <v>140.8</v>
@@ -9244,9 +8970,7 @@
       <c r="T115" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U115" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U115" s="2" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="2" t="n">
         <v>141.8</v>
@@ -9319,9 +9043,7 @@
       <c r="T116" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U116" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U116" s="2" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="2" t="n">
         <v>143.3</v>
@@ -9394,9 +9116,7 @@
       <c r="T117" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U117" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U117" s="2" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
       <c r="W117" s="2" t="n">
         <v>145</v>
@@ -9469,9 +9189,7 @@
       <c r="T118" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U118" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U118" s="2" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
       <c r="W118" s="2" t="n">
         <v>147</v>
@@ -9544,9 +9262,7 @@
       <c r="T119" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U119" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U119" s="2" t="inlineStr"/>
       <c r="V119" t="inlineStr"/>
       <c r="W119" s="2" t="n">
         <v>143.7</v>
@@ -9619,9 +9335,7 @@
       <c r="T120" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U120" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U120" s="2" t="inlineStr"/>
       <c r="V120" t="inlineStr"/>
       <c r="W120" s="2" t="n">
         <v>146.7</v>
@@ -9694,9 +9408,7 @@
       <c r="T121" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U121" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U121" s="2" t="inlineStr"/>
       <c r="V121" t="inlineStr"/>
       <c r="W121" s="2" t="n">
         <v>151.1</v>
@@ -9769,9 +9481,7 @@
       <c r="T122" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U122" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U122" s="2" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
       <c r="W122" s="2" t="n">
         <v>150.4</v>
@@ -9844,9 +9554,7 @@
       <c r="T123" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U123" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U123" s="2" t="inlineStr"/>
       <c r="V123" t="inlineStr"/>
       <c r="W123" s="2" t="n">
         <v>154.8</v>
@@ -9919,9 +9627,7 @@
       <c r="T124" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U124" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U124" s="2" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="2" t="n">
         <v>153.4</v>
@@ -9994,9 +9700,7 @@
       <c r="T125" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U125" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U125" s="2" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="1" t="n">
         <v>159.3</v>
@@ -10069,9 +9773,7 @@
       <c r="T126" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U126" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U126" s="2" t="inlineStr"/>
       <c r="V126" t="inlineStr"/>
       <c r="W126" s="1" t="n">
         <v>159.4</v>
@@ -10144,9 +9846,7 @@
       <c r="T127" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U127" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U127" s="2" t="inlineStr"/>
       <c r="V127" t="inlineStr"/>
       <c r="W127" s="2" t="n">
         <v>145.6</v>
@@ -10219,9 +9919,7 @@
       <c r="T128" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U128" s="2" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="U128" s="2" t="inlineStr"/>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="2" t="n">
         <v>147.6</v>
@@ -10294,9 +9992,7 @@
       <c r="T129" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U129" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U129" s="2" t="inlineStr"/>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="2" t="n">
         <v>149.1</v>
@@ -10369,9 +10065,7 @@
       <c r="T130" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U130" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U130" s="2" t="inlineStr"/>
       <c r="V130" t="inlineStr"/>
       <c r="W130" s="2" t="n">
         <v>154.1</v>
@@ -10444,9 +10138,7 @@
       <c r="T131" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U131" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U131" s="2" t="inlineStr"/>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="2" t="n">
         <v>152.3</v>
@@ -10523,9 +10215,7 @@
       <c r="T132" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U132" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="U132" s="2" t="inlineStr"/>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="1" t="n">
         <v>155.5</v>
@@ -10598,9 +10288,7 @@
       <c r="T133" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U133" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U133" s="2" t="inlineStr"/>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="1" t="n">
         <v>159.3</v>
@@ -10673,9 +10361,7 @@
       <c r="T134" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U134" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U134" s="2" t="inlineStr"/>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="2" t="n">
         <v>149.9</v>
@@ -10748,9 +10434,7 @@
       <c r="T135" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U135" s="2" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U135" s="2" t="inlineStr"/>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="2" t="n">
         <v>149.7</v>
@@ -10823,9 +10507,7 @@
       <c r="T136" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U136" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U136" s="2" t="inlineStr"/>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="2" t="n">
         <v>147</v>
@@ -10898,9 +10580,7 @@
       <c r="T137" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U137" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U137" s="2" t="inlineStr"/>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="2" t="n">
         <v>147.5</v>
@@ -10973,9 +10653,7 @@
       <c r="T138" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U138" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U138" s="2" t="inlineStr"/>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="2" t="n">
         <v>148.6</v>
@@ -11048,9 +10726,7 @@
       <c r="T139" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U139" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U139" s="2" t="inlineStr"/>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="2" t="n">
         <v>151.4</v>
@@ -11123,9 +10799,7 @@
       <c r="T140" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U140" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U140" s="2" t="inlineStr"/>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="2" t="n">
         <v>153.1</v>
@@ -11198,9 +10872,7 @@
       <c r="T141" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U141" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U141" s="2" t="inlineStr"/>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="2" t="n">
         <v>150.6</v>
@@ -11273,9 +10945,7 @@
       <c r="T142" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U142" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U142" s="2" t="inlineStr"/>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="2" t="n">
         <v>153.8</v>
@@ -11348,9 +11018,7 @@
       <c r="T143" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U143" s="2" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U143" s="2" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="2" t="n">
         <v>153.9</v>
@@ -11423,9 +11091,7 @@
       <c r="T144" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U144" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U144" s="2" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="2" t="n">
         <v>153.2</v>
@@ -11502,9 +11168,7 @@
       <c r="T145" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U145" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U145" s="2" t="inlineStr"/>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="2" t="n">
         <v>144.6</v>
@@ -11577,9 +11241,7 @@
       <c r="T146" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U146" s="2" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U146" s="2" t="inlineStr"/>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="2" t="n">
         <v>144.3</v>
@@ -11652,9 +11314,7 @@
       <c r="T147" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U147" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U147" s="2" t="inlineStr"/>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="2" t="n">
         <v>146.4</v>
@@ -11727,9 +11387,7 @@
       <c r="T148" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U148" s="2" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="U148" s="2" t="inlineStr"/>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="2" t="n">
         <v>150</v>
@@ -11802,9 +11460,7 @@
       <c r="T149" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U149" s="2" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U149" s="2" t="inlineStr"/>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="1" t="n">
         <v>156.5</v>
@@ -11877,9 +11533,7 @@
       <c r="T150" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U150" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U150" s="2" t="inlineStr"/>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="2" t="n">
         <v>150.9</v>
@@ -11952,9 +11606,7 @@
       <c r="T151" s="2" t="n">
         <v>14.4</v>
       </c>
-      <c r="U151" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U151" s="2" t="inlineStr"/>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="2" t="n">
         <v>152.5</v>
@@ -12027,9 +11679,7 @@
       <c r="T152" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U152" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U152" s="2" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="2" t="n">
         <v>152.1</v>
@@ -12106,9 +11756,7 @@
       <c r="T153" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U153" s="2" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U153" s="2" t="inlineStr"/>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="2" t="n">
         <v>151.5</v>
@@ -12181,9 +11829,7 @@
       <c r="T154" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U154" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U154" s="2" t="inlineStr"/>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="2" t="n">
         <v>150.2</v>
@@ -12256,9 +11902,7 @@
       <c r="T155" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U155" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U155" s="2" t="inlineStr"/>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="2" t="n">
         <v>154</v>
@@ -12331,9 +11975,7 @@
       <c r="T156" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U156" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U156" s="2" t="inlineStr"/>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="2" t="n">
         <v>148.2</v>
@@ -12406,9 +12048,7 @@
       <c r="T157" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U157" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U157" s="2" t="inlineStr"/>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="2" t="n">
         <v>148.8</v>
@@ -12481,9 +12121,7 @@
       <c r="T158" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U158" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U158" s="2" t="inlineStr"/>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="2" t="n">
         <v>150.9</v>
@@ -12556,9 +12194,7 @@
       <c r="T159" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U159" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U159" s="2" t="inlineStr"/>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="2" t="n">
         <v>151.9</v>
@@ -12631,9 +12267,7 @@
       <c r="T160" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U160" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U160" s="2" t="inlineStr"/>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="2" t="n">
         <v>147.6</v>
@@ -12706,9 +12340,7 @@
       <c r="T161" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U161" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U161" s="2" t="inlineStr"/>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="2" t="n">
         <v>149.5</v>
@@ -12781,9 +12413,7 @@
       <c r="T162" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U162" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U162" s="2" t="inlineStr"/>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="2" t="n">
         <v>152.1</v>
@@ -12856,9 +12486,7 @@
       <c r="T163" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U163" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U163" s="2" t="inlineStr"/>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="2" t="n">
         <v>148.2</v>
@@ -12931,9 +12559,7 @@
       <c r="T164" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U164" s="2" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U164" s="2" t="inlineStr"/>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="2" t="n">
         <v>146.4</v>
@@ -13006,9 +12632,7 @@
       <c r="T165" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U165" s="2" t="n">
-        <v>14.4</v>
-      </c>
+      <c r="U165" s="2" t="inlineStr"/>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="2" t="n">
         <v>148.2</v>
@@ -13081,9 +12705,7 @@
       <c r="T166" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U166" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U166" s="2" t="inlineStr"/>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="2" t="n">
         <v>147</v>
@@ -13156,9 +12778,7 @@
       <c r="T167" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U167" s="2" t="n">
-        <v>9.1</v>
-      </c>
+      <c r="U167" s="2" t="inlineStr"/>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="2" t="n">
         <v>145.5</v>
@@ -13231,9 +12851,7 @@
       <c r="T168" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U168" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U168" s="2" t="inlineStr"/>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="2" t="n">
         <v>146.5</v>
@@ -13306,9 +12924,7 @@
       <c r="T169" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U169" s="2" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U169" s="2" t="inlineStr"/>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="2" t="n">
         <v>145.9</v>
@@ -13381,9 +12997,7 @@
       <c r="T170" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U170" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U170" s="2" t="inlineStr"/>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="2" t="n">
         <v>145.9</v>
@@ -13456,9 +13070,7 @@
       <c r="T171" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U171" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U171" s="2" t="inlineStr"/>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="2" t="n">
         <v>141.5</v>
@@ -13531,9 +13143,7 @@
       <c r="T172" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U172" s="2" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U172" s="2" t="inlineStr"/>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="2" t="n">
         <v>143</v>
@@ -13606,9 +13216,7 @@
       <c r="T173" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U173" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U173" s="2" t="inlineStr"/>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="2" t="n">
         <v>143.4</v>
@@ -13681,9 +13289,7 @@
       <c r="T174" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U174" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U174" s="2" t="inlineStr"/>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="2" t="n">
         <v>143.7</v>
@@ -13756,9 +13362,7 @@
       <c r="T175" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U175" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U175" s="2" t="inlineStr"/>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="2" t="n">
         <v>145.9</v>
@@ -13831,9 +13435,7 @@
       <c r="T176" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U176" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U176" s="2" t="inlineStr"/>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="2" t="n">
         <v>144.6</v>
@@ -13906,9 +13508,7 @@
       <c r="T177" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U177" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U177" s="2" t="inlineStr"/>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="2" t="n">
         <v>142.5</v>
@@ -13981,9 +13581,7 @@
       <c r="T178" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U178" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U178" s="2" t="inlineStr"/>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="2" t="n">
         <v>145.2</v>
@@ -14056,9 +13654,7 @@
       <c r="T179" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U179" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U179" s="2" t="inlineStr"/>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="2" t="n">
         <v>145.8</v>
@@ -14131,9 +13727,7 @@
       <c r="T180" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U180" s="2" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U180" s="2" t="inlineStr"/>
       <c r="V180" t="inlineStr"/>
       <c r="W180" s="2" t="n">
         <v>145.3</v>
@@ -14210,9 +13804,7 @@
       <c r="T181" s="5" t="n">
         <v>21.7</v>
       </c>
-      <c r="U181" s="7" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U181" s="5" t="inlineStr"/>
       <c r="V181" s="3" t="inlineStr"/>
       <c r="W181" s="5" t="n">
         <v>138.9</v>
@@ -14285,9 +13877,7 @@
       <c r="T182" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U182" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U182" s="2" t="inlineStr"/>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="2" t="n">
         <v>142.8</v>
@@ -14364,9 +13954,7 @@
       <c r="T183" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U183" s="2" t="n">
-        <v>17.7</v>
-      </c>
+      <c r="U183" s="2" t="inlineStr"/>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="2" t="n">
         <v>146.5</v>
@@ -14439,9 +14027,7 @@
       <c r="T184" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U184" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U184" s="2" t="inlineStr"/>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="2" t="n">
         <v>145</v>
@@ -14518,9 +14104,7 @@
       <c r="T185" s="6" t="n">
         <v>25.3</v>
       </c>
-      <c r="U185" s="2" t="n">
-        <v>23.8</v>
-      </c>
+      <c r="U185" s="2" t="inlineStr"/>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="2" t="n">
         <v>147.1</v>
@@ -14593,9 +14177,7 @@
       <c r="T186" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U186" s="2" t="n">
-        <v>17.9</v>
-      </c>
+      <c r="U186" s="2" t="inlineStr"/>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="2" t="n">
         <v>147.6</v>
@@ -14668,9 +14250,7 @@
       <c r="T187" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U187" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U187" s="2" t="inlineStr"/>
       <c r="V187" t="inlineStr"/>
       <c r="W187" s="2" t="n">
         <v>151.3</v>
@@ -14743,9 +14323,7 @@
       <c r="T188" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U188" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U188" s="2" t="inlineStr"/>
       <c r="V188" t="inlineStr"/>
       <c r="W188" s="2" t="n">
         <v>149.9</v>
@@ -14818,9 +14396,7 @@
       <c r="T189" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U189" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U189" s="2" t="inlineStr"/>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="2" t="n">
         <v>152.9</v>
@@ -14893,9 +14469,7 @@
       <c r="T190" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U190" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U190" s="2" t="inlineStr"/>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="2" t="n">
         <v>154.3</v>
@@ -14968,9 +14542,7 @@
       <c r="T191" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U191" s="2" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U191" s="2" t="inlineStr"/>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="2" t="n">
         <v>153.5</v>
@@ -15043,9 +14615,7 @@
       <c r="T192" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U192" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U192" s="2" t="inlineStr"/>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="2" t="n">
         <v>148.5</v>
@@ -15118,9 +14688,7 @@
       <c r="T193" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U193" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U193" s="2" t="inlineStr"/>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="2" t="n">
         <v>140.4</v>
@@ -15193,9 +14761,7 @@
       <c r="T194" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U194" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U194" s="2" t="inlineStr"/>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="2" t="n">
         <v>139.4</v>
@@ -15268,9 +14834,7 @@
       <c r="T195" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U195" s="2" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U195" s="2" t="inlineStr"/>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="2" t="n">
         <v>141.1</v>
@@ -15343,9 +14907,7 @@
       <c r="T196" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U196" s="2" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U196" s="2" t="inlineStr"/>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="2" t="n">
         <v>142.8</v>
@@ -15418,9 +14980,7 @@
       <c r="T197" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U197" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="U197" s="2" t="inlineStr"/>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="2" t="n">
         <v>142</v>
@@ -15493,9 +15053,7 @@
       <c r="T198" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U198" s="2" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U198" s="2" t="inlineStr"/>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="2" t="n">
         <v>144</v>
@@ -15568,9 +15126,7 @@
       <c r="T199" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U199" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U199" s="2" t="inlineStr"/>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="2" t="n">
         <v>143.6</v>
@@ -15647,9 +15203,7 @@
       <c r="T200" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U200" s="2" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U200" s="2" t="inlineStr"/>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="2" t="n">
         <v>143.5</v>
@@ -15722,9 +15276,7 @@
       <c r="T201" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U201" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U201" s="2" t="inlineStr"/>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="2" t="n">
         <v>141.3</v>
@@ -15797,9 +15349,7 @@
       <c r="T202" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U202" s="2" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U202" s="2" t="inlineStr"/>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="2" t="n">
         <v>142.9</v>
@@ -15872,9 +15422,7 @@
       <c r="T203" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U203" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U203" s="2" t="inlineStr"/>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="2" t="n">
         <v>143.4</v>
@@ -15947,9 +15495,7 @@
       <c r="T204" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U204" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U204" s="2" t="inlineStr"/>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="2" t="n">
         <v>138.6</v>
@@ -16026,9 +15572,7 @@
       <c r="T205" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="U205" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U205" s="2" t="inlineStr"/>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="2" t="n">
         <v>142.5</v>
@@ -16101,9 +15645,7 @@
       <c r="T206" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U206" s="2" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U206" s="2" t="inlineStr"/>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="2" t="n">
         <v>137.9</v>
@@ -16176,9 +15718,7 @@
       <c r="T207" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U207" s="2" t="n">
-        <v>19.4</v>
-      </c>
+      <c r="U207" s="2" t="inlineStr"/>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="2" t="n">
         <v>140.9</v>
@@ -16255,9 +15795,7 @@
       <c r="T208" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U208" s="2" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="U208" s="2" t="inlineStr"/>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="2" t="n">
         <v>143</v>
@@ -16330,9 +15868,7 @@
       <c r="T209" s="2" t="n">
         <v>23.7</v>
       </c>
-      <c r="U209" s="6" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U209" s="2" t="inlineStr"/>
       <c r="V209" t="inlineStr"/>
       <c r="W209" s="2" t="n">
         <v>143.1</v>
@@ -16405,14 +15941,8 @@
       <c r="T210" s="6" t="n">
         <v>26.4</v>
       </c>
-      <c r="U210" s="6" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="V210" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U210" s="2" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
       <c r="W210" s="2" t="n">
         <v>145</v>
       </c>
@@ -16484,9 +16014,7 @@
       <c r="T211" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U211" s="2" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="U211" s="2" t="inlineStr"/>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="2" t="n">
         <v>148.3</v>
@@ -16559,9 +16087,7 @@
       <c r="T212" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U212" s="2" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U212" s="2" t="inlineStr"/>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="2" t="n">
         <v>148.6</v>
@@ -16634,9 +16160,7 @@
       <c r="T213" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U213" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U213" s="2" t="inlineStr"/>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="2" t="n">
         <v>151.7</v>
@@ -16709,9 +16233,7 @@
       <c r="T214" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U214" s="2" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U214" s="2" t="inlineStr"/>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="2" t="n">
         <v>145</v>
@@ -16784,9 +16306,7 @@
       <c r="T215" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U215" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U215" s="2" t="inlineStr"/>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="2" t="n">
         <v>143</v>
@@ -16859,9 +16379,7 @@
       <c r="T216" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U216" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U216" s="2" t="inlineStr"/>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="2" t="n">
         <v>144.9</v>
@@ -16934,9 +16452,7 @@
       <c r="T217" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U217" s="2" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U217" s="2" t="inlineStr"/>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="2" t="n">
         <v>144.9</v>
@@ -17009,9 +16525,7 @@
       <c r="T218" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U218" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
+      <c r="U218" s="2" t="inlineStr"/>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="2" t="n">
         <v>149.2</v>
@@ -17084,9 +16598,7 @@
       <c r="T219" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U219" s="2" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U219" s="2" t="inlineStr"/>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="2" t="n">
         <v>148.9</v>
@@ -17159,9 +16671,7 @@
       <c r="T220" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U220" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U220" s="2" t="inlineStr"/>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="2" t="n">
         <v>148.8</v>
@@ -17234,9 +16744,7 @@
       <c r="T221" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U221" s="2" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U221" s="2" t="inlineStr"/>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="2" t="n">
         <v>150.6</v>
@@ -17309,9 +16817,7 @@
       <c r="T222" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U222" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U222" s="2" t="inlineStr"/>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="2" t="n">
         <v>150.3</v>
@@ -17384,9 +16890,7 @@
       <c r="T223" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U223" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U223" s="2" t="inlineStr"/>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="2" t="n">
         <v>147.6</v>
@@ -17459,9 +16963,7 @@
       <c r="T224" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U224" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U224" s="2" t="inlineStr"/>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="2" t="n">
         <v>148.3</v>
@@ -17534,9 +17036,7 @@
       <c r="T225" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U225" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U225" s="2" t="inlineStr"/>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="2" t="n">
         <v>153.6</v>
@@ -17613,9 +17113,7 @@
       <c r="T226" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U226" s="2" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U226" s="2" t="inlineStr"/>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="1" t="n">
         <v>161.9</v>
@@ -17688,9 +17186,7 @@
       <c r="T227" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U227" s="2" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U227" s="2" t="inlineStr"/>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="1" t="n">
         <v>157</v>
@@ -17767,9 +17263,7 @@
       <c r="T228" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U228" s="2" t="n">
-        <v>16.9</v>
-      </c>
+      <c r="U228" s="2" t="inlineStr"/>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="2" t="n">
         <v>153.5</v>
@@ -17842,9 +17336,7 @@
       <c r="T229" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U229" s="2" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U229" s="2" t="inlineStr"/>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="1" t="n">
         <v>155.4</v>
@@ -17917,9 +17409,7 @@
       <c r="T230" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U230" s="2" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U230" s="2" t="inlineStr"/>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="1" t="n">
         <v>155.9</v>
@@ -17992,9 +17482,7 @@
       <c r="T231" s="2" t="n">
         <v>14.1</v>
       </c>
-      <c r="U231" s="2" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U231" s="2" t="inlineStr"/>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="1" t="n">
         <v>159.9</v>
@@ -18067,9 +17555,7 @@
       <c r="T232" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="U232" s="2" t="n">
-        <v>7.6</v>
-      </c>
+      <c r="U232" s="2" t="inlineStr"/>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="1" t="n">
         <v>160.5</v>
@@ -18142,9 +17628,7 @@
       <c r="T233" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="U233" s="2" t="n">
-        <v>7.4</v>
-      </c>
+      <c r="U233" s="2" t="inlineStr"/>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="1" t="n">
         <v>160.5</v>
@@ -18217,9 +17701,7 @@
       <c r="T234" s="2" t="n">
         <v>13.6</v>
       </c>
-      <c r="U234" s="2" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U234" s="2" t="inlineStr"/>
       <c r="V234" t="inlineStr"/>
       <c r="W234" s="2" t="n">
         <v>151.4</v>
@@ -18292,9 +17774,7 @@
       <c r="T235" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U235" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="U235" s="2" t="inlineStr"/>
       <c r="V235" t="inlineStr"/>
       <c r="W235" s="2" t="n">
         <v>150.5</v>
@@ -18367,9 +17847,7 @@
       <c r="T236" s="2" t="n">
         <v>14.3</v>
       </c>
-      <c r="U236" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U236" s="2" t="inlineStr"/>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="2" t="n">
         <v>148.3</v>
@@ -18446,9 +17924,7 @@
       <c r="T237" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U237" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U237" s="2" t="inlineStr"/>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="2" t="n">
         <v>148.7</v>
@@ -18521,9 +17997,7 @@
       <c r="T238" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U238" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U238" s="2" t="inlineStr"/>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="2" t="n">
         <v>141.9</v>
@@ -18596,9 +18070,7 @@
       <c r="T239" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U239" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U239" s="2" t="inlineStr"/>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="2" t="n">
         <v>142.4</v>
@@ -18671,9 +18143,7 @@
       <c r="T240" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U240" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="U240" s="2" t="inlineStr"/>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="2" t="n">
         <v>146.2</v>
@@ -18746,9 +18216,7 @@
       <c r="T241" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U241" s="2" t="n">
-        <v>9.199999999999999</v>
-      </c>
+      <c r="U241" s="2" t="inlineStr"/>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="2" t="n">
         <v>143.6</v>
@@ -18821,9 +18289,7 @@
       <c r="T242" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U242" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U242" s="2" t="inlineStr"/>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="2" t="n">
         <v>147.1</v>
@@ -18896,9 +18362,7 @@
       <c r="T243" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U243" s="2" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="U243" s="2" t="inlineStr"/>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="2" t="n">
         <v>146</v>
@@ -18971,9 +18435,7 @@
       <c r="T244" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U244" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U244" s="2" t="inlineStr"/>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="2" t="n">
         <v>149.8</v>
@@ -19046,9 +18508,7 @@
       <c r="T245" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U245" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U245" s="2" t="inlineStr"/>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="2" t="n">
         <v>151.6</v>
@@ -19121,9 +18581,7 @@
       <c r="T246" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U246" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U246" s="2" t="inlineStr"/>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="2" t="n">
         <v>152.5</v>
@@ -19196,9 +18654,7 @@
       <c r="T247" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U247" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U247" s="2" t="inlineStr"/>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="2" t="n">
         <v>151.6</v>
@@ -19271,9 +18727,7 @@
       <c r="T248" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U248" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U248" s="2" t="inlineStr"/>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="2" t="n">
         <v>153.6</v>
@@ -19350,9 +18804,7 @@
       <c r="T249" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U249" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U249" s="2" t="inlineStr"/>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="1" t="n">
         <v>155</v>
@@ -19425,9 +18877,7 @@
       <c r="T250" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U250" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U250" s="2" t="inlineStr"/>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="2" t="n">
         <v>144.4</v>
@@ -19500,9 +18950,7 @@
       <c r="T251" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U251" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U251" s="2" t="inlineStr"/>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="2" t="n">
         <v>141.3</v>
@@ -19575,9 +19023,7 @@
       <c r="T252" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U252" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U252" s="2" t="inlineStr"/>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="2" t="n">
         <v>144</v>
@@ -19650,9 +19096,7 @@
       <c r="T253" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U253" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="U253" s="2" t="inlineStr"/>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="2" t="n">
         <v>148.1</v>
@@ -19725,9 +19169,7 @@
       <c r="T254" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U254" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U254" s="2" t="inlineStr"/>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="2" t="n">
         <v>147.2</v>
@@ -19800,9 +19242,7 @@
       <c r="T255" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U255" s="2" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U255" s="2" t="inlineStr"/>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="2" t="n">
         <v>145</v>
@@ -19875,9 +19315,7 @@
       <c r="T256" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U256" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U256" s="2" t="inlineStr"/>
       <c r="V256" t="inlineStr"/>
       <c r="W256" s="2" t="n">
         <v>143.7</v>
@@ -19954,9 +19392,7 @@
       <c r="T257" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U257" s="2" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U257" s="2" t="inlineStr"/>
       <c r="V257" t="inlineStr"/>
       <c r="W257" s="2" t="n">
         <v>143.6</v>
@@ -20029,9 +19465,7 @@
       <c r="T258" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U258" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U258" s="2" t="inlineStr"/>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="2" t="n">
         <v>146.6</v>
@@ -20108,9 +19542,7 @@
       <c r="T259" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U259" s="2" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U259" s="2" t="inlineStr"/>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="2" t="n">
         <v>143.9</v>
@@ -20183,9 +19615,7 @@
       <c r="T260" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U260" s="2" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U260" s="2" t="inlineStr"/>
       <c r="V260" t="inlineStr"/>
       <c r="W260" s="2" t="n">
         <v>143.2</v>
@@ -20262,9 +19692,7 @@
       <c r="T261" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U261" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U261" s="2" t="inlineStr"/>
       <c r="V261" t="inlineStr"/>
       <c r="W261" s="2" t="n">
         <v>137.2</v>
@@ -20337,9 +19765,7 @@
       <c r="T262" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U262" s="2" t="n">
-        <v>15</v>
-      </c>
+      <c r="U262" s="2" t="inlineStr"/>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="2" t="n">
         <v>140.3</v>
@@ -20412,9 +19838,7 @@
       <c r="T263" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U263" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U263" s="2" t="inlineStr"/>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="2" t="n">
         <v>145.2</v>
@@ -20487,9 +19911,7 @@
       <c r="T264" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U264" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U264" s="2" t="inlineStr"/>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="2" t="n">
         <v>145.7</v>
@@ -20562,9 +19984,7 @@
       <c r="T265" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U265" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U265" s="2" t="inlineStr"/>
       <c r="V265" t="inlineStr"/>
       <c r="W265" s="2" t="n">
         <v>143.8</v>
@@ -20641,9 +20061,7 @@
       <c r="T266" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U266" s="2" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="U266" s="2" t="inlineStr"/>
       <c r="V266" t="inlineStr"/>
       <c r="W266" s="2" t="n">
         <v>142.5</v>
@@ -20716,9 +20134,7 @@
       <c r="T267" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U267" s="2" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="U267" s="2" t="inlineStr"/>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="2" t="n">
         <v>139.4</v>
@@ -20791,9 +20207,7 @@
       <c r="T268" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U268" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U268" s="2" t="inlineStr"/>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="2" t="n">
         <v>140.3</v>
@@ -20866,9 +20280,7 @@
       <c r="T269" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U269" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U269" s="2" t="inlineStr"/>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="2" t="n">
         <v>139.2</v>
@@ -20941,9 +20353,7 @@
       <c r="T270" s="2" t="n">
         <v>20.2</v>
       </c>
-      <c r="U270" s="2" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U270" s="2" t="inlineStr"/>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="2" t="n">
         <v>141.2</v>
@@ -21016,9 +20426,7 @@
       <c r="T271" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U271" s="2" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U271" s="2" t="inlineStr"/>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="2" t="n">
         <v>145.5</v>
@@ -21091,9 +20499,7 @@
       <c r="T272" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U272" s="2" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U272" s="2" t="inlineStr"/>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="2" t="n">
         <v>141.4</v>
@@ -21166,9 +20572,7 @@
       <c r="T273" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U273" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U273" s="2" t="inlineStr"/>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="2" t="n">
         <v>141.9</v>
@@ -21241,9 +20645,7 @@
       <c r="T274" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U274" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U274" s="2" t="inlineStr"/>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="2" t="n">
         <v>146.1</v>
@@ -21320,9 +20722,7 @@
       <c r="T275" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U275" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U275" s="2" t="inlineStr"/>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="2" t="n">
         <v>146.6</v>
@@ -21395,9 +20795,7 @@
       <c r="T276" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U276" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U276" s="2" t="inlineStr"/>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="2" t="n">
         <v>146.7</v>
@@ -21470,9 +20868,7 @@
       <c r="T277" s="2" t="n">
         <v>21.4</v>
       </c>
-      <c r="U277" s="2" t="n">
-        <v>16.3</v>
-      </c>
+      <c r="U277" s="2" t="inlineStr"/>
       <c r="V277" t="inlineStr"/>
       <c r="W277" s="2" t="n">
         <v>151.8</v>
@@ -21545,9 +20941,7 @@
       <c r="T278" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U278" s="2" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="U278" s="2" t="inlineStr"/>
       <c r="V278" t="inlineStr"/>
       <c r="W278" s="2" t="n">
         <v>152.8</v>
@@ -21620,9 +21014,7 @@
       <c r="T279" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U279" s="2" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U279" s="2" t="inlineStr"/>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="2" t="n">
         <v>152.9</v>
@@ -21695,9 +21087,7 @@
       <c r="T280" s="2" t="n">
         <v>23.8</v>
       </c>
-      <c r="U280" s="2" t="n">
-        <v>21.9</v>
-      </c>
+      <c r="U280" s="2" t="inlineStr"/>
       <c r="V280" t="inlineStr"/>
       <c r="W280" s="2" t="n">
         <v>153.9</v>
@@ -21770,14 +21160,8 @@
       <c r="T281" s="6" t="n">
         <v>29.5</v>
       </c>
-      <c r="U281" s="6" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="V281" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U281" s="2" t="inlineStr"/>
+      <c r="V281" t="inlineStr"/>
       <c r="W281" s="2" t="n">
         <v>151.8</v>
       </c>
@@ -21849,9 +21233,7 @@
       <c r="T282" s="6" t="n">
         <v>25.5</v>
       </c>
-      <c r="U282" s="2" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="U282" s="2" t="inlineStr"/>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="1" t="n">
         <v>158</v>
@@ -21924,9 +21306,7 @@
       <c r="T283" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U283" s="2" t="n">
-        <v>21.3</v>
-      </c>
+      <c r="U283" s="2" t="inlineStr"/>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="2" t="n">
         <v>154.5</v>
@@ -21999,9 +21379,7 @@
       <c r="T284" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U284" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U284" s="2" t="inlineStr"/>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="2" t="n">
         <v>152.4</v>
@@ -22068,9 +21446,7 @@
       <c r="T285" s="6" t="n">
         <v>27.3</v>
       </c>
-      <c r="U285" s="2" t="n">
-        <v>24.2</v>
-      </c>
+      <c r="U285" s="2" t="inlineStr"/>
       <c r="V285" t="inlineStr"/>
       <c r="W285" s="2" t="n">
         <v>139.9</v>
@@ -22143,14 +21519,8 @@
       <c r="T286" s="6" t="n">
         <v>27.2</v>
       </c>
-      <c r="U286" s="6" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="V286" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U286" s="2" t="inlineStr"/>
+      <c r="V286" t="inlineStr"/>
       <c r="W286" s="2" t="n">
         <v>137.8</v>
       </c>
@@ -22222,9 +21592,7 @@
       <c r="T287" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U287" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U287" s="2" t="inlineStr"/>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="2" t="n">
         <v>141.5</v>
@@ -22297,9 +21665,7 @@
       <c r="T288" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U288" s="2" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U288" s="2" t="inlineStr"/>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="2" t="n">
         <v>145</v>
@@ -22372,9 +21738,7 @@
       <c r="T289" s="6" t="n">
         <v>25.1</v>
       </c>
-      <c r="U289" s="2" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U289" s="2" t="inlineStr"/>
       <c r="V289" t="inlineStr"/>
       <c r="W289" s="2" t="n">
         <v>136.5</v>
@@ -22447,9 +21811,7 @@
       <c r="T290" s="2" t="n">
         <v>24.1</v>
       </c>
-      <c r="U290" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U290" s="2" t="inlineStr"/>
       <c r="V290" t="inlineStr"/>
       <c r="W290" s="2" t="n">
         <v>138.3</v>
@@ -22522,14 +21884,8 @@
       <c r="T291" s="6" t="n">
         <v>26.8</v>
       </c>
-      <c r="U291" s="6" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="V291" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U291" s="2" t="inlineStr"/>
+      <c r="V291" t="inlineStr"/>
       <c r="W291" s="2" t="n">
         <v>139.1</v>
       </c>
@@ -22601,9 +21957,7 @@
       <c r="T292" s="6" t="n">
         <v>26.1</v>
       </c>
-      <c r="U292" s="2" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U292" s="2" t="inlineStr"/>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="2" t="n">
         <v>142</v>
@@ -22676,9 +22030,7 @@
       <c r="T293" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="U293" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U293" s="2" t="inlineStr"/>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="2" t="n">
         <v>142.6</v>
@@ -22751,9 +22103,7 @@
       <c r="T294" s="6" t="n">
         <v>25.3</v>
       </c>
-      <c r="U294" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U294" s="2" t="inlineStr"/>
       <c r="V294" t="inlineStr"/>
       <c r="W294" s="2" t="n">
         <v>140.9</v>
@@ -22826,9 +22176,7 @@
       <c r="T295" s="6" t="n">
         <v>27.4</v>
       </c>
-      <c r="U295" s="2" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U295" s="2" t="inlineStr"/>
       <c r="V295" t="inlineStr"/>
       <c r="W295" s="2" t="n">
         <v>144</v>
@@ -22905,14 +22253,8 @@
       <c r="T296" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="U296" s="6" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="V296" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U296" s="2" t="inlineStr"/>
+      <c r="V296" t="inlineStr"/>
       <c r="W296" s="2" t="n">
         <v>139</v>
       </c>
@@ -22988,9 +22330,7 @@
       <c r="T297" s="6" t="n">
         <v>30.6</v>
       </c>
-      <c r="U297" s="2" t="n">
-        <v>23</v>
-      </c>
+      <c r="U297" s="2" t="inlineStr"/>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="2" t="n">
         <v>142.2</v>
@@ -23063,9 +22403,7 @@
       <c r="T298" s="6" t="n">
         <v>25.2</v>
       </c>
-      <c r="U298" s="2" t="n">
-        <v>19</v>
-      </c>
+      <c r="U298" s="2" t="inlineStr"/>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="2" t="n">
         <v>145.4</v>
@@ -23138,9 +22476,7 @@
       <c r="T299" s="2" t="n">
         <v>24.5</v>
       </c>
-      <c r="U299" s="2" t="n">
-        <v>23</v>
-      </c>
+      <c r="U299" s="2" t="inlineStr"/>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="2" t="n">
         <v>143.8</v>
@@ -23213,9 +22549,7 @@
       <c r="T300" s="2" t="n">
         <v>23.9</v>
       </c>
-      <c r="U300" s="6" t="n">
-        <v>27.6</v>
-      </c>
+      <c r="U300" s="2" t="inlineStr"/>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="2" t="n">
         <v>146.9</v>
@@ -23288,9 +22622,7 @@
       <c r="T301" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U301" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U301" s="2" t="inlineStr"/>
       <c r="V301" t="inlineStr"/>
       <c r="W301" s="2" t="n">
         <v>147.6</v>
@@ -23363,14 +22695,8 @@
       <c r="T302" s="6" t="n">
         <v>25.8</v>
       </c>
-      <c r="U302" s="6" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="V302" s="6" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U302" s="2" t="inlineStr"/>
+      <c r="V302" t="inlineStr"/>
       <c r="W302" s="2" t="n">
         <v>148.4</v>
       </c>
@@ -23442,9 +22768,7 @@
       <c r="T303" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U303" s="2" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U303" s="2" t="inlineStr"/>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="2" t="n">
         <v>150.4</v>
@@ -23517,9 +22841,7 @@
       <c r="T304" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U304" s="2" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U304" s="2" t="inlineStr"/>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="2" t="n">
         <v>143.3</v>
@@ -23592,9 +22914,7 @@
       <c r="T305" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U305" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U305" s="2" t="inlineStr"/>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="2" t="n">
         <v>144.2</v>
@@ -23667,9 +22987,7 @@
       <c r="T306" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U306" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U306" s="2" t="inlineStr"/>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="1" t="n">
         <v>156.9</v>
@@ -23742,9 +23060,7 @@
       <c r="T307" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U307" s="2" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U307" s="2" t="inlineStr"/>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="2" t="n">
         <v>149.9</v>
@@ -23817,9 +23133,7 @@
       <c r="T308" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U308" s="2" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="U308" s="2" t="inlineStr"/>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="2" t="n">
         <v>139.2</v>
@@ -23892,9 +23206,7 @@
       <c r="T309" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U309" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="U309" s="2" t="inlineStr"/>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="2" t="n">
         <v>140.7</v>
@@ -23967,9 +23279,7 @@
       <c r="T310" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U310" s="2" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U310" s="2" t="inlineStr"/>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="2" t="n">
         <v>141.8</v>
@@ -24042,9 +23352,7 @@
       <c r="T311" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U311" s="2" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U311" s="2" t="inlineStr"/>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="2" t="n">
         <v>141.9</v>
@@ -24117,9 +23425,7 @@
       <c r="T312" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U312" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U312" s="2" t="inlineStr"/>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="2" t="n">
         <v>140.9</v>
@@ -24192,9 +23498,7 @@
       <c r="T313" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U313" s="2" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U313" s="2" t="inlineStr"/>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="2" t="n">
         <v>140.8</v>
@@ -24267,9 +23571,7 @@
       <c r="T314" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U314" s="2" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U314" s="2" t="inlineStr"/>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="2" t="n">
         <v>139.6</v>
@@ -24342,9 +23644,7 @@
       <c r="T315" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U315" s="2" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U315" s="2" t="inlineStr"/>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="2" t="n">
         <v>139.1</v>
@@ -24417,9 +23717,7 @@
       <c r="T316" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U316" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U316" s="2" t="inlineStr"/>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="2" t="n">
         <v>139.6</v>
@@ -24492,9 +23790,7 @@
       <c r="T317" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U317" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U317" s="2" t="inlineStr"/>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="2" t="n">
         <v>138.2</v>
@@ -24567,9 +23863,7 @@
       <c r="T318" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U318" s="2" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U318" s="2" t="inlineStr"/>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="2" t="n">
         <v>141.9</v>
@@ -24642,9 +23936,7 @@
       <c r="T319" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U319" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U319" s="2" t="inlineStr"/>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="2" t="n">
         <v>143.3</v>
@@ -24717,9 +24009,7 @@
       <c r="T320" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U320" s="2" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U320" s="2" t="inlineStr"/>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="2" t="n">
         <v>141.4</v>
@@ -24792,9 +24082,7 @@
       <c r="T321" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U321" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U321" s="2" t="inlineStr"/>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="2" t="n">
         <v>141.7</v>
@@ -24867,9 +24155,7 @@
       <c r="T322" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U322" s="2" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U322" s="2" t="inlineStr"/>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="2" t="n">
         <v>138.7</v>
@@ -24942,9 +24228,7 @@
       <c r="T323" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U323" s="2" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U323" s="2" t="inlineStr"/>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="2" t="n">
         <v>135.4</v>
@@ -25017,9 +24301,7 @@
       <c r="T324" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U324" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U324" s="2" t="inlineStr"/>
       <c r="V324" t="inlineStr"/>
       <c r="W324" s="2" t="n">
         <v>136.1</v>
@@ -25092,9 +24374,7 @@
       <c r="T325" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U325" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U325" s="2" t="inlineStr"/>
       <c r="V325" t="inlineStr"/>
       <c r="W325" s="2" t="n">
         <v>138.2</v>
@@ -25167,9 +24447,7 @@
       <c r="T326" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U326" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U326" s="2" t="inlineStr"/>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="2" t="n">
         <v>140.2</v>
@@ -25242,9 +24520,7 @@
       <c r="T327" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U327" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U327" s="2" t="inlineStr"/>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="2" t="n">
         <v>139.4</v>
@@ -25317,9 +24593,7 @@
       <c r="T328" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U328" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U328" s="2" t="inlineStr"/>
       <c r="V328" t="inlineStr"/>
       <c r="W328" s="2" t="n">
         <v>141.5</v>
@@ -25392,9 +24666,7 @@
       <c r="T329" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U329" s="2" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U329" s="2" t="inlineStr"/>
       <c r="V329" t="inlineStr"/>
       <c r="W329" s="2" t="n">
         <v>139.3</v>
@@ -25467,9 +24739,7 @@
       <c r="T330" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U330" s="2" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U330" s="2" t="inlineStr"/>
       <c r="V330" t="inlineStr"/>
       <c r="W330" s="2" t="n">
         <v>145.8</v>
@@ -25542,9 +24812,7 @@
       <c r="T331" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U331" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U331" s="2" t="inlineStr"/>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="2" t="n">
         <v>138.4</v>
@@ -25617,9 +24885,7 @@
       <c r="T332" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U332" s="2" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U332" s="2" t="inlineStr"/>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="2" t="n">
         <v>135.5</v>
@@ -25692,9 +24958,7 @@
       <c r="T333" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U333" s="2" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U333" s="2" t="inlineStr"/>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="2" t="n">
         <v>132.3</v>
@@ -25767,9 +25031,7 @@
       <c r="T334" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U334" s="2" t="n">
-        <v>14</v>
-      </c>
+      <c r="U334" s="2" t="inlineStr"/>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="2" t="n">
         <v>137</v>
@@ -25842,9 +25104,7 @@
       <c r="T335" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U335" s="2" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U335" s="2" t="inlineStr"/>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="2" t="n">
         <v>137.4</v>
@@ -25917,9 +25177,7 @@
       <c r="T336" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U336" s="2" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U336" s="2" t="inlineStr"/>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="2" t="n">
         <v>139</v>
@@ -25992,9 +25250,7 @@
       <c r="T337" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U337" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U337" s="2" t="inlineStr"/>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="2" t="n">
         <v>138.6</v>
@@ -26067,9 +25323,7 @@
       <c r="T338" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U338" s="2" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U338" s="2" t="inlineStr"/>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="2" t="n">
         <v>139.5</v>
@@ -26142,9 +25396,7 @@
       <c r="T339" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U339" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U339" s="2" t="inlineStr"/>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="2" t="n">
         <v>144.2</v>
@@ -26217,9 +25469,7 @@
       <c r="T340" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U340" s="2" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U340" s="2" t="inlineStr"/>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="2" t="n">
         <v>142.5</v>
@@ -26292,9 +25542,7 @@
       <c r="T341" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U341" s="2" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U341" s="2" t="inlineStr"/>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="2" t="n">
         <v>143.2</v>
@@ -26367,9 +25615,7 @@
       <c r="T342" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U342" s="2" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U342" s="2" t="inlineStr"/>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="2" t="n">
         <v>136.9</v>
@@ -26442,9 +25688,7 @@
       <c r="T343" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U343" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U343" s="2" t="inlineStr"/>
       <c r="V343" t="inlineStr"/>
       <c r="W343" s="2" t="n">
         <v>142.1</v>
@@ -26521,9 +25765,7 @@
       <c r="T344" s="5" t="n">
         <v>21.5</v>
       </c>
-      <c r="U344" s="7" t="n">
-        <v>28.7</v>
-      </c>
+      <c r="U344" s="5" t="inlineStr"/>
       <c r="V344" s="3" t="inlineStr"/>
       <c r="W344" s="5" t="n">
         <v>152.2</v>
@@ -26596,9 +25838,7 @@
       <c r="T345" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U345" s="2" t="n">
-        <v>16</v>
-      </c>
+      <c r="U345" s="2" t="inlineStr"/>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="2" t="n">
         <v>145</v>
@@ -26671,9 +25911,7 @@
       <c r="T346" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U346" s="2" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="U346" s="2" t="inlineStr"/>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="2" t="n">
         <v>142</v>
@@ -26746,9 +25984,7 @@
       <c r="T347" s="2" t="n">
         <v>22.2</v>
       </c>
-      <c r="U347" s="2" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U347" s="2" t="inlineStr"/>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="2" t="n">
         <v>143.1</v>
@@ -26821,9 +26057,7 @@
       <c r="T348" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U348" s="2" t="n">
-        <v>21.1</v>
-      </c>
+      <c r="U348" s="2" t="inlineStr"/>
       <c r="V348" t="inlineStr"/>
       <c r="W348" s="2" t="n">
         <v>143</v>
@@ -26896,9 +26130,7 @@
       <c r="T349" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U349" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U349" s="2" t="inlineStr"/>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="2" t="n">
         <v>142.6</v>
@@ -26971,9 +26203,7 @@
       <c r="T350" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U350" s="2" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U350" s="2" t="inlineStr"/>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="2" t="n">
         <v>144.3</v>
@@ -27046,9 +26276,7 @@
       <c r="T351" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U351" s="2" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U351" s="2" t="inlineStr"/>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="2" t="n">
         <v>142.7</v>
@@ -27125,9 +26353,7 @@
       <c r="T352" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U352" s="2" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U352" s="2" t="inlineStr"/>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="2" t="n">
         <v>142.6</v>
@@ -27200,9 +26426,7 @@
       <c r="T353" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U353" s="2" t="n">
-        <v>15.7</v>
-      </c>
+      <c r="U353" s="2" t="inlineStr"/>
       <c r="V353" t="inlineStr"/>
       <c r="W353" s="2" t="n">
         <v>146.7</v>
@@ -27279,9 +26503,7 @@
       <c r="T354" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U354" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U354" s="2" t="inlineStr"/>
       <c r="V354" t="inlineStr"/>
       <c r="W354" s="2" t="n">
         <v>141.9</v>
@@ -27354,9 +26576,7 @@
       <c r="T355" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U355" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U355" s="2" t="inlineStr"/>
       <c r="V355" t="inlineStr"/>
       <c r="W355" s="2" t="n">
         <v>143.1</v>
@@ -27429,9 +26649,7 @@
       <c r="T356" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U356" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U356" s="2" t="inlineStr"/>
       <c r="V356" t="inlineStr"/>
       <c r="W356" s="2" t="n">
         <v>145.3</v>
@@ -27504,9 +26722,7 @@
       <c r="T357" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U357" s="2" t="n">
-        <v>16</v>
-      </c>
+      <c r="U357" s="2" t="inlineStr"/>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="2" t="n">
         <v>139.9</v>
@@ -27579,9 +26795,7 @@
       <c r="T358" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U358" s="2" t="n">
-        <v>17.6</v>
-      </c>
+      <c r="U358" s="2" t="inlineStr"/>
       <c r="V358" t="inlineStr"/>
       <c r="W358" s="2" t="n">
         <v>139.4</v>
@@ -27654,9 +26868,7 @@
       <c r="T359" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U359" s="2" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U359" s="2" t="inlineStr"/>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="2" t="n">
         <v>144.5</v>
@@ -27729,9 +26941,7 @@
       <c r="T360" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U360" s="2" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U360" s="2" t="inlineStr"/>
       <c r="V360" t="inlineStr"/>
       <c r="W360" s="2" t="n">
         <v>149.6</v>
@@ -27804,9 +27014,7 @@
       <c r="T361" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U361" s="2" t="n">
-        <v>13</v>
-      </c>
+      <c r="U361" s="2" t="inlineStr"/>
       <c r="V361" t="inlineStr"/>
       <c r="W361" s="2" t="n">
         <v>154.8</v>
@@ -27883,9 +27091,7 @@
       <c r="T362" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U362" s="2" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U362" s="2" t="inlineStr"/>
       <c r="V362" t="inlineStr"/>
       <c r="W362" s="2" t="n">
         <v>150</v>
@@ -27958,9 +27164,7 @@
       <c r="T363" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U363" s="2" t="n">
-        <v>8.699999999999999</v>
-      </c>
+      <c r="U363" s="2" t="inlineStr"/>
       <c r="V363" t="inlineStr"/>
       <c r="W363" s="2" t="n">
         <v>145.4</v>
@@ -28037,9 +27241,7 @@
       <c r="T364" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U364" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U364" s="2" t="inlineStr"/>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="2" t="n">
         <v>145.7</v>
@@ -28112,9 +27314,7 @@
       <c r="T365" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U365" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U365" s="2" t="inlineStr"/>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="2" t="n">
         <v>149.8</v>
@@ -28187,9 +27387,7 @@
       <c r="T366" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U366" s="2" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U366" s="2" t="inlineStr"/>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="2" t="n">
         <v>144.7</v>
@@ -28262,9 +27460,7 @@
       <c r="T367" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U367" s="2" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U367" s="2" t="inlineStr"/>
       <c r="V367" t="inlineStr"/>
       <c r="W367" s="2" t="n">
         <v>144.3</v>
@@ -28341,9 +27537,7 @@
       <c r="T368" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U368" s="2" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U368" s="2" t="inlineStr"/>
       <c r="V368" t="inlineStr"/>
       <c r="W368" s="2" t="n">
         <v>145.7</v>
@@ -28416,9 +27610,7 @@
       <c r="T369" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U369" s="2" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U369" s="2" t="inlineStr"/>
       <c r="V369" t="inlineStr"/>
       <c r="W369" s="2" t="n">
         <v>145.1</v>
@@ -28491,9 +27683,7 @@
       <c r="T370" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U370" s="2" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U370" s="2" t="inlineStr"/>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="2" t="n">
         <v>148.5</v>
@@ -28570,9 +27760,7 @@
       <c r="T371" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U371" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U371" s="2" t="inlineStr"/>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="2" t="n">
         <v>145.7</v>
@@ -28645,9 +27833,7 @@
       <c r="T372" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U372" s="2" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U372" s="2" t="inlineStr"/>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="2" t="n">
         <v>147.3</v>
@@ -31611,13 +30797,13 @@
         <v>26172.12</v>
       </c>
       <c r="E413" t="n">
-        <v>25949.48</v>
+        <v>25943.31</v>
       </c>
       <c r="F413" t="n">
-        <v>25981.08</v>
+        <v>25981.57</v>
       </c>
       <c r="G413" t="n">
-        <v>4474114000</v>
+        <v>7070629000</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.78</v>
@@ -31626,16 +30812,16 @@
         <v>2.6</v>
       </c>
       <c r="J413" t="n">
-        <v>26255.52</v>
+        <v>26255.55</v>
       </c>
       <c r="K413" t="n">
-        <v>26007.82</v>
+        <v>26007.83</v>
       </c>
       <c r="L413" t="n">
-        <v>25459.38</v>
+        <v>25459.39</v>
       </c>
       <c r="M413" t="n">
-        <v>24507.88</v>
+        <v>24507.89</v>
       </c>
       <c r="N413" s="2" t="n">
         <v>46.55</v>
@@ -31659,16 +30845,18 @@
         </is>
       </c>
       <c r="S413" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>14.8</v>
+        <v>17.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -30730,7 +30730,7 @@
         <v>25981.57</v>
       </c>
       <c r="G412" t="n">
-        <v>7070629000</v>
+        <v>7934200000</v>
       </c>
       <c r="H412" s="6" t="n">
         <v>-0.78</v>
@@ -30754,7 +30754,7 @@
         <v>46.55</v>
       </c>
       <c r="O412" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -30777,13 +30777,84 @@
       <c r="T412" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U412" s="5" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U412" s="5" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="5" t="n">
         <v>146.6</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>26108.46</v>
+      </c>
+      <c r="D413" t="n">
+        <v>26225.09</v>
+      </c>
+      <c r="E413" t="n">
+        <v>26076.46</v>
+      </c>
+      <c r="F413" t="n">
+        <v>26160.4</v>
+      </c>
+      <c r="G413" t="n">
+        <v>4241867000</v>
+      </c>
+      <c r="H413" s="4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J413" t="n">
+        <v>26249.08</v>
+      </c>
+      <c r="K413" t="n">
+        <v>26007.73</v>
+      </c>
+      <c r="L413" t="n">
+        <v>25494.64</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24522.62</v>
+      </c>
+      <c r="N413" s="5" t="n">
+        <v>50.58</v>
+      </c>
+      <c r="O413" t="n">
+        <v>29</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="T413" s="5" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="U413" s="5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -30801,37 +30801,37 @@
         <v>26225.09</v>
       </c>
       <c r="E413" t="n">
-        <v>26076.46</v>
+        <v>25802.96</v>
       </c>
       <c r="F413" t="n">
-        <v>26160.4</v>
+        <v>25965.34</v>
       </c>
       <c r="G413" t="n">
-        <v>4241867000</v>
-      </c>
-      <c r="H413" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>7690981000</v>
+      </c>
+      <c r="H413" s="6" t="n">
+        <v>-0.06</v>
       </c>
       <c r="I413" t="n">
         <v>2.6</v>
       </c>
       <c r="J413" t="n">
-        <v>26249.08</v>
+        <v>26239.33</v>
       </c>
       <c r="K413" t="n">
-        <v>26007.73</v>
+        <v>26004.48</v>
       </c>
       <c r="L413" t="n">
-        <v>25494.64</v>
+        <v>25493.02</v>
       </c>
       <c r="M413" t="n">
-        <v>24522.62</v>
+        <v>24521.64</v>
       </c>
       <c r="N413" s="5" t="n">
-        <v>50.58</v>
+        <v>46.65</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -30845,13 +30845,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.96</v>
+        <v>5.01</v>
       </c>
       <c r="T413" s="5" t="n">
-        <v>16.8</v>
+        <v>18.1</v>
       </c>
       <c r="U413" s="5" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="5" t="inlineStr"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -1941,7 +1941,7 @@
         <v>2.6</v>
       </c>
       <c r="J20" t="n">
-        <v>19729.47</v>
+        <v>19729.46</v>
       </c>
       <c r="K20" t="n">
         <v>19630.93</v>
@@ -4625,7 +4625,7 @@
         <v>2.6</v>
       </c>
       <c r="J56" t="n">
-        <v>17132.25</v>
+        <v>17132.26</v>
       </c>
       <c r="K56" t="n">
         <v>18472.28</v>
@@ -30804,31 +30804,31 @@
         <v>25802.96</v>
       </c>
       <c r="F413" t="n">
-        <v>25965.34</v>
+        <v>25978.42</v>
       </c>
       <c r="G413" t="n">
-        <v>7690981000</v>
+        <v>9181844000</v>
       </c>
       <c r="H413" s="6" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="I413" t="n">
         <v>2.6</v>
       </c>
       <c r="J413" t="n">
-        <v>26239.33</v>
+        <v>26239.98</v>
       </c>
       <c r="K413" t="n">
-        <v>26004.48</v>
+        <v>26004.7</v>
       </c>
       <c r="L413" t="n">
-        <v>25493.02</v>
+        <v>25493.13</v>
       </c>
       <c r="M413" t="n">
-        <v>24521.64</v>
+        <v>24521.71</v>
       </c>
       <c r="N413" s="5" t="n">
-        <v>46.65</v>
+        <v>46.9</v>
       </c>
       <c r="O413" t="n">
         <v>26</v>
@@ -30848,13 +30848,15 @@
         <v>5.01</v>
       </c>
       <c r="T413" s="5" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="U413" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="5" t="inlineStr"/>
+      <c r="W413" s="5" t="n">
+        <v>145.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -30804,10 +30804,10 @@
         <v>25802.96</v>
       </c>
       <c r="F413" t="n">
-        <v>25978.42</v>
+        <v>25978.43</v>
       </c>
       <c r="G413" t="n">
-        <v>9181844000</v>
+        <v>9968640000</v>
       </c>
       <c r="H413" s="6" t="n">
         <v>-0.01</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -30831,7 +30831,7 @@
         <v>46.9</v>
       </c>
       <c r="O413" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -30850,13 +30850,84 @@
       <c r="T413" s="5" t="n">
         <v>17.7</v>
       </c>
-      <c r="U413" s="5" t="n">
-        <v>17</v>
-      </c>
+      <c r="U413" s="5" t="inlineStr"/>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="5" t="n">
         <v>145.9</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>26377.86</v>
+      </c>
+      <c r="D414" t="n">
+        <v>26419.38</v>
+      </c>
+      <c r="E414" t="n">
+        <v>26289.94</v>
+      </c>
+      <c r="F414" t="n">
+        <v>26404.58</v>
+      </c>
+      <c r="G414" t="n">
+        <v>6419398000</v>
+      </c>
+      <c r="H414" s="4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J414" t="n">
+        <v>26243.66</v>
+      </c>
+      <c r="K414" t="n">
+        <v>26018.32</v>
+      </c>
+      <c r="L414" t="n">
+        <v>25534.76</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24536.9</v>
+      </c>
+      <c r="N414" s="5" t="n">
+        <v>47.22</v>
+      </c>
+      <c r="O414" t="n">
+        <v>29</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T414" s="5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U414" s="5" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -30871,37 +30871,37 @@
         <v>26377.86</v>
       </c>
       <c r="D414" t="n">
-        <v>26419.38</v>
+        <v>26460.64</v>
       </c>
       <c r="E414" t="n">
         <v>26289.94</v>
       </c>
       <c r="F414" t="n">
-        <v>26404.58</v>
+        <v>26418.3</v>
       </c>
       <c r="G414" t="n">
-        <v>6419398000</v>
+        <v>9083079000</v>
       </c>
       <c r="H414" s="4" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="I414" t="n">
         <v>2.6</v>
       </c>
       <c r="J414" t="n">
-        <v>26243.66</v>
+        <v>26244.34</v>
       </c>
       <c r="K414" t="n">
-        <v>26018.32</v>
+        <v>26018.55</v>
       </c>
       <c r="L414" t="n">
-        <v>25534.76</v>
+        <v>25534.88</v>
       </c>
       <c r="M414" t="n">
-        <v>24536.9</v>
+        <v>24536.97</v>
       </c>
       <c r="N414" s="5" t="n">
-        <v>47.22</v>
+        <v>47.51</v>
       </c>
       <c r="O414" t="n">
         <v>29</v>
@@ -30921,13 +30921,15 @@
         <v>4.95</v>
       </c>
       <c r="T414" s="5" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="U414" s="5" t="n">
-        <v>11.7</v>
+        <v>13.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="5" t="inlineStr"/>
+      <c r="W414" s="5" t="n">
+        <v>145.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -30880,7 +30880,7 @@
         <v>26418.3</v>
       </c>
       <c r="G414" t="n">
-        <v>9083079000</v>
+        <v>9127066000</v>
       </c>
       <c r="H414" s="4" t="n">
         <v>1.69</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -30880,7 +30880,7 @@
         <v>26418.3</v>
       </c>
       <c r="G414" t="n">
-        <v>9127066000</v>
+        <v>9884890000</v>
       </c>
       <c r="H414" s="4" t="n">
         <v>1.69</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -30904,7 +30904,7 @@
         <v>47.51</v>
       </c>
       <c r="O414" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -30923,13 +30923,84 @@
       <c r="T414" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U414" s="5" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U414" s="5" t="inlineStr"/>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="5" t="n">
         <v>145.7</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>26522.09</v>
+      </c>
+      <c r="D415" t="n">
+        <v>26544.93</v>
+      </c>
+      <c r="E415" t="n">
+        <v>26398.89</v>
+      </c>
+      <c r="F415" t="n">
+        <v>26419.4</v>
+      </c>
+      <c r="G415" t="n">
+        <v>2361512000</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J415" t="n">
+        <v>26261.95</v>
+      </c>
+      <c r="K415" t="n">
+        <v>26034.26</v>
+      </c>
+      <c r="L415" t="n">
+        <v>25580.47</v>
+      </c>
+      <c r="M415" t="n">
+        <v>24552.69</v>
+      </c>
+      <c r="N415" s="5" t="n">
+        <v>50.36</v>
+      </c>
+      <c r="O415" t="n">
+        <v>29</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" s="5" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U415" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -649,7 +649,9 @@
       <c r="T2" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="U2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V2" s="1" t="inlineStr"/>
       <c r="W2" s="2" t="n">
         <v>168.6</v>
@@ -722,7 +724,9 @@
       <c r="T3" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" s="6" t="n">
         <v>163.6</v>
@@ -795,7 +799,9 @@
       <c r="T4" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="6" t="n">
         <v>157.4</v>
@@ -868,7 +874,9 @@
       <c r="T5" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U5" s="5" t="inlineStr"/>
+      <c r="U5" s="5" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="6" t="n">
         <v>156.7</v>
@@ -941,7 +949,9 @@
       <c r="T6" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="6" t="n">
         <v>158.5</v>
@@ -1018,7 +1028,9 @@
       <c r="T7" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U7" s="5" t="inlineStr"/>
+      <c r="U7" s="5" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="6" t="n">
         <v>155.4</v>
@@ -1091,7 +1103,9 @@
       <c r="T8" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U8" s="5" t="inlineStr"/>
+      <c r="U8" s="5" t="n">
+        <v>15</v>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="6" t="n">
         <v>159.4</v>
@@ -1164,7 +1178,9 @@
       <c r="T9" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U9" s="5" t="inlineStr"/>
+      <c r="U9" s="5" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="6" t="n">
         <v>162.6</v>
@@ -1237,7 +1253,9 @@
       <c r="T10" s="5" t="n">
         <v>15.5</v>
       </c>
-      <c r="U10" s="5" t="inlineStr"/>
+      <c r="U10" s="5" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="6" t="n">
         <v>163.6</v>
@@ -1314,7 +1332,9 @@
       <c r="T11" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U11" s="5" t="inlineStr"/>
+      <c r="U11" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="6" t="n">
         <v>166.5</v>
@@ -1387,7 +1407,9 @@
       <c r="T12" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U12" s="5" t="inlineStr"/>
+      <c r="U12" s="5" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="6" t="n">
         <v>166.9</v>
@@ -1460,7 +1482,9 @@
       <c r="T13" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U13" s="5" t="inlineStr"/>
+      <c r="U13" s="5" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="6" t="n">
         <v>168.8</v>
@@ -1537,7 +1561,9 @@
       <c r="T14" s="5" t="n">
         <v>15.9</v>
       </c>
-      <c r="U14" s="5" t="inlineStr"/>
+      <c r="U14" s="5" t="n">
+        <v>12.8</v>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="6" t="n">
         <v>166.1</v>
@@ -1610,7 +1636,9 @@
       <c r="T15" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U15" s="5" t="inlineStr"/>
+      <c r="U15" s="5" t="n">
+        <v>11</v>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="6" t="n">
         <v>163.4</v>
@@ -1683,7 +1711,9 @@
       <c r="T16" s="5" t="n">
         <v>14.8</v>
       </c>
-      <c r="U16" s="5" t="inlineStr"/>
+      <c r="U16" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="6" t="n">
         <v>168</v>
@@ -1756,7 +1786,9 @@
       <c r="T17" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U17" s="5" t="inlineStr"/>
+      <c r="U17" s="5" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="6" t="n">
         <v>183.1</v>
@@ -1829,7 +1861,9 @@
       <c r="T18" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="U18" s="5" t="inlineStr"/>
+      <c r="U18" s="5" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="6" t="n">
         <v>175.8</v>
@@ -1902,7 +1936,9 @@
       <c r="T19" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U19" s="5" t="inlineStr"/>
+      <c r="U19" s="5" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="6" t="n">
         <v>178.6</v>
@@ -1979,7 +2015,9 @@
       <c r="T20" s="5" t="n">
         <v>18.2</v>
       </c>
-      <c r="U20" s="5" t="inlineStr"/>
+      <c r="U20" s="5" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="6" t="n">
         <v>165</v>
@@ -2052,7 +2090,9 @@
       <c r="T21" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="U21" s="5" t="inlineStr"/>
+      <c r="U21" s="5" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="6" t="n">
         <v>156.9</v>
@@ -2125,7 +2165,9 @@
       <c r="T22" s="5" t="n">
         <v>19.4</v>
       </c>
-      <c r="U22" s="5" t="inlineStr"/>
+      <c r="U22" s="5" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="6" t="n">
         <v>157.6</v>
@@ -2198,7 +2240,9 @@
       <c r="T23" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="U23" s="5" t="inlineStr"/>
+      <c r="U23" s="5" t="n">
+        <v>20.5</v>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="5" t="n">
         <v>153.4</v>
@@ -2275,7 +2319,9 @@
       <c r="T24" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="U24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V24" s="1" t="inlineStr"/>
       <c r="W24" s="3" t="n">
         <v>149.3</v>
@@ -2348,7 +2394,9 @@
       <c r="T25" s="5" t="n">
         <v>19.6</v>
       </c>
-      <c r="U25" s="5" t="inlineStr"/>
+      <c r="U25" s="5" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" s="6" t="n">
         <v>157.9</v>
@@ -2425,7 +2473,9 @@
       <c r="T26" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="U26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V26" s="1" t="inlineStr"/>
       <c r="W26" s="3" t="n">
         <v>154.3</v>
@@ -2502,7 +2552,9 @@
       <c r="T27" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="U27" s="5" t="inlineStr"/>
+      <c r="U27" s="5" t="n">
+        <v>24.6</v>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="5" t="n">
         <v>151.4</v>
@@ -2575,7 +2627,9 @@
       <c r="T28" s="5" t="n">
         <v>21.9</v>
       </c>
-      <c r="U28" s="5" t="inlineStr"/>
+      <c r="U28" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="5" t="n">
         <v>138.9</v>
@@ -2652,7 +2706,9 @@
       <c r="T29" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="U29" s="3" t="inlineStr"/>
+      <c r="U29" s="7" t="n">
+        <v>31.1</v>
+      </c>
       <c r="V29" s="1" t="inlineStr"/>
       <c r="W29" s="3" t="n">
         <v>137.6</v>
@@ -2729,7 +2785,9 @@
       <c r="T30" s="5" t="n">
         <v>23.4</v>
       </c>
-      <c r="U30" s="5" t="inlineStr"/>
+      <c r="U30" s="5" t="n">
+        <v>24.7</v>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" s="5" t="n">
         <v>139.9</v>
@@ -2806,8 +2864,14 @@
       <c r="T31" s="7" t="n">
         <v>27.9</v>
       </c>
-      <c r="U31" s="3" t="inlineStr"/>
-      <c r="V31" s="1" t="inlineStr"/>
+      <c r="U31" s="7" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="V31" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W31" s="3" t="n">
         <v>146</v>
       </c>
@@ -2883,8 +2947,14 @@
       <c r="T32" s="4" t="n">
         <v>26.9</v>
       </c>
-      <c r="U32" s="5" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" s="4" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W32" s="5" t="n">
         <v>132.8</v>
       </c>
@@ -2960,7 +3030,9 @@
       <c r="T33" s="5" t="n">
         <v>24.2</v>
       </c>
-      <c r="U33" s="5" t="inlineStr"/>
+      <c r="U33" s="5" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" s="5" t="n">
         <v>128.7</v>
@@ -3037,7 +3109,9 @@
       <c r="T34" s="5" t="n">
         <v>24.7</v>
       </c>
-      <c r="U34" s="5" t="inlineStr"/>
+      <c r="U34" s="5" t="n">
+        <v>23.4</v>
+      </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="5" t="n">
         <v>128.9</v>
@@ -3110,7 +3184,9 @@
       <c r="T35" s="5" t="n">
         <v>21.8</v>
       </c>
-      <c r="U35" s="5" t="inlineStr"/>
+      <c r="U35" s="5" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="5" t="n">
         <v>130.3</v>
@@ -3183,7 +3259,9 @@
       <c r="T36" s="5" t="n">
         <v>20.5</v>
       </c>
-      <c r="U36" s="5" t="inlineStr"/>
+      <c r="U36" s="5" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="5" t="n">
         <v>133.9</v>
@@ -3256,7 +3334,9 @@
       <c r="T37" s="5" t="n">
         <v>21.7</v>
       </c>
-      <c r="U37" s="5" t="inlineStr"/>
+      <c r="U37" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="5" t="n">
         <v>136.8</v>
@@ -3329,7 +3409,9 @@
       <c r="T38" s="5" t="n">
         <v>19.9</v>
       </c>
-      <c r="U38" s="5" t="inlineStr"/>
+      <c r="U38" s="5" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="5" t="n">
         <v>136.4</v>
@@ -3402,7 +3484,9 @@
       <c r="T39" s="5" t="n">
         <v>19.8</v>
       </c>
-      <c r="U39" s="5" t="inlineStr"/>
+      <c r="U39" s="5" t="n">
+        <v>18.6</v>
+      </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="5" t="n">
         <v>140.8</v>
@@ -3475,7 +3559,9 @@
       <c r="T40" s="5" t="n">
         <v>19.3</v>
       </c>
-      <c r="U40" s="5" t="inlineStr"/>
+      <c r="U40" s="5" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="5" t="n">
         <v>141.7</v>
@@ -3548,7 +3634,9 @@
       <c r="T41" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="U41" s="5" t="inlineStr"/>
+      <c r="U41" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="5" t="n">
         <v>144</v>
@@ -3621,7 +3709,9 @@
       <c r="T42" s="5" t="n">
         <v>17.1</v>
       </c>
-      <c r="U42" s="5" t="inlineStr"/>
+      <c r="U42" s="5" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="5" t="n">
         <v>148.7</v>
@@ -3698,7 +3788,9 @@
       <c r="T43" s="5" t="n">
         <v>18.3</v>
       </c>
-      <c r="U43" s="5" t="inlineStr"/>
+      <c r="U43" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="5" t="n">
         <v>144.8</v>
@@ -3771,7 +3863,9 @@
       <c r="T44" s="5" t="n">
         <v>18.7</v>
       </c>
-      <c r="U44" s="5" t="inlineStr"/>
+      <c r="U44" s="5" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="5" t="n">
         <v>140.9</v>
@@ -3844,7 +3938,9 @@
       <c r="T45" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="U45" s="3" t="inlineStr"/>
+      <c r="U45" s="7" t="n">
+        <v>25.4</v>
+      </c>
       <c r="V45" s="1" t="inlineStr"/>
       <c r="W45" s="3" t="n">
         <v>139</v>
@@ -3917,7 +4013,9 @@
       <c r="T46" s="5" t="n">
         <v>22.3</v>
       </c>
-      <c r="U46" s="5" t="inlineStr"/>
+      <c r="U46" s="5" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" s="5" t="n">
         <v>148.6</v>
@@ -3990,7 +4088,9 @@
       <c r="T47" s="5" t="n">
         <v>21.8</v>
       </c>
-      <c r="U47" s="5" t="inlineStr"/>
+      <c r="U47" s="5" t="n">
+        <v>20.1</v>
+      </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="5" t="n">
         <v>143</v>
@@ -4063,7 +4163,9 @@
       <c r="T48" s="5" t="n">
         <v>21.5</v>
       </c>
-      <c r="U48" s="5" t="inlineStr"/>
+      <c r="U48" s="4" t="n">
+        <v>26.7</v>
+      </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="5" t="n">
         <v>144.3</v>
@@ -4136,8 +4238,14 @@
       <c r="T49" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="U49" s="3" t="inlineStr"/>
-      <c r="V49" s="1" t="inlineStr"/>
+      <c r="U49" s="7" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="V49" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W49" s="3" t="n">
         <v>139.2</v>
       </c>
@@ -4213,8 +4321,14 @@
       <c r="T50" s="7" t="n">
         <v>45.3</v>
       </c>
-      <c r="U50" s="3" t="inlineStr"/>
-      <c r="V50" s="1" t="inlineStr"/>
+      <c r="U50" s="7" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="V50" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W50" s="3" t="n">
         <v>136.5</v>
       </c>
@@ -4290,8 +4404,14 @@
       <c r="T51" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="U51" s="5" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="U51" s="4" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="V51" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W51" s="5" t="n">
         <v>133.8</v>
       </c>
@@ -4367,8 +4487,14 @@
       <c r="T52" s="4" t="n">
         <v>52.3</v>
       </c>
-      <c r="U52" s="5" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="U52" s="4" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="V52" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W52" s="5" t="n">
         <v>135.7</v>
       </c>
@@ -4440,8 +4566,14 @@
       <c r="T53" s="4" t="n">
         <v>33.6</v>
       </c>
-      <c r="U53" s="5" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="U53" s="4" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="V53" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W53" s="5" t="n">
         <v>142.2</v>
       </c>
@@ -4513,8 +4645,14 @@
       <c r="T54" s="7" t="n">
         <v>40.7</v>
       </c>
-      <c r="U54" s="3" t="inlineStr"/>
-      <c r="V54" s="1" t="inlineStr"/>
+      <c r="U54" s="7" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="V54" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W54" s="3" t="n">
         <v>127.5</v>
       </c>
@@ -4586,8 +4724,14 @@
       <c r="T55" s="4" t="n">
         <v>37.6</v>
       </c>
-      <c r="U55" s="5" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="U55" s="4" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="V55" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W55" s="5" t="n">
         <v>128.6</v>
       </c>
@@ -4659,7 +4803,9 @@
       <c r="T56" s="4" t="n">
         <v>30.9</v>
       </c>
-      <c r="U56" s="5" t="inlineStr"/>
+      <c r="U56" s="4" t="n">
+        <v>28.5</v>
+      </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" s="5" t="n">
         <v>135.7</v>
@@ -4732,7 +4878,9 @@
       <c r="T57" s="4" t="n">
         <v>30.1</v>
       </c>
-      <c r="U57" s="5" t="inlineStr"/>
+      <c r="U57" s="4" t="n">
+        <v>26</v>
+      </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="5" t="n">
         <v>135.8</v>
@@ -4805,8 +4953,14 @@
       <c r="T58" s="7" t="n">
         <v>32.6</v>
       </c>
-      <c r="U58" s="3" t="inlineStr"/>
-      <c r="V58" s="1" t="inlineStr"/>
+      <c r="U58" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="V58" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W58" s="3" t="n">
         <v>131.3</v>
       </c>
@@ -4878,8 +5032,14 @@
       <c r="T59" s="4" t="n">
         <v>29.6</v>
       </c>
-      <c r="U59" s="5" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
+      <c r="U59" s="4" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="V59" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W59" s="5" t="n">
         <v>130</v>
       </c>
@@ -4951,7 +5111,9 @@
       <c r="T60" s="4" t="n">
         <v>33.8</v>
       </c>
-      <c r="U60" s="5" t="inlineStr"/>
+      <c r="U60" s="4" t="n">
+        <v>30.6</v>
+      </c>
       <c r="V60" t="inlineStr"/>
       <c r="W60" s="4" t="n">
         <v>125.8</v>
@@ -5024,7 +5186,9 @@
       <c r="T61" s="4" t="n">
         <v>30.6</v>
       </c>
-      <c r="U61" s="5" t="inlineStr"/>
+      <c r="U61" s="4" t="n">
+        <v>29.1</v>
+      </c>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="4" t="n">
         <v>125.9</v>
@@ -5097,8 +5261,14 @@
       <c r="T62" s="4" t="n">
         <v>28.5</v>
       </c>
-      <c r="U62" s="5" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
+      <c r="U62" s="4" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="V62" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W62" s="4" t="n">
         <v>126.7</v>
       </c>
@@ -5170,7 +5340,9 @@
       <c r="T63" s="4" t="n">
         <v>26.5</v>
       </c>
-      <c r="U63" s="5" t="inlineStr"/>
+      <c r="U63" s="4" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V63" t="inlineStr"/>
       <c r="W63" s="5" t="n">
         <v>129</v>
@@ -5243,7 +5415,9 @@
       <c r="T64" s="5" t="n">
         <v>24.8</v>
       </c>
-      <c r="U64" s="5" t="inlineStr"/>
+      <c r="U64" s="5" t="n">
+        <v>23.6</v>
+      </c>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="5" t="n">
         <v>132.4</v>
@@ -5316,7 +5490,9 @@
       <c r="T65" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="U65" s="5" t="inlineStr"/>
+      <c r="U65" s="5" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="5" t="n">
         <v>131.3</v>
@@ -5389,7 +5565,9 @@
       <c r="T66" s="5" t="n">
         <v>24.2</v>
       </c>
-      <c r="U66" s="5" t="inlineStr"/>
+      <c r="U66" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="5" t="n">
         <v>134.3</v>
@@ -5462,7 +5640,9 @@
       <c r="T67" s="5" t="n">
         <v>24.7</v>
       </c>
-      <c r="U67" s="5" t="inlineStr"/>
+      <c r="U67" s="5" t="n">
+        <v>22.9</v>
+      </c>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="5" t="n">
         <v>132.7</v>
@@ -5535,7 +5715,9 @@
       <c r="T68" s="5" t="n">
         <v>24.6</v>
       </c>
-      <c r="U68" s="5" t="inlineStr"/>
+      <c r="U68" s="4" t="n">
+        <v>27.5</v>
+      </c>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="5" t="n">
         <v>134.1</v>
@@ -5608,7 +5790,9 @@
       <c r="T69" s="5" t="n">
         <v>22.7</v>
       </c>
-      <c r="U69" s="5" t="inlineStr"/>
+      <c r="U69" s="5" t="n">
+        <v>20</v>
+      </c>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="5" t="n">
         <v>134.8</v>
@@ -5685,7 +5869,9 @@
       <c r="T70" s="5" t="n">
         <v>23.6</v>
       </c>
-      <c r="U70" s="5" t="inlineStr"/>
+      <c r="U70" s="5" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="5" t="n">
         <v>134.1</v>
@@ -5758,7 +5944,9 @@
       <c r="T71" s="5" t="n">
         <v>24.8</v>
       </c>
-      <c r="U71" s="5" t="inlineStr"/>
+      <c r="U71" s="5" t="n">
+        <v>22.2</v>
+      </c>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="5" t="n">
         <v>133.2</v>
@@ -5831,7 +6019,9 @@
       <c r="T72" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="U72" s="5" t="inlineStr"/>
+      <c r="U72" s="5" t="n">
+        <v>19.8</v>
+      </c>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="5" t="n">
         <v>132.2</v>
@@ -5904,7 +6094,9 @@
       <c r="T73" s="5" t="n">
         <v>22.5</v>
       </c>
-      <c r="U73" s="5" t="inlineStr"/>
+      <c r="U73" s="5" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="5" t="n">
         <v>131.5</v>
@@ -5977,7 +6169,9 @@
       <c r="T74" s="5" t="n">
         <v>21.9</v>
       </c>
-      <c r="U74" s="5" t="inlineStr"/>
+      <c r="U74" s="4" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="5" t="n">
         <v>128.4</v>
@@ -6050,7 +6244,9 @@
       <c r="T75" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U75" s="5" t="inlineStr"/>
+      <c r="U75" s="5" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="5" t="n">
         <v>137.7</v>
@@ -6123,7 +6319,9 @@
       <c r="T76" s="5" t="n">
         <v>18.2</v>
       </c>
-      <c r="U76" s="5" t="inlineStr"/>
+      <c r="U76" s="5" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="5" t="n">
         <v>140.5</v>
@@ -6196,7 +6394,9 @@
       <c r="T77" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U77" s="5" t="inlineStr"/>
+      <c r="U77" s="5" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="5" t="n">
         <v>138.9</v>
@@ -6269,7 +6469,9 @@
       <c r="T78" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U78" s="5" t="inlineStr"/>
+      <c r="U78" s="5" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="5" t="n">
         <v>140.9</v>
@@ -6342,7 +6544,9 @@
       <c r="T79" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U79" s="5" t="inlineStr"/>
+      <c r="U79" s="5" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="5" t="n">
         <v>136</v>
@@ -6415,7 +6619,9 @@
       <c r="T80" s="5" t="n">
         <v>18.1</v>
       </c>
-      <c r="U80" s="5" t="inlineStr"/>
+      <c r="U80" s="5" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="5" t="n">
         <v>135.9</v>
@@ -6488,7 +6694,9 @@
       <c r="T81" s="5" t="n">
         <v>18.1</v>
       </c>
-      <c r="U81" s="5" t="inlineStr"/>
+      <c r="U81" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="5" t="n">
         <v>137.3</v>
@@ -6561,7 +6769,9 @@
       <c r="T82" s="5" t="n">
         <v>20.9</v>
       </c>
-      <c r="U82" s="5" t="inlineStr"/>
+      <c r="U82" s="5" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="5" t="n">
         <v>137.3</v>
@@ -6634,7 +6844,9 @@
       <c r="T83" s="5" t="n">
         <v>20.3</v>
       </c>
-      <c r="U83" s="5" t="inlineStr"/>
+      <c r="U83" s="5" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="5" t="n">
         <v>139</v>
@@ -6707,7 +6919,9 @@
       <c r="T84" s="5" t="n">
         <v>22.3</v>
       </c>
-      <c r="U84" s="5" t="inlineStr"/>
+      <c r="U84" s="5" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="5" t="n">
         <v>139.3</v>
@@ -6780,7 +6994,9 @@
       <c r="T85" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="U85" s="5" t="inlineStr"/>
+      <c r="U85" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="5" t="n">
         <v>140.9</v>
@@ -6853,7 +7069,9 @@
       <c r="T86" s="5" t="n">
         <v>19.3</v>
       </c>
-      <c r="U86" s="5" t="inlineStr"/>
+      <c r="U86" s="5" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="5" t="n">
         <v>137.6</v>
@@ -6926,7 +7144,9 @@
       <c r="T87" s="5" t="n">
         <v>19.2</v>
       </c>
-      <c r="U87" s="5" t="inlineStr"/>
+      <c r="U87" s="5" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="5" t="n">
         <v>137.3</v>
@@ -6999,7 +7219,9 @@
       <c r="T88" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U88" s="5" t="inlineStr"/>
+      <c r="U88" s="5" t="n">
+        <v>17</v>
+      </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="5" t="n">
         <v>138.2</v>
@@ -7072,7 +7294,9 @@
       <c r="T89" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U89" s="5" t="inlineStr"/>
+      <c r="U89" s="5" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="5" t="n">
         <v>141</v>
@@ -7145,7 +7369,9 @@
       <c r="T90" s="5" t="n">
         <v>17.7</v>
       </c>
-      <c r="U90" s="5" t="inlineStr"/>
+      <c r="U90" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" s="5" t="n">
         <v>141.6</v>
@@ -7218,7 +7444,9 @@
       <c r="T91" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="U91" s="5" t="inlineStr"/>
+      <c r="U91" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="5" t="n">
         <v>137.5</v>
@@ -7291,7 +7519,9 @@
       <c r="T92" s="5" t="n">
         <v>18.5</v>
       </c>
-      <c r="U92" s="5" t="inlineStr"/>
+      <c r="U92" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="5" t="n">
         <v>140.1</v>
@@ -7364,7 +7594,9 @@
       <c r="T93" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U93" s="5" t="inlineStr"/>
+      <c r="U93" s="5" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="5" t="n">
         <v>138.9</v>
@@ -7437,7 +7669,9 @@
       <c r="T94" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U94" s="5" t="inlineStr"/>
+      <c r="U94" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="5" t="n">
         <v>139.2</v>
@@ -7510,7 +7744,9 @@
       <c r="T95" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="U95" s="5" t="inlineStr"/>
+      <c r="U95" s="5" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="5" t="n">
         <v>141.2</v>
@@ -7583,7 +7819,9 @@
       <c r="T96" s="5" t="n">
         <v>17.3</v>
       </c>
-      <c r="U96" s="5" t="inlineStr"/>
+      <c r="U96" s="5" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="5" t="n">
         <v>141.4</v>
@@ -7656,7 +7894,9 @@
       <c r="T97" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="U97" s="5" t="inlineStr"/>
+      <c r="U97" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="5" t="n">
         <v>145.6</v>
@@ -7729,7 +7969,9 @@
       <c r="T98" s="5" t="n">
         <v>20.8</v>
       </c>
-      <c r="U98" s="5" t="inlineStr"/>
+      <c r="U98" s="5" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="5" t="n">
         <v>149.6</v>
@@ -7802,7 +8044,9 @@
       <c r="T99" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="U99" s="5" t="inlineStr"/>
+      <c r="U99" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V99" t="inlineStr"/>
       <c r="W99" s="6" t="n">
         <v>156.6</v>
@@ -7875,7 +8119,9 @@
       <c r="T100" s="5" t="n">
         <v>21.6</v>
       </c>
-      <c r="U100" s="5" t="inlineStr"/>
+      <c r="U100" s="5" t="n">
+        <v>21</v>
+      </c>
       <c r="V100" t="inlineStr"/>
       <c r="W100" s="5" t="n">
         <v>154.4</v>
@@ -7948,7 +8194,9 @@
       <c r="T101" s="5" t="n">
         <v>20.1</v>
       </c>
-      <c r="U101" s="5" t="inlineStr"/>
+      <c r="U101" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="5" t="n">
         <v>148.4</v>
@@ -8021,7 +8269,9 @@
       <c r="T102" s="5" t="n">
         <v>20.6</v>
       </c>
-      <c r="U102" s="5" t="inlineStr"/>
+      <c r="U102" s="5" t="n">
+        <v>18.4</v>
+      </c>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="5" t="n">
         <v>149.2</v>
@@ -8094,7 +8344,9 @@
       <c r="T103" s="5" t="n">
         <v>19.8</v>
       </c>
-      <c r="U103" s="5" t="inlineStr"/>
+      <c r="U103" s="5" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="5" t="n">
         <v>154.8</v>
@@ -8167,7 +8419,9 @@
       <c r="T104" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="U104" s="5" t="inlineStr"/>
+      <c r="U104" s="5" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="6" t="n">
         <v>155</v>
@@ -8240,7 +8494,9 @@
       <c r="T105" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U105" s="5" t="inlineStr"/>
+      <c r="U105" s="5" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="5" t="n">
         <v>152.2</v>
@@ -8313,7 +8569,9 @@
       <c r="T106" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U106" s="5" t="inlineStr"/>
+      <c r="U106" s="5" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="5" t="n">
         <v>147.5</v>
@@ -8386,7 +8644,9 @@
       <c r="T107" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U107" s="5" t="inlineStr"/>
+      <c r="U107" s="5" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="5" t="n">
         <v>143.4</v>
@@ -8459,7 +8719,9 @@
       <c r="T108" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U108" s="5" t="inlineStr"/>
+      <c r="U108" s="5" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="5" t="n">
         <v>139.6</v>
@@ -8532,7 +8794,9 @@
       <c r="T109" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U109" s="5" t="inlineStr"/>
+      <c r="U109" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="5" t="n">
         <v>140.1</v>
@@ -8605,7 +8869,9 @@
       <c r="T110" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U110" s="5" t="inlineStr"/>
+      <c r="U110" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="5" t="n">
         <v>139.3</v>
@@ -8678,7 +8944,9 @@
       <c r="T111" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U111" s="5" t="inlineStr"/>
+      <c r="U111" s="5" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="5" t="n">
         <v>141.4</v>
@@ -8751,7 +9019,9 @@
       <c r="T112" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U112" s="5" t="inlineStr"/>
+      <c r="U112" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="5" t="n">
         <v>138</v>
@@ -8824,7 +9094,9 @@
       <c r="T113" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U113" s="5" t="inlineStr"/>
+      <c r="U113" s="5" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="5" t="n">
         <v>140.8</v>
@@ -8897,7 +9169,9 @@
       <c r="T114" s="5" t="n">
         <v>15.9</v>
       </c>
-      <c r="U114" s="5" t="inlineStr"/>
+      <c r="U114" s="5" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="5" t="n">
         <v>141.8</v>
@@ -8970,7 +9244,9 @@
       <c r="T115" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U115" s="5" t="inlineStr"/>
+      <c r="U115" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="5" t="n">
         <v>143.3</v>
@@ -9043,7 +9319,9 @@
       <c r="T116" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U116" s="5" t="inlineStr"/>
+      <c r="U116" s="5" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="5" t="n">
         <v>145</v>
@@ -9116,7 +9394,9 @@
       <c r="T117" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U117" s="5" t="inlineStr"/>
+      <c r="U117" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V117" t="inlineStr"/>
       <c r="W117" s="5" t="n">
         <v>147</v>
@@ -9189,7 +9469,9 @@
       <c r="T118" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U118" s="5" t="inlineStr"/>
+      <c r="U118" s="5" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V118" t="inlineStr"/>
       <c r="W118" s="5" t="n">
         <v>143.7</v>
@@ -9262,7 +9544,9 @@
       <c r="T119" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U119" s="5" t="inlineStr"/>
+      <c r="U119" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V119" t="inlineStr"/>
       <c r="W119" s="5" t="n">
         <v>146.7</v>
@@ -9335,7 +9619,9 @@
       <c r="T120" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U120" s="5" t="inlineStr"/>
+      <c r="U120" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V120" t="inlineStr"/>
       <c r="W120" s="5" t="n">
         <v>151.1</v>
@@ -9408,7 +9694,9 @@
       <c r="T121" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U121" s="5" t="inlineStr"/>
+      <c r="U121" s="5" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V121" t="inlineStr"/>
       <c r="W121" s="5" t="n">
         <v>150.4</v>
@@ -9481,7 +9769,9 @@
       <c r="T122" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U122" s="5" t="inlineStr"/>
+      <c r="U122" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V122" t="inlineStr"/>
       <c r="W122" s="5" t="n">
         <v>154.8</v>
@@ -9554,7 +9844,9 @@
       <c r="T123" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U123" s="5" t="inlineStr"/>
+      <c r="U123" s="5" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V123" t="inlineStr"/>
       <c r="W123" s="5" t="n">
         <v>153.4</v>
@@ -9627,7 +9919,9 @@
       <c r="T124" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U124" s="5" t="inlineStr"/>
+      <c r="U124" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="6" t="n">
         <v>159.3</v>
@@ -9700,7 +9994,9 @@
       <c r="T125" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U125" s="5" t="inlineStr"/>
+      <c r="U125" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="6" t="n">
         <v>159.4</v>
@@ -9773,7 +10069,9 @@
       <c r="T126" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U126" s="5" t="inlineStr"/>
+      <c r="U126" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V126" t="inlineStr"/>
       <c r="W126" s="5" t="n">
         <v>145.6</v>
@@ -9846,7 +10144,9 @@
       <c r="T127" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="U127" s="5" t="inlineStr"/>
+      <c r="U127" s="5" t="n">
+        <v>7.9</v>
+      </c>
       <c r="V127" t="inlineStr"/>
       <c r="W127" s="5" t="n">
         <v>147.6</v>
@@ -9919,7 +10219,9 @@
       <c r="T128" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U128" s="5" t="inlineStr"/>
+      <c r="U128" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="5" t="n">
         <v>149.1</v>
@@ -9992,7 +10294,9 @@
       <c r="T129" s="5" t="n">
         <v>15.5</v>
       </c>
-      <c r="U129" s="5" t="inlineStr"/>
+      <c r="U129" s="5" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="5" t="n">
         <v>154.1</v>
@@ -10065,7 +10369,9 @@
       <c r="T130" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U130" s="5" t="inlineStr"/>
+      <c r="U130" s="5" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V130" t="inlineStr"/>
       <c r="W130" s="5" t="n">
         <v>152.3</v>
@@ -10142,7 +10448,9 @@
       <c r="T131" s="5" t="n">
         <v>20.4</v>
       </c>
-      <c r="U131" s="5" t="inlineStr"/>
+      <c r="U131" s="5" t="n">
+        <v>20</v>
+      </c>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="6" t="n">
         <v>155.5</v>
@@ -10215,7 +10523,9 @@
       <c r="T132" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="U132" s="5" t="inlineStr"/>
+      <c r="U132" s="5" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="6" t="n">
         <v>159.3</v>
@@ -10288,7 +10598,9 @@
       <c r="T133" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U133" s="5" t="inlineStr"/>
+      <c r="U133" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="5" t="n">
         <v>149.9</v>
@@ -10361,7 +10673,9 @@
       <c r="T134" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U134" s="5" t="inlineStr"/>
+      <c r="U134" s="5" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="5" t="n">
         <v>149.7</v>
@@ -10434,7 +10748,9 @@
       <c r="T135" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U135" s="5" t="inlineStr"/>
+      <c r="U135" s="5" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="5" t="n">
         <v>147</v>
@@ -10507,7 +10823,9 @@
       <c r="T136" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U136" s="5" t="inlineStr"/>
+      <c r="U136" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="5" t="n">
         <v>147.5</v>
@@ -10580,7 +10898,9 @@
       <c r="T137" s="5" t="n">
         <v>16.2</v>
       </c>
-      <c r="U137" s="5" t="inlineStr"/>
+      <c r="U137" s="5" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="5" t="n">
         <v>148.6</v>
@@ -10653,7 +10973,9 @@
       <c r="T138" s="5" t="n">
         <v>14.7</v>
       </c>
-      <c r="U138" s="5" t="inlineStr"/>
+      <c r="U138" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="5" t="n">
         <v>151.4</v>
@@ -10726,7 +11048,9 @@
       <c r="T139" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="U139" s="5" t="inlineStr"/>
+      <c r="U139" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="5" t="n">
         <v>153.1</v>
@@ -10799,7 +11123,9 @@
       <c r="T140" s="5" t="n">
         <v>14.8</v>
       </c>
-      <c r="U140" s="5" t="inlineStr"/>
+      <c r="U140" s="5" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="5" t="n">
         <v>150.6</v>
@@ -10872,7 +11198,9 @@
       <c r="T141" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U141" s="5" t="inlineStr"/>
+      <c r="U141" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="5" t="n">
         <v>153.8</v>
@@ -10945,7 +11273,9 @@
       <c r="T142" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="U142" s="5" t="inlineStr"/>
+      <c r="U142" s="5" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="5" t="n">
         <v>153.9</v>
@@ -11018,7 +11348,9 @@
       <c r="T143" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="U143" s="5" t="inlineStr"/>
+      <c r="U143" s="5" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="5" t="n">
         <v>153.2</v>
@@ -11095,7 +11427,9 @@
       <c r="T144" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U144" s="5" t="inlineStr"/>
+      <c r="U144" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="5" t="n">
         <v>144.6</v>
@@ -11168,7 +11502,9 @@
       <c r="T145" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U145" s="5" t="inlineStr"/>
+      <c r="U145" s="5" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="5" t="n">
         <v>144.3</v>
@@ -11241,7 +11577,9 @@
       <c r="T146" s="5" t="n">
         <v>14.2</v>
       </c>
-      <c r="U146" s="5" t="inlineStr"/>
+      <c r="U146" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="5" t="n">
         <v>146.4</v>
@@ -11314,7 +11652,9 @@
       <c r="T147" s="5" t="n">
         <v>14.8</v>
       </c>
-      <c r="U147" s="5" t="inlineStr"/>
+      <c r="U147" s="5" t="n">
+        <v>8.1</v>
+      </c>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="5" t="n">
         <v>150</v>
@@ -11387,7 +11727,9 @@
       <c r="T148" s="5" t="n">
         <v>14.6</v>
       </c>
-      <c r="U148" s="5" t="inlineStr"/>
+      <c r="U148" s="5" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="6" t="n">
         <v>156.5</v>
@@ -11460,7 +11802,9 @@
       <c r="T149" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U149" s="5" t="inlineStr"/>
+      <c r="U149" s="5" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="5" t="n">
         <v>150.9</v>
@@ -11533,7 +11877,9 @@
       <c r="T150" s="5" t="n">
         <v>14.4</v>
       </c>
-      <c r="U150" s="5" t="inlineStr"/>
+      <c r="U150" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="5" t="n">
         <v>152.5</v>
@@ -11606,7 +11952,9 @@
       <c r="T151" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U151" s="5" t="inlineStr"/>
+      <c r="U151" s="5" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="5" t="n">
         <v>152.1</v>
@@ -11683,7 +12031,9 @@
       <c r="T152" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U152" s="5" t="inlineStr"/>
+      <c r="U152" s="5" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="5" t="n">
         <v>151.5</v>
@@ -11756,7 +12106,9 @@
       <c r="T153" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U153" s="5" t="inlineStr"/>
+      <c r="U153" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="5" t="n">
         <v>150.2</v>
@@ -11829,7 +12181,9 @@
       <c r="T154" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="U154" s="5" t="inlineStr"/>
+      <c r="U154" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="5" t="n">
         <v>154</v>
@@ -11902,7 +12256,9 @@
       <c r="T155" s="5" t="n">
         <v>15.2</v>
       </c>
-      <c r="U155" s="5" t="inlineStr"/>
+      <c r="U155" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="5" t="n">
         <v>148.2</v>
@@ -11975,7 +12331,9 @@
       <c r="T156" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U156" s="5" t="inlineStr"/>
+      <c r="U156" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="5" t="n">
         <v>148.8</v>
@@ -12048,7 +12406,9 @@
       <c r="T157" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="U157" s="5" t="inlineStr"/>
+      <c r="U157" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="5" t="n">
         <v>150.9</v>
@@ -12121,7 +12481,9 @@
       <c r="T158" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U158" s="5" t="inlineStr"/>
+      <c r="U158" s="5" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="5" t="n">
         <v>151.9</v>
@@ -12194,7 +12556,9 @@
       <c r="T159" s="5" t="n">
         <v>14.7</v>
       </c>
-      <c r="U159" s="5" t="inlineStr"/>
+      <c r="U159" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="5" t="n">
         <v>147.6</v>
@@ -12267,7 +12631,9 @@
       <c r="T160" s="5" t="n">
         <v>14.8</v>
       </c>
-      <c r="U160" s="5" t="inlineStr"/>
+      <c r="U160" s="5" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="5" t="n">
         <v>149.5</v>
@@ -12340,7 +12706,9 @@
       <c r="T161" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U161" s="5" t="inlineStr"/>
+      <c r="U161" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="5" t="n">
         <v>152.1</v>
@@ -12413,7 +12781,9 @@
       <c r="T162" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U162" s="5" t="inlineStr"/>
+      <c r="U162" s="5" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="5" t="n">
         <v>148.2</v>
@@ -12486,7 +12856,9 @@
       <c r="T163" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U163" s="5" t="inlineStr"/>
+      <c r="U163" s="5" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="5" t="n">
         <v>146.4</v>
@@ -12559,7 +12931,9 @@
       <c r="T164" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U164" s="5" t="inlineStr"/>
+      <c r="U164" s="5" t="n">
+        <v>14.4</v>
+      </c>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="5" t="n">
         <v>148.2</v>
@@ -12632,7 +13006,9 @@
       <c r="T165" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U165" s="5" t="inlineStr"/>
+      <c r="U165" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="5" t="n">
         <v>147</v>
@@ -12705,7 +13081,9 @@
       <c r="T166" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U166" s="5" t="inlineStr"/>
+      <c r="U166" s="5" t="n">
+        <v>9.1</v>
+      </c>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="5" t="n">
         <v>145.5</v>
@@ -12778,7 +13156,9 @@
       <c r="T167" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U167" s="5" t="inlineStr"/>
+      <c r="U167" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="5" t="n">
         <v>146.5</v>
@@ -12851,7 +13231,9 @@
       <c r="T168" s="5" t="n">
         <v>16.2</v>
       </c>
-      <c r="U168" s="5" t="inlineStr"/>
+      <c r="U168" s="5" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="5" t="n">
         <v>145.9</v>
@@ -12924,7 +13306,9 @@
       <c r="T169" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U169" s="5" t="inlineStr"/>
+      <c r="U169" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="5" t="n">
         <v>145.9</v>
@@ -12997,7 +13381,9 @@
       <c r="T170" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="U170" s="5" t="inlineStr"/>
+      <c r="U170" s="5" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="5" t="n">
         <v>141.5</v>
@@ -13070,7 +13456,9 @@
       <c r="T171" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U171" s="5" t="inlineStr"/>
+      <c r="U171" s="5" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="5" t="n">
         <v>143</v>
@@ -13143,7 +13531,9 @@
       <c r="T172" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U172" s="5" t="inlineStr"/>
+      <c r="U172" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="5" t="n">
         <v>143.4</v>
@@ -13216,7 +13606,9 @@
       <c r="T173" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U173" s="5" t="inlineStr"/>
+      <c r="U173" s="5" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="5" t="n">
         <v>143.7</v>
@@ -13289,7 +13681,9 @@
       <c r="T174" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U174" s="5" t="inlineStr"/>
+      <c r="U174" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="5" t="n">
         <v>145.9</v>
@@ -13362,7 +13756,9 @@
       <c r="T175" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U175" s="5" t="inlineStr"/>
+      <c r="U175" s="5" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="5" t="n">
         <v>144.6</v>
@@ -13435,7 +13831,9 @@
       <c r="T176" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U176" s="5" t="inlineStr"/>
+      <c r="U176" s="5" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="5" t="n">
         <v>142.5</v>
@@ -13508,7 +13906,9 @@
       <c r="T177" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U177" s="5" t="inlineStr"/>
+      <c r="U177" s="5" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="5" t="n">
         <v>145.2</v>
@@ -13581,7 +13981,9 @@
       <c r="T178" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U178" s="5" t="inlineStr"/>
+      <c r="U178" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="5" t="n">
         <v>145.8</v>
@@ -13654,7 +14056,9 @@
       <c r="T179" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U179" s="5" t="inlineStr"/>
+      <c r="U179" s="5" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="5" t="n">
         <v>145.3</v>
@@ -13731,7 +14135,9 @@
       <c r="T180" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="U180" s="3" t="inlineStr"/>
+      <c r="U180" s="7" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V180" s="1" t="inlineStr"/>
       <c r="W180" s="3" t="n">
         <v>138.9</v>
@@ -13804,7 +14210,9 @@
       <c r="T181" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="U181" s="5" t="inlineStr"/>
+      <c r="U181" s="5" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V181" t="inlineStr"/>
       <c r="W181" s="5" t="n">
         <v>142.8</v>
@@ -13881,7 +14289,9 @@
       <c r="T182" s="5" t="n">
         <v>20.8</v>
       </c>
-      <c r="U182" s="5" t="inlineStr"/>
+      <c r="U182" s="5" t="n">
+        <v>17.7</v>
+      </c>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="5" t="n">
         <v>146.5</v>
@@ -13954,7 +14364,9 @@
       <c r="T183" s="5" t="n">
         <v>20.6</v>
       </c>
-      <c r="U183" s="5" t="inlineStr"/>
+      <c r="U183" s="5" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="5" t="n">
         <v>145</v>
@@ -14031,7 +14443,9 @@
       <c r="T184" s="4" t="n">
         <v>25.3</v>
       </c>
-      <c r="U184" s="5" t="inlineStr"/>
+      <c r="U184" s="5" t="n">
+        <v>23.8</v>
+      </c>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="5" t="n">
         <v>147.1</v>
@@ -14104,7 +14518,9 @@
       <c r="T185" s="5" t="n">
         <v>20.8</v>
       </c>
-      <c r="U185" s="5" t="inlineStr"/>
+      <c r="U185" s="5" t="n">
+        <v>17.9</v>
+      </c>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="5" t="n">
         <v>147.6</v>
@@ -14177,7 +14593,9 @@
       <c r="T186" s="5" t="n">
         <v>18.2</v>
       </c>
-      <c r="U186" s="5" t="inlineStr"/>
+      <c r="U186" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="5" t="n">
         <v>151.3</v>
@@ -14250,7 +14668,9 @@
       <c r="T187" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U187" s="5" t="inlineStr"/>
+      <c r="U187" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V187" t="inlineStr"/>
       <c r="W187" s="5" t="n">
         <v>149.9</v>
@@ -14323,7 +14743,9 @@
       <c r="T188" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U188" s="5" t="inlineStr"/>
+      <c r="U188" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V188" t="inlineStr"/>
       <c r="W188" s="5" t="n">
         <v>152.9</v>
@@ -14396,7 +14818,9 @@
       <c r="T189" s="5" t="n">
         <v>17.3</v>
       </c>
-      <c r="U189" s="5" t="inlineStr"/>
+      <c r="U189" s="5" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="5" t="n">
         <v>154.3</v>
@@ -14469,7 +14893,9 @@
       <c r="T190" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U190" s="5" t="inlineStr"/>
+      <c r="U190" s="5" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="5" t="n">
         <v>153.5</v>
@@ -14542,7 +14968,9 @@
       <c r="T191" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U191" s="5" t="inlineStr"/>
+      <c r="U191" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="5" t="n">
         <v>148.5</v>
@@ -14615,7 +15043,9 @@
       <c r="T192" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U192" s="5" t="inlineStr"/>
+      <c r="U192" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="5" t="n">
         <v>140.4</v>
@@ -14688,7 +15118,9 @@
       <c r="T193" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U193" s="5" t="inlineStr"/>
+      <c r="U193" s="5" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="5" t="n">
         <v>139.4</v>
@@ -14761,7 +15193,9 @@
       <c r="T194" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U194" s="5" t="inlineStr"/>
+      <c r="U194" s="5" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="5" t="n">
         <v>141.1</v>
@@ -14834,7 +15268,9 @@
       <c r="T195" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U195" s="5" t="inlineStr"/>
+      <c r="U195" s="5" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="5" t="n">
         <v>142.8</v>
@@ -14907,7 +15343,9 @@
       <c r="T196" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U196" s="5" t="inlineStr"/>
+      <c r="U196" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="5" t="n">
         <v>142</v>
@@ -14980,7 +15418,9 @@
       <c r="T197" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="U197" s="5" t="inlineStr"/>
+      <c r="U197" s="5" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="5" t="n">
         <v>144</v>
@@ -15053,7 +15493,9 @@
       <c r="T198" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="U198" s="5" t="inlineStr"/>
+      <c r="U198" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="5" t="n">
         <v>143.6</v>
@@ -15130,7 +15572,9 @@
       <c r="T199" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="U199" s="5" t="inlineStr"/>
+      <c r="U199" s="5" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="5" t="n">
         <v>143.5</v>
@@ -15203,7 +15647,9 @@
       <c r="T200" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="U200" s="5" t="inlineStr"/>
+      <c r="U200" s="5" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="5" t="n">
         <v>141.3</v>
@@ -15276,7 +15722,9 @@
       <c r="T201" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="U201" s="5" t="inlineStr"/>
+      <c r="U201" s="5" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="5" t="n">
         <v>142.9</v>
@@ -15349,7 +15797,9 @@
       <c r="T202" s="5" t="n">
         <v>17.3</v>
       </c>
-      <c r="U202" s="5" t="inlineStr"/>
+      <c r="U202" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="5" t="n">
         <v>143.4</v>
@@ -15422,7 +15872,9 @@
       <c r="T203" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="U203" s="5" t="inlineStr"/>
+      <c r="U203" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="5" t="n">
         <v>138.6</v>
@@ -15499,7 +15951,9 @@
       <c r="T204" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="U204" s="5" t="inlineStr"/>
+      <c r="U204" s="5" t="n">
+        <v>17</v>
+      </c>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="5" t="n">
         <v>142.5</v>
@@ -15572,7 +16026,9 @@
       <c r="T205" s="5" t="n">
         <v>19.8</v>
       </c>
-      <c r="U205" s="5" t="inlineStr"/>
+      <c r="U205" s="5" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="5" t="n">
         <v>137.9</v>
@@ -15645,7 +16101,9 @@
       <c r="T206" s="5" t="n">
         <v>22.4</v>
       </c>
-      <c r="U206" s="5" t="inlineStr"/>
+      <c r="U206" s="5" t="n">
+        <v>19.4</v>
+      </c>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="5" t="n">
         <v>140.9</v>
@@ -15722,7 +16180,9 @@
       <c r="T207" s="5" t="n">
         <v>24.7</v>
       </c>
-      <c r="U207" s="5" t="inlineStr"/>
+      <c r="U207" s="5" t="n">
+        <v>20.9</v>
+      </c>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="5" t="n">
         <v>143</v>
@@ -15795,7 +16255,9 @@
       <c r="T208" s="5" t="n">
         <v>23.7</v>
       </c>
-      <c r="U208" s="5" t="inlineStr"/>
+      <c r="U208" s="4" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="5" t="n">
         <v>143.1</v>
@@ -15868,8 +16330,14 @@
       <c r="T209" s="4" t="n">
         <v>26.4</v>
       </c>
-      <c r="U209" s="5" t="inlineStr"/>
-      <c r="V209" t="inlineStr"/>
+      <c r="U209" s="4" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V209" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W209" s="5" t="n">
         <v>145</v>
       </c>
@@ -15941,7 +16409,9 @@
       <c r="T210" s="5" t="n">
         <v>23.4</v>
       </c>
-      <c r="U210" s="5" t="inlineStr"/>
+      <c r="U210" s="5" t="n">
+        <v>23.3</v>
+      </c>
       <c r="V210" t="inlineStr"/>
       <c r="W210" s="5" t="n">
         <v>148.3</v>
@@ -16014,7 +16484,9 @@
       <c r="T211" s="5" t="n">
         <v>20.5</v>
       </c>
-      <c r="U211" s="5" t="inlineStr"/>
+      <c r="U211" s="5" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="5" t="n">
         <v>148.6</v>
@@ -16087,7 +16559,9 @@
       <c r="T212" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U212" s="5" t="inlineStr"/>
+      <c r="U212" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="5" t="n">
         <v>151.7</v>
@@ -16160,7 +16634,9 @@
       <c r="T213" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U213" s="5" t="inlineStr"/>
+      <c r="U213" s="5" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="5" t="n">
         <v>145</v>
@@ -16233,7 +16709,9 @@
       <c r="T214" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U214" s="5" t="inlineStr"/>
+      <c r="U214" s="5" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="5" t="n">
         <v>143</v>
@@ -16306,7 +16784,9 @@
       <c r="T215" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U215" s="5" t="inlineStr"/>
+      <c r="U215" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="5" t="n">
         <v>144.9</v>
@@ -16379,7 +16859,9 @@
       <c r="T216" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U216" s="5" t="inlineStr"/>
+      <c r="U216" s="5" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="5" t="n">
         <v>144.9</v>
@@ -16452,7 +16934,9 @@
       <c r="T217" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U217" s="5" t="inlineStr"/>
+      <c r="U217" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="5" t="n">
         <v>149.2</v>
@@ -16525,7 +17009,9 @@
       <c r="T218" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U218" s="5" t="inlineStr"/>
+      <c r="U218" s="5" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="5" t="n">
         <v>148.9</v>
@@ -16598,7 +17084,9 @@
       <c r="T219" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U219" s="5" t="inlineStr"/>
+      <c r="U219" s="5" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="5" t="n">
         <v>148.8</v>
@@ -16671,7 +17159,9 @@
       <c r="T220" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U220" s="5" t="inlineStr"/>
+      <c r="U220" s="5" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="5" t="n">
         <v>150.6</v>
@@ -16744,7 +17234,9 @@
       <c r="T221" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U221" s="5" t="inlineStr"/>
+      <c r="U221" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="5" t="n">
         <v>150.3</v>
@@ -16817,7 +17309,9 @@
       <c r="T222" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U222" s="5" t="inlineStr"/>
+      <c r="U222" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="5" t="n">
         <v>147.6</v>
@@ -16890,7 +17384,9 @@
       <c r="T223" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U223" s="5" t="inlineStr"/>
+      <c r="U223" s="5" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="5" t="n">
         <v>148.3</v>
@@ -16963,7 +17459,9 @@
       <c r="T224" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U224" s="5" t="inlineStr"/>
+      <c r="U224" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="5" t="n">
         <v>153.6</v>
@@ -17040,7 +17538,9 @@
       <c r="T225" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U225" s="5" t="inlineStr"/>
+      <c r="U225" s="5" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="6" t="n">
         <v>161.9</v>
@@ -17113,7 +17613,9 @@
       <c r="T226" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U226" s="5" t="inlineStr"/>
+      <c r="U226" s="5" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="6" t="n">
         <v>157</v>
@@ -17190,7 +17692,9 @@
       <c r="T227" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="U227" s="5" t="inlineStr"/>
+      <c r="U227" s="5" t="n">
+        <v>16.9</v>
+      </c>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="5" t="n">
         <v>153.5</v>
@@ -17263,7 +17767,9 @@
       <c r="T228" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U228" s="5" t="inlineStr"/>
+      <c r="U228" s="5" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="6" t="n">
         <v>155.4</v>
@@ -17336,7 +17842,9 @@
       <c r="T229" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U229" s="5" t="inlineStr"/>
+      <c r="U229" s="5" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="6" t="n">
         <v>155.9</v>
@@ -17409,7 +17917,9 @@
       <c r="T230" s="5" t="n">
         <v>14.1</v>
       </c>
-      <c r="U230" s="5" t="inlineStr"/>
+      <c r="U230" s="5" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="6" t="n">
         <v>159.9</v>
@@ -17482,7 +17992,9 @@
       <c r="T231" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="U231" s="5" t="inlineStr"/>
+      <c r="U231" s="5" t="n">
+        <v>7.6</v>
+      </c>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="6" t="n">
         <v>160.5</v>
@@ -17555,7 +18067,9 @@
       <c r="T232" s="5" t="n">
         <v>13.5</v>
       </c>
-      <c r="U232" s="5" t="inlineStr"/>
+      <c r="U232" s="5" t="n">
+        <v>7.4</v>
+      </c>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="6" t="n">
         <v>160.5</v>
@@ -17628,7 +18142,9 @@
       <c r="T233" s="5" t="n">
         <v>13.6</v>
       </c>
-      <c r="U233" s="5" t="inlineStr"/>
+      <c r="U233" s="5" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="5" t="n">
         <v>151.4</v>
@@ -17701,7 +18217,9 @@
       <c r="T234" s="5" t="n">
         <v>14.2</v>
       </c>
-      <c r="U234" s="5" t="inlineStr"/>
+      <c r="U234" s="5" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="V234" t="inlineStr"/>
       <c r="W234" s="5" t="n">
         <v>150.5</v>
@@ -17774,7 +18292,9 @@
       <c r="T235" s="5" t="n">
         <v>14.3</v>
       </c>
-      <c r="U235" s="5" t="inlineStr"/>
+      <c r="U235" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V235" t="inlineStr"/>
       <c r="W235" s="5" t="n">
         <v>148.3</v>
@@ -17851,7 +18371,9 @@
       <c r="T236" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U236" s="5" t="inlineStr"/>
+      <c r="U236" s="5" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="5" t="n">
         <v>148.7</v>
@@ -17924,7 +18446,9 @@
       <c r="T237" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="U237" s="5" t="inlineStr"/>
+      <c r="U237" s="5" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="5" t="n">
         <v>141.9</v>
@@ -17997,7 +18521,9 @@
       <c r="T238" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U238" s="5" t="inlineStr"/>
+      <c r="U238" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="5" t="n">
         <v>142.4</v>
@@ -18070,7 +18596,9 @@
       <c r="T239" s="5" t="n">
         <v>14.8</v>
       </c>
-      <c r="U239" s="5" t="inlineStr"/>
+      <c r="U239" s="5" t="n">
+        <v>8</v>
+      </c>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="5" t="n">
         <v>146.2</v>
@@ -18143,7 +18671,9 @@
       <c r="T240" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U240" s="5" t="inlineStr"/>
+      <c r="U240" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="5" t="n">
         <v>143.6</v>
@@ -18216,7 +18746,9 @@
       <c r="T241" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U241" s="5" t="inlineStr"/>
+      <c r="U241" s="5" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="5" t="n">
         <v>147.1</v>
@@ -18289,7 +18821,9 @@
       <c r="T242" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="U242" s="5" t="inlineStr"/>
+      <c r="U242" s="5" t="n">
+        <v>8.5</v>
+      </c>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="5" t="n">
         <v>146</v>
@@ -18362,7 +18896,9 @@
       <c r="T243" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U243" s="5" t="inlineStr"/>
+      <c r="U243" s="5" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="5" t="n">
         <v>149.8</v>
@@ -18435,7 +18971,9 @@
       <c r="T244" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U244" s="5" t="inlineStr"/>
+      <c r="U244" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="5" t="n">
         <v>151.6</v>
@@ -18508,7 +19046,9 @@
       <c r="T245" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U245" s="5" t="inlineStr"/>
+      <c r="U245" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="5" t="n">
         <v>152.5</v>
@@ -18581,7 +19121,9 @@
       <c r="T246" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U246" s="5" t="inlineStr"/>
+      <c r="U246" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="5" t="n">
         <v>151.6</v>
@@ -18654,7 +19196,9 @@
       <c r="T247" s="5" t="n">
         <v>15.9</v>
       </c>
-      <c r="U247" s="5" t="inlineStr"/>
+      <c r="U247" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="5" t="n">
         <v>153.6</v>
@@ -18731,7 +19275,9 @@
       <c r="T248" s="5" t="n">
         <v>20.1</v>
       </c>
-      <c r="U248" s="5" t="inlineStr"/>
+      <c r="U248" s="5" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="6" t="n">
         <v>155</v>
@@ -18804,7 +19350,9 @@
       <c r="T249" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U249" s="5" t="inlineStr"/>
+      <c r="U249" s="5" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="5" t="n">
         <v>144.4</v>
@@ -18877,7 +19425,9 @@
       <c r="T250" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="U250" s="5" t="inlineStr"/>
+      <c r="U250" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="5" t="n">
         <v>141.3</v>
@@ -18950,7 +19500,9 @@
       <c r="T251" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U251" s="5" t="inlineStr"/>
+      <c r="U251" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="5" t="n">
         <v>144</v>
@@ -19023,7 +19575,9 @@
       <c r="T252" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U252" s="5" t="inlineStr"/>
+      <c r="U252" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="5" t="n">
         <v>148.1</v>
@@ -19096,7 +19650,9 @@
       <c r="T253" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U253" s="5" t="inlineStr"/>
+      <c r="U253" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="5" t="n">
         <v>147.2</v>
@@ -19169,7 +19725,9 @@
       <c r="T254" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U254" s="5" t="inlineStr"/>
+      <c r="U254" s="5" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="5" t="n">
         <v>145</v>
@@ -19242,7 +19800,9 @@
       <c r="T255" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U255" s="5" t="inlineStr"/>
+      <c r="U255" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="5" t="n">
         <v>143.7</v>
@@ -19319,7 +19879,9 @@
       <c r="T256" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U256" s="5" t="inlineStr"/>
+      <c r="U256" s="5" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V256" t="inlineStr"/>
       <c r="W256" s="5" t="n">
         <v>143.6</v>
@@ -19392,7 +19954,9 @@
       <c r="T257" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U257" s="5" t="inlineStr"/>
+      <c r="U257" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V257" t="inlineStr"/>
       <c r="W257" s="5" t="n">
         <v>146.6</v>
@@ -19469,7 +20033,9 @@
       <c r="T258" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="U258" s="5" t="inlineStr"/>
+      <c r="U258" s="5" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="5" t="n">
         <v>143.9</v>
@@ -19542,7 +20108,9 @@
       <c r="T259" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U259" s="5" t="inlineStr"/>
+      <c r="U259" s="5" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="5" t="n">
         <v>143.2</v>
@@ -19619,7 +20187,9 @@
       <c r="T260" s="5" t="n">
         <v>21.8</v>
       </c>
-      <c r="U260" s="5" t="inlineStr"/>
+      <c r="U260" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V260" t="inlineStr"/>
       <c r="W260" s="5" t="n">
         <v>137.2</v>
@@ -19692,7 +20262,9 @@
       <c r="T261" s="5" t="n">
         <v>20.4</v>
       </c>
-      <c r="U261" s="5" t="inlineStr"/>
+      <c r="U261" s="5" t="n">
+        <v>15</v>
+      </c>
       <c r="V261" t="inlineStr"/>
       <c r="W261" s="5" t="n">
         <v>140.3</v>
@@ -19765,7 +20337,9 @@
       <c r="T262" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U262" s="5" t="inlineStr"/>
+      <c r="U262" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="5" t="n">
         <v>145.2</v>
@@ -19838,7 +20412,9 @@
       <c r="T263" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U263" s="5" t="inlineStr"/>
+      <c r="U263" s="5" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="5" t="n">
         <v>145.7</v>
@@ -19911,7 +20487,9 @@
       <c r="T264" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="U264" s="5" t="inlineStr"/>
+      <c r="U264" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="5" t="n">
         <v>143.8</v>
@@ -19988,7 +20566,9 @@
       <c r="T265" s="5" t="n">
         <v>20.8</v>
       </c>
-      <c r="U265" s="5" t="inlineStr"/>
+      <c r="U265" s="5" t="n">
+        <v>21.5</v>
+      </c>
       <c r="V265" t="inlineStr"/>
       <c r="W265" s="5" t="n">
         <v>142.5</v>
@@ -20061,7 +20641,9 @@
       <c r="T266" s="5" t="n">
         <v>20.6</v>
       </c>
-      <c r="U266" s="5" t="inlineStr"/>
+      <c r="U266" s="5" t="n">
+        <v>22.4</v>
+      </c>
       <c r="V266" t="inlineStr"/>
       <c r="W266" s="5" t="n">
         <v>139.4</v>
@@ -20134,7 +20716,9 @@
       <c r="T267" s="5" t="n">
         <v>20.3</v>
       </c>
-      <c r="U267" s="5" t="inlineStr"/>
+      <c r="U267" s="5" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="5" t="n">
         <v>140.3</v>
@@ -20207,7 +20791,9 @@
       <c r="T268" s="5" t="n">
         <v>19.6</v>
       </c>
-      <c r="U268" s="5" t="inlineStr"/>
+      <c r="U268" s="5" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="5" t="n">
         <v>139.2</v>
@@ -20280,7 +20866,9 @@
       <c r="T269" s="5" t="n">
         <v>20.2</v>
       </c>
-      <c r="U269" s="5" t="inlineStr"/>
+      <c r="U269" s="5" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="5" t="n">
         <v>141.2</v>
@@ -20353,7 +20941,9 @@
       <c r="T270" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="U270" s="5" t="inlineStr"/>
+      <c r="U270" s="5" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="5" t="n">
         <v>145.5</v>
@@ -20426,7 +21016,9 @@
       <c r="T271" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="U271" s="5" t="inlineStr"/>
+      <c r="U271" s="5" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="5" t="n">
         <v>141.4</v>
@@ -20499,7 +21091,9 @@
       <c r="T272" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="U272" s="5" t="inlineStr"/>
+      <c r="U272" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="5" t="n">
         <v>141.9</v>
@@ -20572,7 +21166,9 @@
       <c r="T273" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U273" s="5" t="inlineStr"/>
+      <c r="U273" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="5" t="n">
         <v>146.1</v>
@@ -20649,7 +21245,9 @@
       <c r="T274" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U274" s="5" t="inlineStr"/>
+      <c r="U274" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="5" t="n">
         <v>146.6</v>
@@ -20722,7 +21320,9 @@
       <c r="T275" s="5" t="n">
         <v>19.9</v>
       </c>
-      <c r="U275" s="5" t="inlineStr"/>
+      <c r="U275" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="5" t="n">
         <v>146.7</v>
@@ -20795,7 +21395,9 @@
       <c r="T276" s="5" t="n">
         <v>21.4</v>
       </c>
-      <c r="U276" s="5" t="inlineStr"/>
+      <c r="U276" s="5" t="n">
+        <v>16.3</v>
+      </c>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="5" t="n">
         <v>151.8</v>
@@ -20868,7 +21470,9 @@
       <c r="T277" s="5" t="n">
         <v>23.6</v>
       </c>
-      <c r="U277" s="5" t="inlineStr"/>
+      <c r="U277" s="5" t="n">
+        <v>20.3</v>
+      </c>
       <c r="V277" t="inlineStr"/>
       <c r="W277" s="5" t="n">
         <v>152.8</v>
@@ -20941,7 +21545,9 @@
       <c r="T278" s="5" t="n">
         <v>21.1</v>
       </c>
-      <c r="U278" s="5" t="inlineStr"/>
+      <c r="U278" s="5" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V278" t="inlineStr"/>
       <c r="W278" s="5" t="n">
         <v>152.9</v>
@@ -21014,7 +21620,9 @@
       <c r="T279" s="5" t="n">
         <v>23.8</v>
       </c>
-      <c r="U279" s="5" t="inlineStr"/>
+      <c r="U279" s="5" t="n">
+        <v>21.9</v>
+      </c>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="5" t="n">
         <v>153.9</v>
@@ -21087,8 +21695,14 @@
       <c r="T280" s="4" t="n">
         <v>29.5</v>
       </c>
-      <c r="U280" s="5" t="inlineStr"/>
-      <c r="V280" t="inlineStr"/>
+      <c r="U280" s="4" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="V280" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W280" s="5" t="n">
         <v>151.8</v>
       </c>
@@ -21160,7 +21774,9 @@
       <c r="T281" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="U281" s="5" t="inlineStr"/>
+      <c r="U281" s="5" t="n">
+        <v>22.7</v>
+      </c>
       <c r="V281" t="inlineStr"/>
       <c r="W281" s="6" t="n">
         <v>158</v>
@@ -21233,7 +21849,9 @@
       <c r="T282" s="5" t="n">
         <v>24.9</v>
       </c>
-      <c r="U282" s="5" t="inlineStr"/>
+      <c r="U282" s="5" t="n">
+        <v>21.3</v>
+      </c>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="5" t="n">
         <v>154.5</v>
@@ -21306,7 +21924,9 @@
       <c r="T283" s="5" t="n">
         <v>24.2</v>
       </c>
-      <c r="U283" s="5" t="inlineStr"/>
+      <c r="U283" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="5" t="n">
         <v>152.4</v>
@@ -21373,7 +21993,9 @@
       <c r="T284" s="4" t="n">
         <v>27.3</v>
       </c>
-      <c r="U284" s="5" t="inlineStr"/>
+      <c r="U284" s="5" t="n">
+        <v>24.2</v>
+      </c>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="5" t="n">
         <v>139.9</v>
@@ -21446,8 +22068,14 @@
       <c r="T285" s="4" t="n">
         <v>27.2</v>
       </c>
-      <c r="U285" s="5" t="inlineStr"/>
-      <c r="V285" t="inlineStr"/>
+      <c r="U285" s="4" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="V285" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W285" s="5" t="n">
         <v>137.8</v>
       </c>
@@ -21519,7 +22147,9 @@
       <c r="T286" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="U286" s="5" t="inlineStr"/>
+      <c r="U286" s="5" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V286" t="inlineStr"/>
       <c r="W286" s="5" t="n">
         <v>141.5</v>
@@ -21592,7 +22222,9 @@
       <c r="T287" s="5" t="n">
         <v>22.4</v>
       </c>
-      <c r="U287" s="5" t="inlineStr"/>
+      <c r="U287" s="5" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="5" t="n">
         <v>145</v>
@@ -21665,7 +22297,9 @@
       <c r="T288" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="U288" s="5" t="inlineStr"/>
+      <c r="U288" s="5" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="5" t="n">
         <v>136.5</v>
@@ -21738,7 +22372,9 @@
       <c r="T289" s="5" t="n">
         <v>24.1</v>
       </c>
-      <c r="U289" s="5" t="inlineStr"/>
+      <c r="U289" s="5" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V289" t="inlineStr"/>
       <c r="W289" s="5" t="n">
         <v>138.3</v>
@@ -21811,8 +22447,14 @@
       <c r="T290" s="4" t="n">
         <v>26.8</v>
       </c>
-      <c r="U290" s="5" t="inlineStr"/>
-      <c r="V290" t="inlineStr"/>
+      <c r="U290" s="4" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="V290" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W290" s="5" t="n">
         <v>139.1</v>
       </c>
@@ -21884,7 +22526,9 @@
       <c r="T291" s="4" t="n">
         <v>26.1</v>
       </c>
-      <c r="U291" s="5" t="inlineStr"/>
+      <c r="U291" s="5" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V291" t="inlineStr"/>
       <c r="W291" s="5" t="n">
         <v>142</v>
@@ -21957,7 +22601,9 @@
       <c r="T292" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="U292" s="5" t="inlineStr"/>
+      <c r="U292" s="5" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="5" t="n">
         <v>142.6</v>
@@ -22030,7 +22676,9 @@
       <c r="T293" s="4" t="n">
         <v>25.3</v>
       </c>
-      <c r="U293" s="5" t="inlineStr"/>
+      <c r="U293" s="5" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="5" t="n">
         <v>140.9</v>
@@ -22103,7 +22751,9 @@
       <c r="T294" s="4" t="n">
         <v>27.4</v>
       </c>
-      <c r="U294" s="5" t="inlineStr"/>
+      <c r="U294" s="5" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V294" t="inlineStr"/>
       <c r="W294" s="5" t="n">
         <v>144</v>
@@ -22180,8 +22830,14 @@
       <c r="T295" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="U295" s="5" t="inlineStr"/>
-      <c r="V295" t="inlineStr"/>
+      <c r="U295" s="4" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="V295" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W295" s="5" t="n">
         <v>139</v>
       </c>
@@ -22257,7 +22913,9 @@
       <c r="T296" s="4" t="n">
         <v>30.6</v>
       </c>
-      <c r="U296" s="5" t="inlineStr"/>
+      <c r="U296" s="5" t="n">
+        <v>23</v>
+      </c>
       <c r="V296" t="inlineStr"/>
       <c r="W296" s="5" t="n">
         <v>142.2</v>
@@ -22330,7 +22988,9 @@
       <c r="T297" s="4" t="n">
         <v>25.2</v>
       </c>
-      <c r="U297" s="5" t="inlineStr"/>
+      <c r="U297" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="5" t="n">
         <v>145.4</v>
@@ -22403,7 +23063,9 @@
       <c r="T298" s="5" t="n">
         <v>24.5</v>
       </c>
-      <c r="U298" s="5" t="inlineStr"/>
+      <c r="U298" s="5" t="n">
+        <v>23</v>
+      </c>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="5" t="n">
         <v>143.8</v>
@@ -22476,7 +23138,9 @@
       <c r="T299" s="5" t="n">
         <v>23.9</v>
       </c>
-      <c r="U299" s="5" t="inlineStr"/>
+      <c r="U299" s="4" t="n">
+        <v>27.6</v>
+      </c>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="5" t="n">
         <v>146.9</v>
@@ -22549,7 +23213,9 @@
       <c r="T300" s="5" t="n">
         <v>24.2</v>
       </c>
-      <c r="U300" s="5" t="inlineStr"/>
+      <c r="U300" s="5" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="5" t="n">
         <v>147.6</v>
@@ -22622,8 +23288,14 @@
       <c r="T301" s="4" t="n">
         <v>25.8</v>
       </c>
-      <c r="U301" s="5" t="inlineStr"/>
-      <c r="V301" t="inlineStr"/>
+      <c r="U301" s="4" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="V301" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W301" s="5" t="n">
         <v>148.4</v>
       </c>
@@ -22695,7 +23367,9 @@
       <c r="T302" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="U302" s="5" t="inlineStr"/>
+      <c r="U302" s="5" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V302" t="inlineStr"/>
       <c r="W302" s="5" t="n">
         <v>150.4</v>
@@ -22768,7 +23442,9 @@
       <c r="T303" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="U303" s="5" t="inlineStr"/>
+      <c r="U303" s="5" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="5" t="n">
         <v>143.3</v>
@@ -22841,7 +23517,9 @@
       <c r="T304" s="5" t="n">
         <v>19.2</v>
       </c>
-      <c r="U304" s="5" t="inlineStr"/>
+      <c r="U304" s="5" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="5" t="n">
         <v>144.2</v>
@@ -22914,7 +23592,9 @@
       <c r="T305" s="5" t="n">
         <v>19.1</v>
       </c>
-      <c r="U305" s="5" t="inlineStr"/>
+      <c r="U305" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="6" t="n">
         <v>156.9</v>
@@ -22987,7 +23667,9 @@
       <c r="T306" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U306" s="5" t="inlineStr"/>
+      <c r="U306" s="5" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="5" t="n">
         <v>149.9</v>
@@ -23060,7 +23742,9 @@
       <c r="T307" s="5" t="n">
         <v>18.2</v>
       </c>
-      <c r="U307" s="5" t="inlineStr"/>
+      <c r="U307" s="5" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="5" t="n">
         <v>139.2</v>
@@ -23133,7 +23817,9 @@
       <c r="T308" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U308" s="5" t="inlineStr"/>
+      <c r="U308" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="5" t="n">
         <v>140.7</v>
@@ -23206,7 +23892,9 @@
       <c r="T309" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="U309" s="5" t="inlineStr"/>
+      <c r="U309" s="5" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="5" t="n">
         <v>141.8</v>
@@ -23279,7 +23967,9 @@
       <c r="T310" s="5" t="n">
         <v>18.9</v>
       </c>
-      <c r="U310" s="5" t="inlineStr"/>
+      <c r="U310" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="5" t="n">
         <v>141.9</v>
@@ -23352,7 +24042,9 @@
       <c r="T311" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="U311" s="5" t="inlineStr"/>
+      <c r="U311" s="5" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="5" t="n">
         <v>140.9</v>
@@ -23425,7 +24117,9 @@
       <c r="T312" s="5" t="n">
         <v>18.9</v>
       </c>
-      <c r="U312" s="5" t="inlineStr"/>
+      <c r="U312" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="5" t="n">
         <v>140.8</v>
@@ -23498,7 +24192,9 @@
       <c r="T313" s="5" t="n">
         <v>19.3</v>
       </c>
-      <c r="U313" s="5" t="inlineStr"/>
+      <c r="U313" s="5" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="5" t="n">
         <v>139.6</v>
@@ -23571,7 +24267,9 @@
       <c r="T314" s="5" t="n">
         <v>18.7</v>
       </c>
-      <c r="U314" s="5" t="inlineStr"/>
+      <c r="U314" s="5" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="5" t="n">
         <v>139.1</v>
@@ -23644,7 +24342,9 @@
       <c r="T315" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="U315" s="5" t="inlineStr"/>
+      <c r="U315" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="5" t="n">
         <v>139.6</v>
@@ -23717,7 +24417,9 @@
       <c r="T316" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U316" s="5" t="inlineStr"/>
+      <c r="U316" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="5" t="n">
         <v>138.2</v>
@@ -23790,7 +24492,9 @@
       <c r="T317" s="5" t="n">
         <v>18.8</v>
       </c>
-      <c r="U317" s="5" t="inlineStr"/>
+      <c r="U317" s="5" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="5" t="n">
         <v>141.9</v>
@@ -23863,7 +24567,9 @@
       <c r="T318" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U318" s="5" t="inlineStr"/>
+      <c r="U318" s="5" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="5" t="n">
         <v>143.3</v>
@@ -23936,7 +24642,9 @@
       <c r="T319" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="U319" s="5" t="inlineStr"/>
+      <c r="U319" s="5" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="5" t="n">
         <v>141.4</v>
@@ -24009,7 +24717,9 @@
       <c r="T320" s="5" t="n">
         <v>18.3</v>
       </c>
-      <c r="U320" s="5" t="inlineStr"/>
+      <c r="U320" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="5" t="n">
         <v>141.7</v>
@@ -24082,7 +24792,9 @@
       <c r="T321" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U321" s="5" t="inlineStr"/>
+      <c r="U321" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="5" t="n">
         <v>138.7</v>
@@ -24155,7 +24867,9 @@
       <c r="T322" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U322" s="5" t="inlineStr"/>
+      <c r="U322" s="5" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="5" t="n">
         <v>135.4</v>
@@ -24228,7 +24942,9 @@
       <c r="T323" s="5" t="n">
         <v>17.1</v>
       </c>
-      <c r="U323" s="5" t="inlineStr"/>
+      <c r="U323" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="5" t="n">
         <v>136.1</v>
@@ -24301,7 +25017,9 @@
       <c r="T324" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U324" s="5" t="inlineStr"/>
+      <c r="U324" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V324" t="inlineStr"/>
       <c r="W324" s="5" t="n">
         <v>138.2</v>
@@ -24374,7 +25092,9 @@
       <c r="T325" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U325" s="5" t="inlineStr"/>
+      <c r="U325" s="5" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V325" t="inlineStr"/>
       <c r="W325" s="5" t="n">
         <v>140.2</v>
@@ -24447,7 +25167,9 @@
       <c r="T326" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="U326" s="5" t="inlineStr"/>
+      <c r="U326" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="5" t="n">
         <v>139.4</v>
@@ -24520,7 +25242,9 @@
       <c r="T327" s="5" t="n">
         <v>17.9</v>
       </c>
-      <c r="U327" s="5" t="inlineStr"/>
+      <c r="U327" s="5" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="5" t="n">
         <v>141.5</v>
@@ -24593,7 +25317,9 @@
       <c r="T328" s="5" t="n">
         <v>17.3</v>
       </c>
-      <c r="U328" s="5" t="inlineStr"/>
+      <c r="U328" s="5" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V328" t="inlineStr"/>
       <c r="W328" s="5" t="n">
         <v>139.3</v>
@@ -24666,7 +25392,9 @@
       <c r="T329" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U329" s="5" t="inlineStr"/>
+      <c r="U329" s="5" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V329" t="inlineStr"/>
       <c r="W329" s="5" t="n">
         <v>145.8</v>
@@ -24739,7 +25467,9 @@
       <c r="T330" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U330" s="5" t="inlineStr"/>
+      <c r="U330" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V330" t="inlineStr"/>
       <c r="W330" s="5" t="n">
         <v>138.4</v>
@@ -24812,7 +25542,9 @@
       <c r="T331" s="5" t="n">
         <v>18.1</v>
       </c>
-      <c r="U331" s="5" t="inlineStr"/>
+      <c r="U331" s="5" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="5" t="n">
         <v>135.5</v>
@@ -24885,7 +25617,9 @@
       <c r="T332" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="U332" s="5" t="inlineStr"/>
+      <c r="U332" s="5" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="5" t="n">
         <v>132.3</v>
@@ -24958,7 +25692,9 @@
       <c r="T333" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="U333" s="5" t="inlineStr"/>
+      <c r="U333" s="5" t="n">
+        <v>14</v>
+      </c>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="5" t="n">
         <v>137</v>
@@ -25031,7 +25767,9 @@
       <c r="T334" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U334" s="5" t="inlineStr"/>
+      <c r="U334" s="5" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="5" t="n">
         <v>137.4</v>
@@ -25104,7 +25842,9 @@
       <c r="T335" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="U335" s="5" t="inlineStr"/>
+      <c r="U335" s="5" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="5" t="n">
         <v>139</v>
@@ -25177,7 +25917,9 @@
       <c r="T336" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U336" s="5" t="inlineStr"/>
+      <c r="U336" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="5" t="n">
         <v>138.6</v>
@@ -25250,7 +25992,9 @@
       <c r="T337" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U337" s="5" t="inlineStr"/>
+      <c r="U337" s="5" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="5" t="n">
         <v>139.5</v>
@@ -25323,7 +26067,9 @@
       <c r="T338" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="U338" s="5" t="inlineStr"/>
+      <c r="U338" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="5" t="n">
         <v>144.2</v>
@@ -25396,7 +26142,9 @@
       <c r="T339" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U339" s="5" t="inlineStr"/>
+      <c r="U339" s="5" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="5" t="n">
         <v>142.5</v>
@@ -25469,7 +26217,9 @@
       <c r="T340" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U340" s="5" t="inlineStr"/>
+      <c r="U340" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="5" t="n">
         <v>143.2</v>
@@ -25542,7 +26292,9 @@
       <c r="T341" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U341" s="5" t="inlineStr"/>
+      <c r="U341" s="5" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="5" t="n">
         <v>136.9</v>
@@ -25615,7 +26367,9 @@
       <c r="T342" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U342" s="5" t="inlineStr"/>
+      <c r="U342" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="5" t="n">
         <v>142.1</v>
@@ -25692,7 +26446,9 @@
       <c r="T343" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="U343" s="3" t="inlineStr"/>
+      <c r="U343" s="7" t="n">
+        <v>28.7</v>
+      </c>
       <c r="V343" s="1" t="inlineStr"/>
       <c r="W343" s="3" t="n">
         <v>152.2</v>
@@ -25765,7 +26521,9 @@
       <c r="T344" s="5" t="n">
         <v>18.9</v>
       </c>
-      <c r="U344" s="5" t="inlineStr"/>
+      <c r="U344" s="5" t="n">
+        <v>16</v>
+      </c>
       <c r="V344" t="inlineStr"/>
       <c r="W344" s="5" t="n">
         <v>145</v>
@@ -25838,7 +26596,9 @@
       <c r="T345" s="5" t="n">
         <v>19.9</v>
       </c>
-      <c r="U345" s="5" t="inlineStr"/>
+      <c r="U345" s="5" t="n">
+        <v>20.6</v>
+      </c>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="5" t="n">
         <v>142</v>
@@ -25911,7 +26671,9 @@
       <c r="T346" s="5" t="n">
         <v>22.2</v>
       </c>
-      <c r="U346" s="5" t="inlineStr"/>
+      <c r="U346" s="5" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="5" t="n">
         <v>143.1</v>
@@ -25984,7 +26746,9 @@
       <c r="T347" s="5" t="n">
         <v>19.4</v>
       </c>
-      <c r="U347" s="5" t="inlineStr"/>
+      <c r="U347" s="5" t="n">
+        <v>21.1</v>
+      </c>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="5" t="n">
         <v>143</v>
@@ -26057,7 +26821,9 @@
       <c r="T348" s="5" t="n">
         <v>17.7</v>
       </c>
-      <c r="U348" s="5" t="inlineStr"/>
+      <c r="U348" s="5" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V348" t="inlineStr"/>
       <c r="W348" s="5" t="n">
         <v>142.6</v>
@@ -26130,7 +26896,9 @@
       <c r="T349" s="5" t="n">
         <v>16.2</v>
       </c>
-      <c r="U349" s="5" t="inlineStr"/>
+      <c r="U349" s="5" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="5" t="n">
         <v>144.3</v>
@@ -26203,7 +26971,9 @@
       <c r="T350" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U350" s="5" t="inlineStr"/>
+      <c r="U350" s="5" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="5" t="n">
         <v>142.7</v>
@@ -26280,7 +27050,9 @@
       <c r="T351" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U351" s="5" t="inlineStr"/>
+      <c r="U351" s="5" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="5" t="n">
         <v>142.6</v>
@@ -26353,7 +27125,9 @@
       <c r="T352" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="U352" s="5" t="inlineStr"/>
+      <c r="U352" s="5" t="n">
+        <v>15.7</v>
+      </c>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="5" t="n">
         <v>146.7</v>
@@ -26430,7 +27204,9 @@
       <c r="T353" s="5" t="n">
         <v>17.3</v>
       </c>
-      <c r="U353" s="5" t="inlineStr"/>
+      <c r="U353" s="5" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V353" t="inlineStr"/>
       <c r="W353" s="5" t="n">
         <v>141.9</v>
@@ -26503,7 +27279,9 @@
       <c r="T354" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="U354" s="5" t="inlineStr"/>
+      <c r="U354" s="5" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V354" t="inlineStr"/>
       <c r="W354" s="5" t="n">
         <v>143.1</v>
@@ -26576,7 +27354,9 @@
       <c r="T355" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U355" s="5" t="inlineStr"/>
+      <c r="U355" s="5" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V355" t="inlineStr"/>
       <c r="W355" s="5" t="n">
         <v>145.3</v>
@@ -26649,7 +27429,9 @@
       <c r="T356" s="5" t="n">
         <v>18.9</v>
       </c>
-      <c r="U356" s="5" t="inlineStr"/>
+      <c r="U356" s="5" t="n">
+        <v>16</v>
+      </c>
       <c r="V356" t="inlineStr"/>
       <c r="W356" s="5" t="n">
         <v>139.9</v>
@@ -26722,7 +27504,9 @@
       <c r="T357" s="5" t="n">
         <v>18.4</v>
       </c>
-      <c r="U357" s="5" t="inlineStr"/>
+      <c r="U357" s="5" t="n">
+        <v>17.6</v>
+      </c>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="5" t="n">
         <v>139.4</v>
@@ -26795,7 +27579,9 @@
       <c r="T358" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="U358" s="5" t="inlineStr"/>
+      <c r="U358" s="5" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V358" t="inlineStr"/>
       <c r="W358" s="5" t="n">
         <v>144.5</v>
@@ -26868,7 +27654,9 @@
       <c r="T359" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U359" s="5" t="inlineStr"/>
+      <c r="U359" s="5" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="5" t="n">
         <v>149.6</v>
@@ -26941,7 +27729,9 @@
       <c r="T360" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U360" s="5" t="inlineStr"/>
+      <c r="U360" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="V360" t="inlineStr"/>
       <c r="W360" s="5" t="n">
         <v>154.8</v>
@@ -27018,7 +27808,9 @@
       <c r="T361" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U361" s="5" t="inlineStr"/>
+      <c r="U361" s="5" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V361" t="inlineStr"/>
       <c r="W361" s="5" t="n">
         <v>150</v>
@@ -27091,7 +27883,9 @@
       <c r="T362" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="U362" s="5" t="inlineStr"/>
+      <c r="U362" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V362" t="inlineStr"/>
       <c r="W362" s="5" t="n">
         <v>145.4</v>
@@ -27168,7 +27962,9 @@
       <c r="T363" s="5" t="n">
         <v>16.1</v>
       </c>
-      <c r="U363" s="5" t="inlineStr"/>
+      <c r="U363" s="5" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V363" t="inlineStr"/>
       <c r="W363" s="5" t="n">
         <v>145.7</v>
@@ -27241,7 +28037,9 @@
       <c r="T364" s="5" t="n">
         <v>16.9</v>
       </c>
-      <c r="U364" s="5" t="inlineStr"/>
+      <c r="U364" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="5" t="n">
         <v>149.8</v>
@@ -27314,7 +28112,9 @@
       <c r="T365" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U365" s="5" t="inlineStr"/>
+      <c r="U365" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="5" t="n">
         <v>144.7</v>
@@ -27387,7 +28187,9 @@
       <c r="T366" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="U366" s="5" t="inlineStr"/>
+      <c r="U366" s="5" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="5" t="n">
         <v>144.3</v>
@@ -27464,7 +28266,9 @@
       <c r="T367" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U367" s="5" t="inlineStr"/>
+      <c r="U367" s="5" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V367" t="inlineStr"/>
       <c r="W367" s="5" t="n">
         <v>145.7</v>
@@ -27537,7 +28341,9 @@
       <c r="T368" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U368" s="5" t="inlineStr"/>
+      <c r="U368" s="5" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V368" t="inlineStr"/>
       <c r="W368" s="5" t="n">
         <v>145.1</v>
@@ -27610,7 +28416,9 @@
       <c r="T369" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U369" s="5" t="inlineStr"/>
+      <c r="U369" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V369" t="inlineStr"/>
       <c r="W369" s="5" t="n">
         <v>148.5</v>
@@ -27687,7 +28495,9 @@
       <c r="T370" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="U370" s="5" t="inlineStr"/>
+      <c r="U370" s="5" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="5" t="n">
         <v>145.7</v>
@@ -27760,7 +28570,9 @@
       <c r="T371" s="5" t="n">
         <v>18.8</v>
       </c>
-      <c r="U371" s="5" t="inlineStr"/>
+      <c r="U371" s="5" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="5" t="n">
         <v>147.3</v>
@@ -27833,7 +28645,9 @@
       <c r="T372" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U372" s="5" t="inlineStr"/>
+      <c r="U372" s="5" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="5" t="n">
         <v>146.1</v>
@@ -27906,7 +28720,9 @@
       <c r="T373" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="U373" s="5" t="inlineStr"/>
+      <c r="U373" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V373" t="inlineStr"/>
       <c r="W373" s="5" t="n">
         <v>151.7</v>
@@ -27979,7 +28795,9 @@
       <c r="T374" s="5" t="n">
         <v>16.6</v>
       </c>
-      <c r="U374" s="5" t="inlineStr"/>
+      <c r="U374" s="5" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V374" t="inlineStr"/>
       <c r="W374" s="5" t="n">
         <v>150.2</v>
@@ -28052,7 +28870,9 @@
       <c r="T375" s="5" t="n">
         <v>18.7</v>
       </c>
-      <c r="U375" s="5" t="inlineStr"/>
+      <c r="U375" s="5" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V375" t="inlineStr"/>
       <c r="W375" s="5" t="n">
         <v>145.9</v>
@@ -28125,7 +28945,9 @@
       <c r="T376" s="5" t="n">
         <v>18.6</v>
       </c>
-      <c r="U376" s="5" t="inlineStr"/>
+      <c r="U376" s="5" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V376" t="inlineStr"/>
       <c r="W376" s="5" t="n">
         <v>147.3</v>
@@ -28198,7 +29020,9 @@
       <c r="T377" s="5" t="n">
         <v>18.7</v>
       </c>
-      <c r="U377" s="5" t="inlineStr"/>
+      <c r="U377" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V377" t="inlineStr"/>
       <c r="W377" s="5" t="n">
         <v>146.6</v>
@@ -28271,7 +29095,9 @@
       <c r="T378" s="5" t="n">
         <v>18.2</v>
       </c>
-      <c r="U378" s="5" t="inlineStr"/>
+      <c r="U378" s="5" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V378" t="inlineStr"/>
       <c r="W378" s="5" t="n">
         <v>143</v>
@@ -28348,7 +29174,9 @@
       <c r="T379" s="5" t="n">
         <v>20.7</v>
       </c>
-      <c r="U379" s="5" t="inlineStr"/>
+      <c r="U379" s="5" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V379" t="inlineStr"/>
       <c r="W379" s="5" t="n">
         <v>139.6</v>
@@ -28421,7 +29249,9 @@
       <c r="T380" s="5" t="n">
         <v>17.1</v>
       </c>
-      <c r="U380" s="5" t="inlineStr"/>
+      <c r="U380" s="5" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V380" t="inlineStr"/>
       <c r="W380" s="5" t="n">
         <v>139.9</v>
@@ -28494,7 +29324,9 @@
       <c r="T381" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U381" s="5" t="inlineStr"/>
+      <c r="U381" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V381" t="inlineStr"/>
       <c r="W381" s="5" t="n">
         <v>141.2</v>
@@ -28567,7 +29399,9 @@
       <c r="T382" s="5" t="n">
         <v>15.9</v>
       </c>
-      <c r="U382" s="5" t="inlineStr"/>
+      <c r="U382" s="5" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V382" t="inlineStr"/>
       <c r="W382" s="5" t="n">
         <v>140</v>
@@ -28640,7 +29474,9 @@
       <c r="T383" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U383" s="5" t="inlineStr"/>
+      <c r="U383" s="5" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V383" t="inlineStr"/>
       <c r="W383" s="4" t="n">
         <v>126.4</v>
@@ -28713,7 +29549,9 @@
       <c r="T384" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U384" s="5" t="inlineStr"/>
+      <c r="U384" s="5" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V384" t="inlineStr"/>
       <c r="W384" s="5" t="n">
         <v>133.3</v>
@@ -28786,7 +29624,9 @@
       <c r="T385" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U385" s="5" t="inlineStr"/>
+      <c r="U385" s="5" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V385" t="inlineStr"/>
       <c r="W385" s="5" t="n">
         <v>134.7</v>
@@ -28859,7 +29699,9 @@
       <c r="T386" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U386" s="5" t="inlineStr"/>
+      <c r="U386" s="5" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V386" t="inlineStr"/>
       <c r="W386" s="5" t="n">
         <v>132.6</v>
@@ -28932,7 +29774,9 @@
       <c r="T387" s="5" t="n">
         <v>15.5</v>
       </c>
-      <c r="U387" s="5" t="inlineStr"/>
+      <c r="U387" s="5" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V387" t="inlineStr"/>
       <c r="W387" s="5" t="n">
         <v>137.1</v>
@@ -29005,7 +29849,9 @@
       <c r="T388" s="5" t="n">
         <v>15.3</v>
       </c>
-      <c r="U388" s="5" t="inlineStr"/>
+      <c r="U388" s="5" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V388" t="inlineStr"/>
       <c r="W388" s="5" t="n">
         <v>135.6</v>
@@ -29078,7 +29924,9 @@
       <c r="T389" s="5" t="n">
         <v>14.6</v>
       </c>
-      <c r="U389" s="5" t="inlineStr"/>
+      <c r="U389" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V389" t="inlineStr"/>
       <c r="W389" s="5" t="n">
         <v>136.5</v>
@@ -29151,7 +29999,9 @@
       <c r="T390" s="5" t="n">
         <v>14.6</v>
       </c>
-      <c r="U390" s="5" t="inlineStr"/>
+      <c r="U390" s="5" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V390" t="inlineStr"/>
       <c r="W390" s="5" t="n">
         <v>134.4</v>
@@ -29224,7 +30074,9 @@
       <c r="T391" s="5" t="n">
         <v>14.2</v>
       </c>
-      <c r="U391" s="5" t="inlineStr"/>
+      <c r="U391" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V391" t="inlineStr"/>
       <c r="W391" s="5" t="n">
         <v>138.4</v>
@@ -29297,7 +30149,9 @@
       <c r="T392" s="5" t="n">
         <v>15.2</v>
       </c>
-      <c r="U392" s="5" t="inlineStr"/>
+      <c r="U392" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V392" t="inlineStr"/>
       <c r="W392" s="5" t="n">
         <v>142.9</v>
@@ -29370,7 +30224,9 @@
       <c r="T393" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U393" s="5" t="inlineStr"/>
+      <c r="U393" s="5" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V393" t="inlineStr"/>
       <c r="W393" s="5" t="n">
         <v>143.6</v>
@@ -29443,7 +30299,9 @@
       <c r="T394" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U394" s="5" t="inlineStr"/>
+      <c r="U394" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V394" t="inlineStr"/>
       <c r="W394" s="5" t="n">
         <v>142.9</v>
@@ -29516,7 +30374,9 @@
       <c r="T395" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="U395" s="5" t="inlineStr"/>
+      <c r="U395" s="5" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V395" t="inlineStr"/>
       <c r="W395" s="5" t="n">
         <v>143.2</v>
@@ -29589,7 +30449,9 @@
       <c r="T396" s="5" t="n">
         <v>15.1</v>
       </c>
-      <c r="U396" s="5" t="inlineStr"/>
+      <c r="U396" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="V396" t="inlineStr"/>
       <c r="W396" s="5" t="n">
         <v>143.9</v>
@@ -29666,7 +30528,9 @@
       <c r="T397" s="5" t="n">
         <v>15.9</v>
       </c>
-      <c r="U397" s="5" t="inlineStr"/>
+      <c r="U397" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V397" t="inlineStr"/>
       <c r="W397" s="5" t="n">
         <v>145.6</v>
@@ -29739,7 +30603,9 @@
       <c r="T398" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U398" s="5" t="inlineStr"/>
+      <c r="U398" s="5" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V398" t="inlineStr"/>
       <c r="W398" s="5" t="n">
         <v>143.3</v>
@@ -29812,7 +30678,9 @@
       <c r="T399" s="5" t="n">
         <v>15.2</v>
       </c>
-      <c r="U399" s="5" t="inlineStr"/>
+      <c r="U399" s="5" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V399" t="inlineStr"/>
       <c r="W399" s="5" t="n">
         <v>143</v>
@@ -29885,7 +30753,9 @@
       <c r="T400" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="U400" s="5" t="inlineStr"/>
+      <c r="U400" s="5" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V400" t="inlineStr"/>
       <c r="W400" s="5" t="n">
         <v>144.1</v>
@@ -29958,7 +30828,9 @@
       <c r="T401" s="5" t="n">
         <v>14.4</v>
       </c>
-      <c r="U401" s="5" t="inlineStr"/>
+      <c r="U401" s="5" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V401" t="inlineStr"/>
       <c r="W401" s="5" t="n">
         <v>149.8</v>
@@ -30035,7 +30907,9 @@
       <c r="T402" s="5" t="n">
         <v>14.9</v>
       </c>
-      <c r="U402" s="5" t="inlineStr"/>
+      <c r="U402" s="5" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V402" t="inlineStr"/>
       <c r="W402" s="5" t="n">
         <v>148.5</v>
@@ -30108,7 +30982,9 @@
       <c r="T403" s="5" t="n">
         <v>16.3</v>
       </c>
-      <c r="U403" s="5" t="inlineStr"/>
+      <c r="U403" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V403" t="inlineStr"/>
       <c r="W403" s="5" t="n">
         <v>149.2</v>
@@ -30181,7 +31057,9 @@
       <c r="T404" s="5" t="n">
         <v>15.2</v>
       </c>
-      <c r="U404" s="5" t="inlineStr"/>
+      <c r="U404" s="5" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V404" t="inlineStr"/>
       <c r="W404" s="5" t="n">
         <v>144.1</v>
@@ -30254,7 +31132,9 @@
       <c r="T405" s="5" t="n">
         <v>14.3</v>
       </c>
-      <c r="U405" s="5" t="inlineStr"/>
+      <c r="U405" s="5" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V405" t="inlineStr"/>
       <c r="W405" s="5" t="n">
         <v>150.6</v>
@@ -30327,7 +31207,9 @@
       <c r="T406" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="U406" s="5" t="inlineStr"/>
+      <c r="U406" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="V406" t="inlineStr"/>
       <c r="W406" s="5" t="n">
         <v>151.6</v>
@@ -30400,7 +31282,9 @@
       <c r="T407" s="5" t="n">
         <v>15.7</v>
       </c>
-      <c r="U407" s="5" t="inlineStr"/>
+      <c r="U407" s="5" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V407" t="inlineStr"/>
       <c r="W407" s="5" t="n">
         <v>148.9</v>
@@ -30477,7 +31361,9 @@
       <c r="T408" s="5" t="n">
         <v>16.5</v>
       </c>
-      <c r="U408" s="5" t="inlineStr"/>
+      <c r="U408" s="5" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V408" t="inlineStr"/>
       <c r="W408" s="5" t="n">
         <v>149.2</v>
@@ -30550,7 +31436,9 @@
       <c r="T409" s="5" t="n">
         <v>17.8</v>
       </c>
-      <c r="U409" s="5" t="inlineStr"/>
+      <c r="U409" s="5" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V409" t="inlineStr"/>
       <c r="W409" s="5" t="n">
         <v>147</v>
@@ -30623,7 +31511,9 @@
       <c r="T410" s="5" t="n">
         <v>15.8</v>
       </c>
-      <c r="U410" s="5" t="inlineStr"/>
+      <c r="U410" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="V410" t="inlineStr"/>
       <c r="W410" s="5" t="n">
         <v>154.5</v>
@@ -30700,7 +31590,9 @@
       <c r="T411" s="5" t="n">
         <v>17.1</v>
       </c>
-      <c r="U411" s="5" t="inlineStr"/>
+      <c r="U411" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="V411" t="inlineStr"/>
       <c r="W411" s="5" t="n">
         <v>152.1</v>
@@ -30777,7 +31669,9 @@
       <c r="T412" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="U412" s="5" t="inlineStr"/>
+      <c r="U412" s="5" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="5" t="n">
         <v>146.6</v>
@@ -30850,7 +31744,9 @@
       <c r="T413" s="5" t="n">
         <v>17.7</v>
       </c>
-      <c r="U413" s="5" t="inlineStr"/>
+      <c r="U413" s="5" t="n">
+        <v>17</v>
+      </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="5" t="n">
         <v>145.9</v>
@@ -30923,7 +31819,9 @@
       <c r="T414" s="5" t="n">
         <v>15.4</v>
       </c>
-      <c r="U414" s="5" t="inlineStr"/>
+      <c r="U414" s="5" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="5" t="n">
         <v>145.7</v>
@@ -30947,34 +31845,34 @@
         <v>26544.93</v>
       </c>
       <c r="E415" t="n">
-        <v>26398.89</v>
+        <v>26333.98</v>
       </c>
       <c r="F415" t="n">
-        <v>26419.4</v>
+        <v>26412.55</v>
       </c>
       <c r="G415" t="n">
-        <v>2361512000</v>
-      </c>
-      <c r="H415" s="5" t="n">
-        <v>0</v>
+        <v>5673471000</v>
+      </c>
+      <c r="H415" s="6" t="n">
+        <v>-0.02</v>
       </c>
       <c r="I415" t="n">
         <v>2.6</v>
       </c>
       <c r="J415" t="n">
-        <v>26261.95</v>
+        <v>26261.61</v>
       </c>
       <c r="K415" t="n">
-        <v>26034.26</v>
+        <v>26034.15</v>
       </c>
       <c r="L415" t="n">
-        <v>25580.47</v>
+        <v>25580.41</v>
       </c>
       <c r="M415" t="n">
-        <v>24552.69</v>
+        <v>24552.65</v>
       </c>
       <c r="N415" s="5" t="n">
-        <v>50.36</v>
+        <v>50.22</v>
       </c>
       <c r="O415" t="n">
         <v>29</v>
@@ -30994,10 +31892,10 @@
         <v>5</v>
       </c>
       <c r="T415" s="5" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="U415" s="5" t="n">
-        <v>7.5</v>
+        <v>10.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="5" t="inlineStr"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31848,31 +31848,31 @@
         <v>26333.98</v>
       </c>
       <c r="F415" t="n">
-        <v>26412.55</v>
+        <v>26522.54</v>
       </c>
       <c r="G415" t="n">
-        <v>5673471000</v>
-      </c>
-      <c r="H415" s="6" t="n">
-        <v>-0.02</v>
+        <v>12765500000</v>
+      </c>
+      <c r="H415" s="4" t="n">
+        <v>0.39</v>
       </c>
       <c r="I415" t="n">
         <v>2.6</v>
       </c>
       <c r="J415" t="n">
-        <v>26261.61</v>
+        <v>26267.11</v>
       </c>
       <c r="K415" t="n">
-        <v>26034.15</v>
+        <v>26035.98</v>
       </c>
       <c r="L415" t="n">
-        <v>25580.41</v>
+        <v>25581.33</v>
       </c>
       <c r="M415" t="n">
-        <v>24552.65</v>
+        <v>24553.2</v>
       </c>
       <c r="N415" s="5" t="n">
-        <v>50.22</v>
+        <v>52.46</v>
       </c>
       <c r="O415" t="n">
         <v>29</v>
@@ -31892,13 +31892,15 @@
         <v>5</v>
       </c>
       <c r="T415" s="5" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="U415" s="5" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="5" t="inlineStr"/>
+      <c r="W415" s="5" t="n">
+        <v>148.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31851,7 +31851,7 @@
         <v>26522.54</v>
       </c>
       <c r="G415" t="n">
-        <v>12765500000</v>
+        <v>12789451000</v>
       </c>
       <c r="H415" s="4" t="n">
         <v>0.39</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1748,7 +1748,7 @@
         <v>2.6</v>
       </c>
       <c r="J17" t="n">
-        <v>19729.46</v>
+        <v>19729.47</v>
       </c>
       <c r="K17" t="n">
         <v>19630.93</v>
@@ -4540,7 +4540,7 @@
         <v>2.6</v>
       </c>
       <c r="J53" t="n">
-        <v>17132.26</v>
+        <v>17132.25</v>
       </c>
       <c r="K53" t="n">
         <v>18472.28</v>
@@ -31646,7 +31646,7 @@
         <v>52.46</v>
       </c>
       <c r="O412" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31672,6 +31672,79 @@
       <c r="W412" s="2" t="n">
         <v>148.1</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>26723.19</v>
+      </c>
+      <c r="D413" t="n">
+        <v>27064.05</v>
+      </c>
+      <c r="E413" t="n">
+        <v>26707.42</v>
+      </c>
+      <c r="F413" t="n">
+        <v>27045.13</v>
+      </c>
+      <c r="G413" t="n">
+        <v>4438515000</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J413" t="n">
+        <v>26310.34</v>
+      </c>
+      <c r="K413" t="n">
+        <v>26064.09</v>
+      </c>
+      <c r="L413" t="n">
+        <v>25633.42</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24571.36</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="O413" t="n">
+        <v>34</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31688,37 +31688,37 @@
         <v>26723.19</v>
       </c>
       <c r="D413" t="n">
-        <v>27064.05</v>
+        <v>27183.93</v>
       </c>
       <c r="E413" t="n">
         <v>26707.42</v>
       </c>
       <c r="F413" t="n">
-        <v>27045.13</v>
+        <v>27122.09</v>
       </c>
       <c r="G413" t="n">
-        <v>4438515000</v>
+        <v>7779786000</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="I413" t="n">
         <v>2.6</v>
       </c>
       <c r="J413" t="n">
-        <v>26310.34</v>
+        <v>26314.19</v>
       </c>
       <c r="K413" t="n">
-        <v>26064.09</v>
+        <v>26065.37</v>
       </c>
       <c r="L413" t="n">
-        <v>25633.42</v>
+        <v>25634.06</v>
       </c>
       <c r="M413" t="n">
-        <v>24571.36</v>
+        <v>24571.74</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>61.5</v>
+        <v>62.49</v>
       </c>
       <c r="O413" t="n">
         <v>34</v>
@@ -31735,13 +31735,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31697,7 +31697,7 @@
         <v>27122.09</v>
       </c>
       <c r="G413" t="n">
-        <v>7779786000</v>
+        <v>7862256000</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>2.26</v>
@@ -31744,7 +31744,9 @@
         <v>10</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>142.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31622,7 +31622,7 @@
         <v>27122.09</v>
       </c>
       <c r="G412" t="n">
-        <v>7862256000</v>
+        <v>8813260000</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>2.26</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31673,6 +31673,79 @@
         <v>142.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>27161.2</v>
+      </c>
+      <c r="D413" t="n">
+        <v>27270.9</v>
+      </c>
+      <c r="E413" t="n">
+        <v>27161.2</v>
+      </c>
+      <c r="F413" t="n">
+        <v>27251.37</v>
+      </c>
+      <c r="G413" t="n">
+        <v>2316665000</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J413" t="n">
+        <v>26377.75</v>
+      </c>
+      <c r="K413" t="n">
+        <v>26097.94</v>
+      </c>
+      <c r="L413" t="n">
+        <v>25681.23</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24590.73</v>
+      </c>
+      <c r="N413" s="1" t="n">
+        <v>70.09</v>
+      </c>
+      <c r="O413" t="n">
+        <v>37</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31688,40 +31688,40 @@
         <v>27161.2</v>
       </c>
       <c r="D413" t="n">
-        <v>27270.9</v>
+        <v>27272.72</v>
       </c>
       <c r="E413" t="n">
         <v>27161.2</v>
       </c>
       <c r="F413" t="n">
-        <v>27251.37</v>
+        <v>27240.58</v>
       </c>
       <c r="G413" t="n">
-        <v>2316665000</v>
+        <v>5599825000</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>0.48</v>
+        <v>0.44</v>
       </c>
       <c r="I413" t="n">
         <v>2.6</v>
       </c>
       <c r="J413" t="n">
-        <v>26377.75</v>
+        <v>26377.21</v>
       </c>
       <c r="K413" t="n">
-        <v>26097.94</v>
+        <v>26097.76</v>
       </c>
       <c r="L413" t="n">
-        <v>25681.23</v>
+        <v>25681.14</v>
       </c>
       <c r="M413" t="n">
-        <v>24590.73</v>
-      </c>
-      <c r="N413" s="1" t="n">
-        <v>70.09</v>
+        <v>24590.68</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>69.98</v>
       </c>
       <c r="O413" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31738,10 +31738,10 @@
         <v>4.95</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31688,40 +31688,40 @@
         <v>27161.2</v>
       </c>
       <c r="D413" t="n">
-        <v>27272.72</v>
+        <v>27288.79</v>
       </c>
       <c r="E413" t="n">
         <v>27161.2</v>
       </c>
       <c r="F413" t="n">
-        <v>27240.58</v>
+        <v>27244.28</v>
       </c>
       <c r="G413" t="n">
-        <v>5599825000</v>
+        <v>8014146000</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="I413" t="n">
         <v>2.6</v>
       </c>
       <c r="J413" t="n">
-        <v>26377.21</v>
+        <v>26377.4</v>
       </c>
       <c r="K413" t="n">
-        <v>26097.76</v>
+        <v>26097.82</v>
       </c>
       <c r="L413" t="n">
-        <v>25681.14</v>
+        <v>25681.17</v>
       </c>
       <c r="M413" t="n">
-        <v>24590.68</v>
-      </c>
-      <c r="N413" s="2" t="n">
-        <v>69.98</v>
+        <v>24590.69</v>
+      </c>
+      <c r="N413" s="1" t="n">
+        <v>70.02</v>
       </c>
       <c r="O413" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31735,16 +31735,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.97</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>144.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31609,41 +31609,25 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="C412" t="n">
-        <v>27161.2</v>
-      </c>
-      <c r="D412" t="n">
-        <v>27288.79</v>
-      </c>
-      <c r="E412" t="n">
-        <v>27161.2</v>
-      </c>
-      <c r="F412" t="n">
-        <v>27244.28</v>
-      </c>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr"/>
       <c r="G412" t="n">
         <v>8014146000</v>
       </c>
-      <c r="H412" s="3" t="n">
-        <v>0.45</v>
+      <c r="H412" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I412" t="n">
         <v>2.6</v>
       </c>
-      <c r="J412" t="n">
-        <v>26377.4</v>
-      </c>
-      <c r="K412" t="n">
-        <v>26097.82</v>
-      </c>
-      <c r="L412" t="n">
-        <v>25681.17</v>
-      </c>
-      <c r="M412" t="n">
-        <v>24590.69</v>
-      </c>
-      <c r="N412" s="1" t="n">
-        <v>70.02</v>
+      <c r="J412" t="inlineStr"/>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr"/>
+      <c r="N412" s="2" t="n">
+        <v>68.68000000000001</v>
       </c>
       <c r="O412" t="n">
         <v>35</v>
@@ -31659,19 +31643,11 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="T412" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U412" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="S412" t="inlineStr"/>
+      <c r="T412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
-      <c r="W412" s="2" t="n">
-        <v>144.8</v>
-      </c>
+      <c r="W412" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31606,31 +31606,47 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>27213.52</v>
+      </c>
+      <c r="D412" t="n">
+        <v>27217.33</v>
+      </c>
+      <c r="E412" t="n">
+        <v>26902.25</v>
+      </c>
+      <c r="F412" t="n">
+        <v>26944.2</v>
+      </c>
       <c r="G412" t="n">
-        <v>8014146000</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>3924462000</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>-0.66</v>
       </c>
       <c r="I412" t="n">
         <v>2.6</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>26362.39</v>
+      </c>
+      <c r="K412" t="n">
+        <v>26092.82</v>
+      </c>
+      <c r="L412" t="n">
+        <v>25678.67</v>
+      </c>
+      <c r="M412" t="n">
+        <v>24589.19</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>68.68000000000001</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="O412" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31643,9 +31659,15 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="inlineStr"/>
-      <c r="T412" s="2" t="inlineStr"/>
-      <c r="U412" s="2" t="inlineStr"/>
+      <c r="S412" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T412" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="U412" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -1598,7 +1598,7 @@
         <v>2.6</v>
       </c>
       <c r="J15" t="n">
-        <v>19729.47</v>
+        <v>19729.46</v>
       </c>
       <c r="K15" t="n">
         <v>19630.93</v>
@@ -4390,7 +4390,7 @@
         <v>2.6</v>
       </c>
       <c r="J51" t="n">
-        <v>17132.25</v>
+        <v>17132.26</v>
       </c>
       <c r="K51" t="n">
         <v>18472.28</v>
@@ -31616,37 +31616,37 @@
         <v>27217.33</v>
       </c>
       <c r="E412" t="n">
-        <v>26902.25</v>
+        <v>26873.54</v>
       </c>
       <c r="F412" t="n">
-        <v>26944.2</v>
+        <v>26936.04</v>
       </c>
       <c r="G412" t="n">
-        <v>3924462000</v>
+        <v>6531846000</v>
       </c>
       <c r="H412" s="1" t="n">
-        <v>-0.66</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I412" t="n">
         <v>2.6</v>
       </c>
       <c r="J412" t="n">
-        <v>26362.39</v>
+        <v>26361.99</v>
       </c>
       <c r="K412" t="n">
-        <v>26092.82</v>
+        <v>26092.68</v>
       </c>
       <c r="L412" t="n">
-        <v>25678.67</v>
+        <v>25678.6</v>
       </c>
       <c r="M412" t="n">
-        <v>24589.19</v>
+        <v>24589.15</v>
       </c>
       <c r="N412" s="2" t="n">
-        <v>64.48999999999999</v>
+        <v>64.31</v>
       </c>
       <c r="O412" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31660,13 +31660,13 @@
       </c>
       <c r="R412" t="inlineStr"/>
       <c r="S412" t="n">
-        <v>5.09</v>
+        <v>5.11</v>
       </c>
       <c r="T412" s="2" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="U412" s="2" t="n">
-        <v>8.4</v>
+        <v>10.6</v>
       </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="inlineStr"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31622,7 +31622,7 @@
         <v>26936.04</v>
       </c>
       <c r="G412" t="n">
-        <v>6531846000</v>
+        <v>7578948000</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-0.6899999999999999</v>
@@ -31666,10 +31666,12 @@
         <v>15.2</v>
       </c>
       <c r="U412" s="2" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="V412" t="inlineStr"/>
-      <c r="W412" s="2" t="inlineStr"/>
+      <c r="W412" s="2" t="n">
+        <v>146.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31622,7 +31622,7 @@
         <v>26936.04</v>
       </c>
       <c r="G412" t="n">
-        <v>7578948000</v>
+        <v>8491740000</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-0.6899999999999999</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31646,7 +31646,7 @@
         <v>64.31</v>
       </c>
       <c r="O412" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31672,6 +31672,79 @@
       <c r="W412" s="2" t="n">
         <v>146.1</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>26734.51</v>
+      </c>
+      <c r="D413" t="n">
+        <v>26971.04</v>
+      </c>
+      <c r="E413" t="n">
+        <v>26706.14</v>
+      </c>
+      <c r="F413" t="n">
+        <v>26904.35</v>
+      </c>
+      <c r="G413" t="n">
+        <v>4902954000</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J413" t="n">
+        <v>26399.64</v>
+      </c>
+      <c r="K413" t="n">
+        <v>26110.75</v>
+      </c>
+      <c r="L413" t="n">
+        <v>25720.8</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24606.15</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="O413" t="n">
+        <v>35</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31694,34 +31694,34 @@
         <v>26706.14</v>
       </c>
       <c r="F413" t="n">
-        <v>26904.35</v>
+        <v>26939.37</v>
       </c>
       <c r="G413" t="n">
-        <v>4902954000</v>
-      </c>
-      <c r="H413" s="1" t="n">
-        <v>-0.12</v>
+        <v>7111923000</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0.01</v>
       </c>
       <c r="I413" t="n">
         <v>2.6</v>
       </c>
       <c r="J413" t="n">
-        <v>26399.64</v>
+        <v>26401.39</v>
       </c>
       <c r="K413" t="n">
-        <v>26110.75</v>
+        <v>26111.33</v>
       </c>
       <c r="L413" t="n">
-        <v>25720.8</v>
+        <v>25721.09</v>
       </c>
       <c r="M413" t="n">
-        <v>24606.15</v>
+        <v>24606.32</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>62.1</v>
+        <v>62.85</v>
       </c>
       <c r="O413" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31735,16 +31735,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.18</v>
+        <v>5.16</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31697,7 +31697,7 @@
         <v>26939.37</v>
       </c>
       <c r="G413" t="n">
-        <v>7111923000</v>
+        <v>8078820000</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>0.01</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31606,47 +31606,47 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>27213.52</v>
+        <v>27161.2</v>
       </c>
       <c r="D412" t="n">
-        <v>27217.33</v>
+        <v>27288.79</v>
       </c>
       <c r="E412" t="n">
-        <v>26873.54</v>
+        <v>27161.2</v>
       </c>
       <c r="F412" t="n">
-        <v>26936.04</v>
+        <v>27244.28</v>
       </c>
       <c r="G412" t="n">
-        <v>8491740000</v>
-      </c>
-      <c r="H412" s="1" t="n">
-        <v>-0.6899999999999999</v>
+        <v>9334690000</v>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>0.45</v>
       </c>
       <c r="I412" t="n">
         <v>2.6</v>
       </c>
       <c r="J412" t="n">
-        <v>26361.99</v>
+        <v>26377.4</v>
       </c>
       <c r="K412" t="n">
-        <v>26092.68</v>
+        <v>26097.82</v>
       </c>
       <c r="L412" t="n">
-        <v>25678.6</v>
+        <v>25681.17</v>
       </c>
       <c r="M412" t="n">
-        <v>24589.15</v>
-      </c>
-      <c r="N412" s="2" t="n">
-        <v>64.31</v>
+        <v>24590.69</v>
+      </c>
+      <c r="N412" s="1" t="n">
+        <v>70.02</v>
       </c>
       <c r="O412" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31660,17 +31660,17 @@
       </c>
       <c r="R412" t="inlineStr"/>
       <c r="S412" t="n">
-        <v>5.11</v>
+        <v>4.97</v>
       </c>
       <c r="T412" s="2" t="n">
-        <v>15.2</v>
+        <v>14.2</v>
       </c>
       <c r="U412" s="2" t="n">
-        <v>10.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
-        <v>146.1</v>
+        <v>144.8</v>
       </c>
     </row>
     <row r="413">
@@ -31681,47 +31681,47 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C413" t="n">
-        <v>26734.51</v>
+        <v>27213.52</v>
       </c>
       <c r="D413" t="n">
-        <v>26971.04</v>
+        <v>27217.33</v>
       </c>
       <c r="E413" t="n">
-        <v>26706.14</v>
+        <v>26873.54</v>
       </c>
       <c r="F413" t="n">
-        <v>26939.37</v>
+        <v>26936.04</v>
       </c>
       <c r="G413" t="n">
-        <v>8078820000</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>0.01</v>
+        <v>8491740000</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-1.13</v>
       </c>
       <c r="I413" t="n">
         <v>2.6</v>
       </c>
       <c r="J413" t="n">
-        <v>26401.39</v>
+        <v>26416.63</v>
       </c>
       <c r="K413" t="n">
-        <v>26111.33</v>
+        <v>26116.42</v>
       </c>
       <c r="L413" t="n">
-        <v>25721.09</v>
+        <v>25723.63</v>
       </c>
       <c r="M413" t="n">
-        <v>24606.32</v>
+        <v>24607.85</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>62.85</v>
+        <v>61.78</v>
       </c>
       <c r="O413" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31735,16 +31735,91 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.16</v>
+        <v>5.11</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.7</v>
+        <v>15.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>12.1</v>
+        <v>10.7</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
+        <v>146.1</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>26734.51</v>
+      </c>
+      <c r="D414" t="n">
+        <v>26971.04</v>
+      </c>
+      <c r="E414" t="n">
+        <v>26706.14</v>
+      </c>
+      <c r="F414" t="n">
+        <v>26939.37</v>
+      </c>
+      <c r="G414" t="n">
+        <v>8078820000</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J414" t="n">
+        <v>26457.09</v>
+      </c>
+      <c r="K414" t="n">
+        <v>26128.51</v>
+      </c>
+      <c r="L414" t="n">
+        <v>25765.8</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24624.66</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="O414" t="n">
+        <v>36</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
         <v>146</v>
       </c>
     </row>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31823,6 +31823,79 @@
         <v>146</v>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>26970.95</v>
+      </c>
+      <c r="D415" t="n">
+        <v>27122.76</v>
+      </c>
+      <c r="E415" t="n">
+        <v>26876.27</v>
+      </c>
+      <c r="F415" t="n">
+        <v>27091.33</v>
+      </c>
+      <c r="G415" t="n">
+        <v>4254202000</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J415" t="n">
+        <v>26484.59</v>
+      </c>
+      <c r="K415" t="n">
+        <v>26146.03</v>
+      </c>
+      <c r="L415" t="n">
+        <v>25808.26</v>
+      </c>
+      <c r="M415" t="n">
+        <v>24642.38</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>60.58</v>
+      </c>
+      <c r="O415" t="n">
+        <v>38</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31844,34 +31844,34 @@
         <v>26876.27</v>
       </c>
       <c r="F415" t="n">
-        <v>27091.33</v>
+        <v>27068.72</v>
       </c>
       <c r="G415" t="n">
-        <v>4254202000</v>
+        <v>6299972000</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="I415" t="n">
         <v>2.6</v>
       </c>
       <c r="J415" t="n">
-        <v>26484.59</v>
+        <v>26483.46</v>
       </c>
       <c r="K415" t="n">
-        <v>26146.03</v>
+        <v>26145.66</v>
       </c>
       <c r="L415" t="n">
-        <v>25808.26</v>
+        <v>25808.07</v>
       </c>
       <c r="M415" t="n">
-        <v>24642.38</v>
+        <v>24642.27</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>60.58</v>
+        <v>60.26</v>
       </c>
       <c r="O415" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31885,16 +31885,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>144.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31768,7 +31768,7 @@
         <v>27068.72</v>
       </c>
       <c r="G414" t="n">
-        <v>6299972000</v>
+        <v>7275260000</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>0.48</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1369,7 +1369,7 @@
         <v>2.6</v>
       </c>
       <c r="J12" t="n">
-        <v>19729.46</v>
+        <v>19729.47</v>
       </c>
       <c r="K12" t="n">
         <v>19630.93</v>
@@ -4161,7 +4161,7 @@
         <v>2.6</v>
       </c>
       <c r="J48" t="n">
-        <v>17132.26</v>
+        <v>17132.25</v>
       </c>
       <c r="K48" t="n">
         <v>18472.28</v>
@@ -7177,7 +7177,7 @@
         <v>2.6</v>
       </c>
       <c r="J88" t="n">
-        <v>19240.31</v>
+        <v>19240.32</v>
       </c>
       <c r="K88" t="n">
         <v>17918.44</v>
@@ -31668,6 +31668,79 @@
       <c r="W412" s="2" t="n">
         <v>144.9</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>26935.76</v>
+      </c>
+      <c r="D413" t="n">
+        <v>26976.59</v>
+      </c>
+      <c r="E413" t="n">
+        <v>26709.69</v>
+      </c>
+      <c r="F413" t="n">
+        <v>26764.69</v>
+      </c>
+      <c r="G413" t="n">
+        <v>2178969000</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J413" t="n">
+        <v>26501.57</v>
+      </c>
+      <c r="K413" t="n">
+        <v>26161.19</v>
+      </c>
+      <c r="L413" t="n">
+        <v>25847.63</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24658.21</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>55.81</v>
+      </c>
+      <c r="O413" t="n">
+        <v>34</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -1369,7 +1369,7 @@
         <v>2.6</v>
       </c>
       <c r="J12" t="n">
-        <v>19729.47</v>
+        <v>19729.46</v>
       </c>
       <c r="K12" t="n">
         <v>19630.93</v>
@@ -4161,7 +4161,7 @@
         <v>2.6</v>
       </c>
       <c r="J48" t="n">
-        <v>17132.25</v>
+        <v>17132.26</v>
       </c>
       <c r="K48" t="n">
         <v>18472.28</v>
@@ -7177,7 +7177,7 @@
         <v>2.6</v>
       </c>
       <c r="J88" t="n">
-        <v>19240.32</v>
+        <v>19240.31</v>
       </c>
       <c r="K88" t="n">
         <v>17918.44</v>
@@ -31684,37 +31684,37 @@
         <v>26935.76</v>
       </c>
       <c r="D413" t="n">
-        <v>26976.59</v>
+        <v>26990.02</v>
       </c>
       <c r="E413" t="n">
         <v>26709.69</v>
       </c>
       <c r="F413" t="n">
-        <v>26764.69</v>
+        <v>26820.38</v>
       </c>
       <c r="G413" t="n">
-        <v>2178969000</v>
+        <v>6158504000</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>-1.12</v>
+        <v>-0.92</v>
       </c>
       <c r="I413" t="n">
         <v>2.6</v>
       </c>
       <c r="J413" t="n">
-        <v>26501.57</v>
+        <v>26504.36</v>
       </c>
       <c r="K413" t="n">
-        <v>26161.19</v>
+        <v>26162.12</v>
       </c>
       <c r="L413" t="n">
-        <v>25847.63</v>
+        <v>25848.09</v>
       </c>
       <c r="M413" t="n">
-        <v>24658.21</v>
+        <v>24658.49</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>55.81</v>
+        <v>56.88</v>
       </c>
       <c r="O413" t="n">
         <v>34</v>
@@ -31731,16 +31731,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>9.5</v>
+        <v>11.3</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31618,7 +31618,7 @@
         <v>26820.38</v>
       </c>
       <c r="G412" t="n">
-        <v>6158504000</v>
+        <v>7030730000</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-0.92</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31669,6 +31669,79 @@
         <v>146.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>26908.76</v>
+      </c>
+      <c r="D413" t="n">
+        <v>26919.72</v>
+      </c>
+      <c r="E413" t="n">
+        <v>26757</v>
+      </c>
+      <c r="F413" t="n">
+        <v>26771.52</v>
+      </c>
+      <c r="G413" t="n">
+        <v>2585805000</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J413" t="n">
+        <v>26524.39</v>
+      </c>
+      <c r="K413" t="n">
+        <v>26172.96</v>
+      </c>
+      <c r="L413" t="n">
+        <v>25882.56</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24674.08</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>59.31</v>
+      </c>
+      <c r="O413" t="n">
+        <v>33</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -1294,7 +1294,7 @@
         <v>2.6</v>
       </c>
       <c r="J11" t="n">
-        <v>19729.46</v>
+        <v>19729.47</v>
       </c>
       <c r="K11" t="n">
         <v>19630.93</v>
@@ -4086,7 +4086,7 @@
         <v>2.6</v>
       </c>
       <c r="J47" t="n">
-        <v>17132.26</v>
+        <v>17132.25</v>
       </c>
       <c r="K47" t="n">
         <v>18472.28</v>
@@ -31687,37 +31687,37 @@
         <v>26919.72</v>
       </c>
       <c r="E413" t="n">
-        <v>26757</v>
+        <v>26717.95</v>
       </c>
       <c r="F413" t="n">
-        <v>26771.52</v>
+        <v>26797.54</v>
       </c>
       <c r="G413" t="n">
-        <v>2585805000</v>
+        <v>6118564000</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-0.18</v>
+        <v>-0.09</v>
       </c>
       <c r="I413" t="n">
         <v>2.6</v>
       </c>
       <c r="J413" t="n">
-        <v>26524.39</v>
+        <v>26525.69</v>
       </c>
       <c r="K413" t="n">
-        <v>26172.96</v>
+        <v>26173.39</v>
       </c>
       <c r="L413" t="n">
-        <v>25882.56</v>
+        <v>25882.78</v>
       </c>
       <c r="M413" t="n">
-        <v>24674.08</v>
+        <v>24674.21</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>59.31</v>
+        <v>59.87</v>
       </c>
       <c r="O413" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31731,13 +31731,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31614,7 +31614,7 @@
         <v>26797.54</v>
       </c>
       <c r="G412" t="n">
-        <v>6276261000</v>
+        <v>7097250000</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>-0.09</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31638,7 +31638,7 @@
         <v>59.87</v>
       </c>
       <c r="O412" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31665,6 +31665,79 @@
         <v>144.6</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>26892.8</v>
+      </c>
+      <c r="D413" t="n">
+        <v>27108.2</v>
+      </c>
+      <c r="E413" t="n">
+        <v>26885.35</v>
+      </c>
+      <c r="F413" t="n">
+        <v>27011.11</v>
+      </c>
+      <c r="G413" t="n">
+        <v>5480495000</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J413" t="n">
+        <v>26571.26</v>
+      </c>
+      <c r="K413" t="n">
+        <v>26193.26</v>
+      </c>
+      <c r="L413" t="n">
+        <v>25917.68</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24691.29</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>66.61</v>
+      </c>
+      <c r="O413" t="n">
+        <v>33</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -1215,7 +1215,7 @@
         <v>2.6</v>
       </c>
       <c r="J10" t="n">
-        <v>19729.47</v>
+        <v>19729.46</v>
       </c>
       <c r="K10" t="n">
         <v>19630.93</v>
@@ -4007,7 +4007,7 @@
         <v>2.6</v>
       </c>
       <c r="J46" t="n">
-        <v>17132.25</v>
+        <v>17132.26</v>
       </c>
       <c r="K46" t="n">
         <v>18472.28</v>
@@ -31683,37 +31683,37 @@
         <v>27108.2</v>
       </c>
       <c r="E413" t="n">
-        <v>26885.35</v>
+        <v>26861.06</v>
       </c>
       <c r="F413" t="n">
-        <v>27011.11</v>
+        <v>26861.06</v>
       </c>
       <c r="G413" t="n">
-        <v>5480495000</v>
+        <v>7822640000</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>0.8</v>
+        <v>0.24</v>
       </c>
       <c r="I413" t="n">
         <v>2.6</v>
       </c>
       <c r="J413" t="n">
-        <v>26571.26</v>
+        <v>26563.76</v>
       </c>
       <c r="K413" t="n">
-        <v>26193.26</v>
+        <v>26190.76</v>
       </c>
       <c r="L413" t="n">
-        <v>25917.68</v>
+        <v>25916.43</v>
       </c>
       <c r="M413" t="n">
-        <v>24691.29</v>
+        <v>24690.54</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>66.61</v>
+        <v>64.72</v>
       </c>
       <c r="O413" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31727,16 +31727,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>141.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31689,7 +31689,7 @@
         <v>26861.06</v>
       </c>
       <c r="G413" t="n">
-        <v>7822640000</v>
+        <v>8300260000</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>0.24</v>
@@ -31713,7 +31713,7 @@
         <v>64.72</v>
       </c>
       <c r="O413" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31740,6 +31740,79 @@
         <v>141.9</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>26992.31</v>
+      </c>
+      <c r="D414" t="n">
+        <v>27014.47</v>
+      </c>
+      <c r="E414" t="n">
+        <v>26733.89</v>
+      </c>
+      <c r="F414" t="n">
+        <v>26815.81</v>
+      </c>
+      <c r="G414" t="n">
+        <v>2806370000</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J414" t="n">
+        <v>26593.66</v>
+      </c>
+      <c r="K414" t="n">
+        <v>26206.52</v>
+      </c>
+      <c r="L414" t="n">
+        <v>25949.04</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24708.65</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>59.89</v>
+      </c>
+      <c r="O414" t="n">
+        <v>27</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31761,34 +31761,34 @@
         <v>26733.89</v>
       </c>
       <c r="F414" t="n">
-        <v>26815.81</v>
+        <v>26871.6</v>
       </c>
       <c r="G414" t="n">
-        <v>2806370000</v>
-      </c>
-      <c r="H414" s="3" t="n">
-        <v>-0.17</v>
+        <v>6226957000</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.04</v>
       </c>
       <c r="I414" t="n">
         <v>2.6</v>
       </c>
       <c r="J414" t="n">
-        <v>26593.66</v>
+        <v>26596.44</v>
       </c>
       <c r="K414" t="n">
-        <v>26206.52</v>
+        <v>26207.45</v>
       </c>
       <c r="L414" t="n">
-        <v>25949.04</v>
+        <v>25949.51</v>
       </c>
       <c r="M414" t="n">
-        <v>24708.65</v>
+        <v>24708.92</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>59.89</v>
+        <v>61.19</v>
       </c>
       <c r="O414" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31797,21 +31797,23 @@
       </c>
       <c r="Q414" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>BUY STOP</t>
         </is>
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.3</v>
+        <v>16.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>142.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31764,7 +31764,7 @@
         <v>26871.6</v>
       </c>
       <c r="G414" t="n">
-        <v>6226957000</v>
+        <v>7329610000</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>0.04</v>
@@ -31788,7 +31788,7 @@
         <v>61.19</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31788,7 +31788,7 @@
         <v>61.19</v>
       </c>
       <c r="O414" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31814,6 +31814,79 @@
       <c r="W414" s="2" t="n">
         <v>142.8</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>27216.91</v>
+      </c>
+      <c r="D415" t="n">
+        <v>27353.68</v>
+      </c>
+      <c r="E415" t="n">
+        <v>27112.24</v>
+      </c>
+      <c r="F415" t="n">
+        <v>27156.51</v>
+      </c>
+      <c r="G415" t="n">
+        <v>3100087000</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J415" t="n">
+        <v>26625.07</v>
+      </c>
+      <c r="K415" t="n">
+        <v>26223.27</v>
+      </c>
+      <c r="L415" t="n">
+        <v>25982.61</v>
+      </c>
+      <c r="M415" t="n">
+        <v>24729.42</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>69.06</v>
+      </c>
+      <c r="O415" t="n">
+        <v>31</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31836,31 +31836,31 @@
         <v>27112.24</v>
       </c>
       <c r="F415" t="n">
-        <v>27156.51</v>
+        <v>27190.86</v>
       </c>
       <c r="G415" t="n">
-        <v>3100087000</v>
+        <v>6784922000</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="I415" t="n">
         <v>2.6</v>
       </c>
       <c r="J415" t="n">
-        <v>26625.07</v>
+        <v>26626.78</v>
       </c>
       <c r="K415" t="n">
-        <v>26223.27</v>
+        <v>26223.84</v>
       </c>
       <c r="L415" t="n">
-        <v>25982.61</v>
+        <v>25982.9</v>
       </c>
       <c r="M415" t="n">
-        <v>24729.42</v>
+        <v>24729.59</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>69.06</v>
+        <v>69.47</v>
       </c>
       <c r="O415" t="n">
         <v>31</v>
@@ -31877,13 +31877,13 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31764,7 +31764,7 @@
         <v>27190.86</v>
       </c>
       <c r="G414" t="n">
-        <v>6857506000</v>
+        <v>7954430000</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>1.19</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31634,7 +31634,7 @@
         <v>69.47</v>
       </c>
       <c r="O412" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -19700,7 +19700,7 @@
         <v>22966.21</v>
       </c>
       <c r="M254" t="n">
-        <v>21804.64</v>
+        <v>21804.65</v>
       </c>
       <c r="N254" s="1" t="n">
         <v>29.62</v>
@@ -31634,7 +31634,7 @@
         <v>69.47</v>
       </c>
       <c r="O412" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31660,6 +31660,79 @@
       <c r="W412" s="2" t="n">
         <v>144.9</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>27225.93</v>
+      </c>
+      <c r="D413" t="n">
+        <v>27478.17</v>
+      </c>
+      <c r="E413" t="n">
+        <v>27223.49</v>
+      </c>
+      <c r="F413" t="n">
+        <v>27448.3</v>
+      </c>
+      <c r="G413" t="n">
+        <v>4047251000</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J413" t="n">
+        <v>26673.85</v>
+      </c>
+      <c r="K413" t="n">
+        <v>26243.29</v>
+      </c>
+      <c r="L413" t="n">
+        <v>26014.64</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24751.28</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>77.86</v>
+      </c>
+      <c r="O413" t="n">
+        <v>44</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31610,7 +31610,7 @@
         <v>27477.31</v>
       </c>
       <c r="G412" t="n">
-        <v>7042231000</v>
+        <v>7828480000</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>1.05</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31634,7 +31634,7 @@
         <v>78.11</v>
       </c>
       <c r="O412" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31660,6 +31660,79 @@
       <c r="W412" s="2" t="n">
         <v>143</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>27641.17</v>
+      </c>
+      <c r="D413" t="n">
+        <v>27704.12</v>
+      </c>
+      <c r="E413" t="n">
+        <v>27613.54</v>
+      </c>
+      <c r="F413" t="n">
+        <v>27693.27</v>
+      </c>
+      <c r="G413" t="n">
+        <v>2837762000</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J413" t="n">
+        <v>26738.89</v>
+      </c>
+      <c r="K413" t="n">
+        <v>26274.11</v>
+      </c>
+      <c r="L413" t="n">
+        <v>26045.53</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24776.42</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>79.84</v>
+      </c>
+      <c r="O413" t="n">
+        <v>48</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -6719,7 +6719,7 @@
         <v>2.6</v>
       </c>
       <c r="J82" t="n">
-        <v>19240.32</v>
+        <v>19240.31</v>
       </c>
       <c r="K82" t="n">
         <v>17918.44</v>
@@ -31676,37 +31676,37 @@
         <v>27641.17</v>
       </c>
       <c r="D413" t="n">
-        <v>27704.12</v>
+        <v>27722.75</v>
       </c>
       <c r="E413" t="n">
-        <v>27613.54</v>
+        <v>27592.56</v>
       </c>
       <c r="F413" t="n">
-        <v>27693.27</v>
+        <v>27599.79</v>
       </c>
       <c r="G413" t="n">
-        <v>2837762000</v>
+        <v>6787865000</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>0.79</v>
+        <v>0.45</v>
       </c>
       <c r="I413" t="n">
         <v>2.6</v>
       </c>
       <c r="J413" t="n">
-        <v>26738.89</v>
+        <v>26734.22</v>
       </c>
       <c r="K413" t="n">
-        <v>26274.11</v>
+        <v>26272.55</v>
       </c>
       <c r="L413" t="n">
-        <v>26045.53</v>
+        <v>26044.75</v>
       </c>
       <c r="M413" t="n">
-        <v>24776.42</v>
+        <v>24775.95</v>
       </c>
       <c r="N413" s="3" t="n">
-        <v>79.84</v>
+        <v>79.16</v>
       </c>
       <c r="O413" t="n">
         <v>48</v>
@@ -31723,13 +31723,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31607,10 +31607,10 @@
         <v>27592.56</v>
       </c>
       <c r="F412" t="n">
-        <v>27599.89</v>
+        <v>27599.79</v>
       </c>
       <c r="G412" t="n">
-        <v>7658736000</v>
+        <v>8451470000</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>0.45</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31661,6 +31661,79 @@
         <v>141.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>27430.54</v>
+      </c>
+      <c r="D413" t="n">
+        <v>27458.28</v>
+      </c>
+      <c r="E413" t="n">
+        <v>27341.31</v>
+      </c>
+      <c r="F413" t="n">
+        <v>27411.21</v>
+      </c>
+      <c r="G413" t="n">
+        <v>1819844000</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="I413" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J413" t="n">
+        <v>26792.11</v>
+      </c>
+      <c r="K413" t="n">
+        <v>26294.29</v>
+      </c>
+      <c r="L413" t="n">
+        <v>26072.32</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24797.98</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>69.63</v>
+      </c>
+      <c r="O413" t="n">
+        <v>42</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31472,7 +31472,7 @@
         <v>26626.78</v>
       </c>
       <c r="K410" t="n">
-        <v>26223.84</v>
+        <v>26223.85</v>
       </c>
       <c r="L410" t="n">
         <v>25982.9</v>
@@ -31676,40 +31676,40 @@
         <v>27430.54</v>
       </c>
       <c r="D413" t="n">
-        <v>27458.28</v>
+        <v>27547.2</v>
       </c>
       <c r="E413" t="n">
         <v>27341.31</v>
       </c>
       <c r="F413" t="n">
-        <v>27411.21</v>
+        <v>27538.69</v>
       </c>
       <c r="G413" t="n">
-        <v>1819844000</v>
+        <v>6354730000</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.22</v>
       </c>
       <c r="I413" t="n">
         <v>2.6</v>
       </c>
       <c r="J413" t="n">
-        <v>26792.11</v>
+        <v>26798.49</v>
       </c>
       <c r="K413" t="n">
-        <v>26294.29</v>
+        <v>26296.41</v>
       </c>
       <c r="L413" t="n">
-        <v>26072.32</v>
+        <v>26073.38</v>
       </c>
       <c r="M413" t="n">
-        <v>24797.98</v>
-      </c>
-      <c r="N413" s="2" t="n">
-        <v>69.63</v>
+        <v>24798.61</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>73.33</v>
       </c>
       <c r="O413" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31723,13 +31723,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31685,7 +31685,7 @@
         <v>27538.69</v>
       </c>
       <c r="G413" t="n">
-        <v>6354730000</v>
+        <v>6457816000</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>-0.22</v>
@@ -31732,7 +31732,9 @@
         <v>9.300000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>141.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31685,7 +31685,7 @@
         <v>27538.69</v>
       </c>
       <c r="G413" t="n">
-        <v>6457816000</v>
+        <v>7315500000</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>-0.22</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31709,7 +31709,7 @@
         <v>73.33</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31735,6 +31735,79 @@
       <c r="W413" s="2" t="n">
         <v>141.8</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>27416.03</v>
+      </c>
+      <c r="D414" t="n">
+        <v>27491.89</v>
+      </c>
+      <c r="E414" t="n">
+        <v>27352.51</v>
+      </c>
+      <c r="F414" t="n">
+        <v>27394.35</v>
+      </c>
+      <c r="G414" t="n">
+        <v>2881763000</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J414" t="n">
+        <v>26864.12</v>
+      </c>
+      <c r="K414" t="n">
+        <v>26315.16</v>
+      </c>
+      <c r="L414" t="n">
+        <v>26097.76</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24819.05</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>67.84999999999999</v>
+      </c>
+      <c r="O414" t="n">
+        <v>41</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31754,37 +31754,37 @@
         <v>27491.89</v>
       </c>
       <c r="E414" t="n">
-        <v>27352.51</v>
+        <v>27066.76</v>
       </c>
       <c r="F414" t="n">
-        <v>27394.35</v>
+        <v>27193.34</v>
       </c>
       <c r="G414" t="n">
-        <v>2881763000</v>
+        <v>7798570000</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>-0.52</v>
+        <v>-1.25</v>
       </c>
       <c r="I414" t="n">
         <v>2.6</v>
       </c>
       <c r="J414" t="n">
-        <v>26864.12</v>
+        <v>26854.07</v>
       </c>
       <c r="K414" t="n">
-        <v>26315.16</v>
+        <v>26311.81</v>
       </c>
       <c r="L414" t="n">
-        <v>26097.76</v>
+        <v>26096.09</v>
       </c>
       <c r="M414" t="n">
-        <v>24819.05</v>
+        <v>24818.04</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>67.84999999999999</v>
+        <v>62.69</v>
       </c>
       <c r="O414" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,13 +31798,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.3</v>
+        <v>5.23</v>
       </c>
       <c r="T414" s="2" t="n">
         <v>15.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31760,7 +31760,7 @@
         <v>27193.34</v>
       </c>
       <c r="G414" t="n">
-        <v>7798570000</v>
+        <v>7830408000</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>-1.25</v>
@@ -31807,7 +31807,9 @@
         <v>10.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31760,7 +31760,7 @@
         <v>27193.34</v>
       </c>
       <c r="G414" t="n">
-        <v>7830408000</v>
+        <v>8820120000</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>-1.25</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31784,7 +31784,7 @@
         <v>62.69</v>
       </c>
       <c r="O414" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31810,6 +31810,79 @@
       <c r="W414" s="2" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>27342.27</v>
+      </c>
+      <c r="D415" t="n">
+        <v>27375.55</v>
+      </c>
+      <c r="E415" t="n">
+        <v>27254.03</v>
+      </c>
+      <c r="F415" t="n">
+        <v>27344.25</v>
+      </c>
+      <c r="G415" t="n">
+        <v>2782480000</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J415" t="n">
+        <v>26904.63</v>
+      </c>
+      <c r="K415" t="n">
+        <v>26336.18</v>
+      </c>
+      <c r="L415" t="n">
+        <v>26120.59</v>
+      </c>
+      <c r="M415" t="n">
+        <v>24837.62</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>55.06</v>
+      </c>
+      <c r="O415" t="n">
+        <v>44</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31826,40 +31826,40 @@
         <v>27342.27</v>
       </c>
       <c r="D415" t="n">
-        <v>27375.55</v>
+        <v>27395.41</v>
       </c>
       <c r="E415" t="n">
         <v>27254.03</v>
       </c>
       <c r="F415" t="n">
-        <v>27344.25</v>
+        <v>27366.17</v>
       </c>
       <c r="G415" t="n">
-        <v>2782480000</v>
+        <v>6036875000</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="I415" t="n">
         <v>2.6</v>
       </c>
       <c r="J415" t="n">
-        <v>26904.63</v>
+        <v>26905.72</v>
       </c>
       <c r="K415" t="n">
-        <v>26336.18</v>
+        <v>26336.55</v>
       </c>
       <c r="L415" t="n">
-        <v>26120.59</v>
+        <v>26120.77</v>
       </c>
       <c r="M415" t="n">
-        <v>24837.62</v>
+        <v>24837.73</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>55.06</v>
+        <v>55.51</v>
       </c>
       <c r="O415" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31873,13 +31873,13 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>27366.17</v>
       </c>
       <c r="G415" t="n">
-        <v>6036875000</v>
+        <v>6095485000</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>0.64</v>
@@ -31882,7 +31882,9 @@
         <v>9.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>154.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>27366.17</v>
       </c>
       <c r="G415" t="n">
-        <v>6095485000</v>
+        <v>6845310000</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>0.64</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6494,7 +6494,7 @@
         <v>2.6</v>
       </c>
       <c r="J79" t="n">
-        <v>19240.31</v>
+        <v>19240.32</v>
       </c>
       <c r="K79" t="n">
         <v>17918.44</v>
@@ -31322,7 +31322,7 @@
         <v>26626.78</v>
       </c>
       <c r="K408" t="n">
-        <v>26223.85</v>
+        <v>26223.84</v>
       </c>
       <c r="L408" t="n">
         <v>25982.9</v>
@@ -31709,11 +31709,11 @@
         <v>55.51</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -31734,6 +31734,81 @@
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
         <v>154.3</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>27352.51</v>
+      </c>
+      <c r="D414" t="n">
+        <v>27376.66</v>
+      </c>
+      <c r="E414" t="n">
+        <v>27219.42</v>
+      </c>
+      <c r="F414" t="n">
+        <v>27245.9</v>
+      </c>
+      <c r="G414" t="n">
+        <v>5794275000</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J414" t="n">
+        <v>26958.7</v>
+      </c>
+      <c r="K414" t="n">
+        <v>26365.31</v>
+      </c>
+      <c r="L414" t="n">
+        <v>26145.65</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24856.15</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="O414" t="n">
+        <v>46</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>155.1</v>
       </c>
     </row>
   </sheetData>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31685,7 +31685,7 @@
         <v>27245.9</v>
       </c>
       <c r="G413" t="n">
-        <v>5794275000</v>
+        <v>6285170000</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-0.44</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31736,6 +31736,79 @@
         <v>155.1</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>27138.73</v>
+      </c>
+      <c r="D414" t="n">
+        <v>27277.88</v>
+      </c>
+      <c r="E414" t="n">
+        <v>27116.08</v>
+      </c>
+      <c r="F414" t="n">
+        <v>27170.34</v>
+      </c>
+      <c r="G414" t="n">
+        <v>3904737000</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J414" t="n">
+        <v>27018.14</v>
+      </c>
+      <c r="K414" t="n">
+        <v>26393.02</v>
+      </c>
+      <c r="L414" t="n">
+        <v>26166.59</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24873.94</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>55.91</v>
+      </c>
+      <c r="O414" t="n">
+        <v>44</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31757,34 +31757,34 @@
         <v>27116.08</v>
       </c>
       <c r="F414" t="n">
-        <v>27170.34</v>
+        <v>27204.38</v>
       </c>
       <c r="G414" t="n">
-        <v>3904737000</v>
+        <v>6273913000</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-0.28</v>
+        <v>-0.15</v>
       </c>
       <c r="I414" t="n">
         <v>2.6</v>
       </c>
       <c r="J414" t="n">
-        <v>27018.14</v>
+        <v>27019.84</v>
       </c>
       <c r="K414" t="n">
-        <v>26393.02</v>
+        <v>26393.58</v>
       </c>
       <c r="L414" t="n">
-        <v>26166.59</v>
+        <v>26166.88</v>
       </c>
       <c r="M414" t="n">
-        <v>24873.94</v>
+        <v>24874.11</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>55.91</v>
+        <v>56.89</v>
       </c>
       <c r="O414" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31800,12 +31800,8 @@
       <c r="S414" t="n">
         <v>5.22</v>
       </c>
-      <c r="T414" s="2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="U414" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="T414" s="2" t="inlineStr"/>
+      <c r="U414" s="2" t="inlineStr"/>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31709,7 +31709,7 @@
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31705,11 +31705,11 @@
         <v>56.89</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -31731,6 +31731,83 @@
       <c r="W413" s="2" t="n">
         <v>154.7</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>27031.64</v>
+      </c>
+      <c r="D414" t="n">
+        <v>27134.29</v>
+      </c>
+      <c r="E414" t="n">
+        <v>26915.51</v>
+      </c>
+      <c r="F414" t="n">
+        <v>26966.48</v>
+      </c>
+      <c r="G414" t="n">
+        <v>2525092000</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J414" t="n">
+        <v>27069.24</v>
+      </c>
+      <c r="K414" t="n">
+        <v>26412.4</v>
+      </c>
+      <c r="L414" t="n">
+        <v>26187.94</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24890.97</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="O414" t="n">
+        <v>37</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31750,37 +31750,37 @@
         <v>27134.29</v>
       </c>
       <c r="E414" t="n">
-        <v>26915.51</v>
+        <v>26602.12</v>
       </c>
       <c r="F414" t="n">
-        <v>26966.48</v>
+        <v>26634.23</v>
       </c>
       <c r="G414" t="n">
-        <v>2525092000</v>
+        <v>5528953000</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-0.87</v>
+        <v>-2.1</v>
       </c>
       <c r="I414" t="n">
         <v>2.6</v>
       </c>
       <c r="J414" t="n">
-        <v>27069.24</v>
+        <v>27052.63</v>
       </c>
       <c r="K414" t="n">
-        <v>26412.4</v>
+        <v>26406.87</v>
       </c>
       <c r="L414" t="n">
-        <v>26187.94</v>
+        <v>26185.17</v>
       </c>
       <c r="M414" t="n">
-        <v>24890.97</v>
+        <v>24889.31</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>50.62</v>
+        <v>43.93</v>
       </c>
       <c r="O414" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,13 +31798,13 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>15.7</v>
+        <v>17.2</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>8.1</v>
+        <v>14</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -3324,7 +3324,7 @@
         <v>2.6</v>
       </c>
       <c r="J37" t="n">
-        <v>17132.25</v>
+        <v>17132.26</v>
       </c>
       <c r="K37" t="n">
         <v>18472.28</v>
@@ -6340,7 +6340,7 @@
         <v>2.6</v>
       </c>
       <c r="J77" t="n">
-        <v>19240.32</v>
+        <v>19240.31</v>
       </c>
       <c r="K77" t="n">
         <v>17918.44</v>
@@ -31753,34 +31753,34 @@
         <v>26602.12</v>
       </c>
       <c r="F414" t="n">
-        <v>26634.23</v>
+        <v>26692.87</v>
       </c>
       <c r="G414" t="n">
-        <v>5528953000</v>
+        <v>7640476000</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-2.1</v>
+        <v>-1.88</v>
       </c>
       <c r="I414" t="n">
         <v>2.6</v>
       </c>
       <c r="J414" t="n">
-        <v>27052.63</v>
+        <v>27055.56</v>
       </c>
       <c r="K414" t="n">
-        <v>26406.87</v>
+        <v>26407.84</v>
       </c>
       <c r="L414" t="n">
-        <v>26185.17</v>
+        <v>26185.66</v>
       </c>
       <c r="M414" t="n">
-        <v>24889.31</v>
+        <v>24889.6</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>43.93</v>
+        <v>44.98</v>
       </c>
       <c r="O414" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31801,13 +31801,15 @@
         <v>5.19</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.2</v>
+        <v>16.9</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>157.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31756,7 +31756,7 @@
         <v>26692.87</v>
       </c>
       <c r="G414" t="n">
-        <v>7640476000</v>
+        <v>8568280000</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-1.88</v>
@@ -31780,7 +31780,7 @@
         <v>44.98</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31780,7 +31780,7 @@
         <v>44.98</v>
       </c>
       <c r="O414" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31810,6 +31810,79 @@
       <c r="W414" s="1" t="n">
         <v>157.3</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>26380.77</v>
+      </c>
+      <c r="D415" t="n">
+        <v>26478.87</v>
+      </c>
+      <c r="E415" t="n">
+        <v>26308.85</v>
+      </c>
+      <c r="F415" t="n">
+        <v>26469.09</v>
+      </c>
+      <c r="G415" t="n">
+        <v>3198225000</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J415" t="n">
+        <v>27058.1</v>
+      </c>
+      <c r="K415" t="n">
+        <v>26420.81</v>
+      </c>
+      <c r="L415" t="n">
+        <v>26199.27</v>
+      </c>
+      <c r="M415" t="n">
+        <v>24904.58</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="O415" t="n">
+        <v>24</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31826,60 +31826,60 @@
         <v>26380.77</v>
       </c>
       <c r="D415" t="n">
-        <v>26478.87</v>
+        <v>26697.96</v>
       </c>
       <c r="E415" t="n">
         <v>26308.85</v>
       </c>
       <c r="F415" t="n">
-        <v>26469.09</v>
+        <v>26626.61</v>
       </c>
       <c r="G415" t="n">
-        <v>3198225000</v>
+        <v>7401741000</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-0.84</v>
+        <v>-0.25</v>
       </c>
       <c r="I415" t="n">
         <v>2.6</v>
       </c>
       <c r="J415" t="n">
-        <v>27058.1</v>
+        <v>27065.98</v>
       </c>
       <c r="K415" t="n">
-        <v>26420.81</v>
+        <v>26423.44</v>
       </c>
       <c r="L415" t="n">
-        <v>26199.27</v>
+        <v>26200.58</v>
       </c>
       <c r="M415" t="n">
-        <v>24904.58</v>
+        <v>24905.37</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>38.24</v>
+        <v>40.76</v>
       </c>
       <c r="O415" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>extreme fear</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>3x BUY</t>
+          <t>2x BUY</t>
         </is>
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.05</v>
+        <v>5.08</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>17.6</v>
+        <v>16.8</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.7</v>
+        <v>12.5</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31826,40 +31826,40 @@
         <v>26380.77</v>
       </c>
       <c r="D415" t="n">
-        <v>26697.96</v>
+        <v>26754.02</v>
       </c>
       <c r="E415" t="n">
         <v>26308.85</v>
       </c>
       <c r="F415" t="n">
-        <v>26626.61</v>
+        <v>26713.03</v>
       </c>
       <c r="G415" t="n">
-        <v>7401741000</v>
-      </c>
-      <c r="H415" s="1" t="n">
-        <v>-0.25</v>
+        <v>9708091000</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>0.08</v>
       </c>
       <c r="I415" t="n">
         <v>2.6</v>
       </c>
       <c r="J415" t="n">
-        <v>27065.98</v>
+        <v>27070.3</v>
       </c>
       <c r="K415" t="n">
-        <v>26423.44</v>
+        <v>26424.88</v>
       </c>
       <c r="L415" t="n">
-        <v>26200.58</v>
+        <v>26201.3</v>
       </c>
       <c r="M415" t="n">
-        <v>24905.37</v>
+        <v>24905.8</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>40.76</v>
+        <v>42.42</v>
       </c>
       <c r="O415" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31873,16 +31873,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="1" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>26713.03</v>
       </c>
       <c r="G415" t="n">
-        <v>9708091000</v>
+        <v>10869960000</v>
       </c>
       <c r="H415" s="3" t="n">
         <v>0.08</v>
@@ -31859,7 +31859,7 @@
         <v>42.42</v>
       </c>
       <c r="O415" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31859,7 +31859,7 @@
         <v>42.42</v>
       </c>
       <c r="O415" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31859,7 +31859,7 @@
         <v>42.42</v>
       </c>
       <c r="O415" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31885,6 +31885,83 @@
       <c r="W415" s="1" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>26652.98</v>
+      </c>
+      <c r="D416" t="n">
+        <v>26674.66</v>
+      </c>
+      <c r="E416" t="n">
+        <v>26407.13</v>
+      </c>
+      <c r="F416" t="n">
+        <v>26432.65</v>
+      </c>
+      <c r="G416" t="n">
+        <v>3247769000</v>
+      </c>
+      <c r="H416" s="1" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="I416" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J416" t="n">
+        <v>27065.8</v>
+      </c>
+      <c r="K416" t="n">
+        <v>26446.46</v>
+      </c>
+      <c r="L416" t="n">
+        <v>26214.18</v>
+      </c>
+      <c r="M416" t="n">
+        <v>24920.87</v>
+      </c>
+      <c r="N416" s="2" t="n">
+        <v>41.85</v>
+      </c>
+      <c r="O416" t="n">
+        <v>30</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S416" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U416" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31904,61 +31904,61 @@
         <v>26674.66</v>
       </c>
       <c r="E416" t="n">
-        <v>26407.13</v>
+        <v>26023.1</v>
       </c>
       <c r="F416" t="n">
-        <v>26432.65</v>
+        <v>26140.24</v>
       </c>
       <c r="G416" t="n">
-        <v>3247769000</v>
+        <v>6302461000</v>
       </c>
       <c r="H416" s="1" t="n">
-        <v>-1.05</v>
+        <v>-2.14</v>
       </c>
       <c r="I416" t="n">
         <v>2.6</v>
       </c>
       <c r="J416" t="n">
-        <v>27065.8</v>
+        <v>27051.18</v>
       </c>
       <c r="K416" t="n">
-        <v>26446.46</v>
+        <v>26441.59</v>
       </c>
       <c r="L416" t="n">
-        <v>26214.18</v>
+        <v>26211.74</v>
       </c>
       <c r="M416" t="n">
-        <v>24920.87</v>
+        <v>24919.4</v>
       </c>
       <c r="N416" s="2" t="n">
-        <v>41.85</v>
+        <v>37.27</v>
       </c>
       <c r="O416" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>extreme fear</t>
         </is>
       </c>
       <c r="Q416" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>3x BUY</t>
         </is>
       </c>
       <c r="R416" t="inlineStr">
         <is>
-          <t>2nd: MA60, 50% cash, 5d</t>
+          <t>3rd: MA120, 50% cash, 5d</t>
         </is>
       </c>
       <c r="S416" t="n">
-        <v>5.09</v>
+        <v>5.1</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>15.9</v>
+        <v>21.3</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>8.1</v>
+        <v>22</v>
       </c>
       <c r="V416" t="inlineStr"/>
       <c r="W416" s="2" t="inlineStr"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31907,19 +31907,19 @@
         <v>26023.1</v>
       </c>
       <c r="F416" t="n">
-        <v>26140.24</v>
+        <v>26140.03</v>
       </c>
       <c r="G416" t="n">
-        <v>6302461000</v>
+        <v>8351719000</v>
       </c>
       <c r="H416" s="1" t="n">
-        <v>-2.14</v>
+        <v>-2.15</v>
       </c>
       <c r="I416" t="n">
         <v>2.6</v>
       </c>
       <c r="J416" t="n">
-        <v>27051.18</v>
+        <v>27051.17</v>
       </c>
       <c r="K416" t="n">
         <v>26441.59</v>
@@ -31931,7 +31931,7 @@
         <v>24919.4</v>
       </c>
       <c r="N416" s="2" t="n">
-        <v>37.27</v>
+        <v>37.26</v>
       </c>
       <c r="O416" t="n">
         <v>18</v>
@@ -31955,13 +31955,15 @@
         <v>5.1</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" s="2" t="inlineStr"/>
+      <c r="W416" s="1" t="n">
+        <v>168.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>26140.03</v>
       </c>
       <c r="G415" t="n">
-        <v>8351719000</v>
+        <v>9505000000</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-2.15</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31709,7 +31709,7 @@
         <v>37.26</v>
       </c>
       <c r="O413" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3099,7 +3099,7 @@
         <v>2.6</v>
       </c>
       <c r="J34" t="n">
-        <v>17132.26</v>
+        <v>17132.25</v>
       </c>
       <c r="K34" t="n">
         <v>18472.28</v>
@@ -30943,7 +30943,7 @@
         <v>26626.78</v>
       </c>
       <c r="K403" t="n">
-        <v>26223.84</v>
+        <v>26223.85</v>
       </c>
       <c r="L403" t="n">
         <v>25982.9</v>
@@ -31709,7 +31709,7 @@
         <v>37.26</v>
       </c>
       <c r="O413" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31739,6 +31739,79 @@
       <c r="W413" s="7" t="n">
         <v>168.6</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>26395.29</v>
+      </c>
+      <c r="D414" t="n">
+        <v>26613.15</v>
+      </c>
+      <c r="E414" t="n">
+        <v>26344.67</v>
+      </c>
+      <c r="F414" t="n">
+        <v>26477.97</v>
+      </c>
+      <c r="G414" t="n">
+        <v>4802747000</v>
+      </c>
+      <c r="H414" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J414" t="n">
+        <v>27018.97</v>
+      </c>
+      <c r="K414" t="n">
+        <v>26466.62</v>
+      </c>
+      <c r="L414" t="n">
+        <v>26226.86</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24935.58</v>
+      </c>
+      <c r="N414" s="6" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="O414" t="n">
+        <v>24</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>3x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="T414" s="6" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="U414" s="6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -6115,7 +6115,7 @@
         <v>2.6</v>
       </c>
       <c r="J74" t="n">
-        <v>19240.31</v>
+        <v>19240.32</v>
       </c>
       <c r="K74" t="n">
         <v>17918.44</v>
@@ -30943,7 +30943,7 @@
         <v>26626.78</v>
       </c>
       <c r="K403" t="n">
-        <v>26223.85</v>
+        <v>26223.84</v>
       </c>
       <c r="L403" t="n">
         <v>25982.9</v>
@@ -31761,34 +31761,34 @@
         <v>26344.67</v>
       </c>
       <c r="F414" t="n">
-        <v>26477.97</v>
+        <v>26430.89</v>
       </c>
       <c r="G414" t="n">
-        <v>4802747000</v>
+        <v>6737330000</v>
       </c>
       <c r="H414" s="5" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="I414" t="n">
         <v>2.6</v>
       </c>
       <c r="J414" t="n">
-        <v>27018.97</v>
+        <v>27016.61</v>
       </c>
       <c r="K414" t="n">
-        <v>26466.62</v>
+        <v>26465.84</v>
       </c>
       <c r="L414" t="n">
-        <v>26226.86</v>
+        <v>26226.47</v>
       </c>
       <c r="M414" t="n">
-        <v>24935.58</v>
+        <v>24935.35</v>
       </c>
       <c r="N414" s="6" t="n">
-        <v>44.65</v>
+        <v>43.76</v>
       </c>
       <c r="O414" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31802,16 +31802,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.13</v>
+        <v>5.14</v>
       </c>
       <c r="T414" s="6" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="U414" s="6" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="6" t="inlineStr"/>
+      <c r="W414" s="7" t="n">
+        <v>161.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31685,7 +31685,7 @@
         <v>26430.89</v>
       </c>
       <c r="G413" t="n">
-        <v>6737330000</v>
+        <v>7537660000</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>1.11</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31709,7 +31709,7 @@
         <v>43.76</v>
       </c>
       <c r="O413" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31735,6 +31735,79 @@
       <c r="W413" s="3" t="n">
         <v>161.9</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>26332.92</v>
+      </c>
+      <c r="D414" t="n">
+        <v>26601.71</v>
+      </c>
+      <c r="E414" t="n">
+        <v>26179.74</v>
+      </c>
+      <c r="F414" t="n">
+        <v>26563.52</v>
+      </c>
+      <c r="G414" t="n">
+        <v>2696975000</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J414" t="n">
+        <v>26982.57</v>
+      </c>
+      <c r="K414" t="n">
+        <v>26493.03</v>
+      </c>
+      <c r="L414" t="n">
+        <v>26242.22</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24951.99</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>45.05</v>
+      </c>
+      <c r="O414" t="n">
+        <v>28</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31757,34 +31757,34 @@
         <v>26179.74</v>
       </c>
       <c r="F414" t="n">
-        <v>26563.52</v>
+        <v>26452.54</v>
       </c>
       <c r="G414" t="n">
-        <v>2696975000</v>
+        <v>5021321000</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="I414" t="n">
         <v>2.6</v>
       </c>
       <c r="J414" t="n">
-        <v>26982.57</v>
+        <v>26977.03</v>
       </c>
       <c r="K414" t="n">
-        <v>26493.03</v>
+        <v>26491.18</v>
       </c>
       <c r="L414" t="n">
-        <v>26242.22</v>
+        <v>26241.29</v>
       </c>
       <c r="M414" t="n">
-        <v>24951.99</v>
+        <v>24951.43</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>45.05</v>
+        <v>42.95</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,13 +31798,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.08</v>
+        <v>5.12</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31757,31 +31757,31 @@
         <v>26179.74</v>
       </c>
       <c r="F414" t="n">
-        <v>26452.54</v>
+        <v>26424.82</v>
       </c>
       <c r="G414" t="n">
-        <v>5021321000</v>
-      </c>
-      <c r="H414" s="1" t="n">
-        <v>0.08</v>
+        <v>6999145000</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="I414" t="n">
         <v>2.6</v>
       </c>
       <c r="J414" t="n">
-        <v>26977.03</v>
+        <v>26975.64</v>
       </c>
       <c r="K414" t="n">
-        <v>26491.18</v>
+        <v>26490.72</v>
       </c>
       <c r="L414" t="n">
-        <v>26241.29</v>
+        <v>26241.06</v>
       </c>
       <c r="M414" t="n">
-        <v>24951.43</v>
+        <v>24951.29</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>42.95</v>
+        <v>42.43</v>
       </c>
       <c r="O414" t="n">
         <v>27</v>
@@ -31801,13 +31801,15 @@
         <v>5.12</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31679,13 +31679,13 @@
         <v>26601.71</v>
       </c>
       <c r="E413" t="n">
-        <v>26179.74</v>
+        <v>26179.73</v>
       </c>
       <c r="F413" t="n">
         <v>26424.82</v>
       </c>
       <c r="G413" t="n">
-        <v>6999145000</v>
+        <v>7660360000</v>
       </c>
       <c r="H413" s="5" t="n">
         <v>-0.02</v>
@@ -31709,7 +31709,7 @@
         <v>42.43</v>
       </c>
       <c r="O413" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31709,7 +31709,7 @@
         <v>42.43</v>
       </c>
       <c r="O413" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31735,6 +31735,77 @@
       <c r="W413" s="5" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>26601.73</v>
+      </c>
+      <c r="D414" t="n">
+        <v>26612.68</v>
+      </c>
+      <c r="E414" t="n">
+        <v>26538.11</v>
+      </c>
+      <c r="F414" t="n">
+        <v>26572.36</v>
+      </c>
+      <c r="G414" t="n">
+        <v>1092756000</v>
+      </c>
+      <c r="H414" s="6" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J414" t="n">
+        <v>26957.46</v>
+      </c>
+      <c r="K414" t="n">
+        <v>26518.97</v>
+      </c>
+      <c r="L414" t="n">
+        <v>26255.06</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24967.18</v>
+      </c>
+      <c r="N414" s="7" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="O414" t="n">
+        <v>29</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T414" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="U414" s="7" t="inlineStr"/>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31709,7 +31709,7 @@
         <v>42.43</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31751,40 +31751,40 @@
         <v>26601.73</v>
       </c>
       <c r="D414" t="n">
-        <v>26612.68</v>
+        <v>26778.9</v>
       </c>
       <c r="E414" t="n">
-        <v>26538.11</v>
+        <v>26507.07</v>
       </c>
       <c r="F414" t="n">
-        <v>26572.36</v>
+        <v>26760.56</v>
       </c>
       <c r="G414" t="n">
-        <v>1092756000</v>
+        <v>4669711000</v>
       </c>
       <c r="H414" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="I414" t="n">
         <v>2.6</v>
       </c>
       <c r="J414" t="n">
-        <v>26957.46</v>
+        <v>26966.87</v>
       </c>
       <c r="K414" t="n">
-        <v>26518.97</v>
+        <v>26522.11</v>
       </c>
       <c r="L414" t="n">
-        <v>26255.06</v>
+        <v>26256.63</v>
       </c>
       <c r="M414" t="n">
-        <v>24967.18</v>
+        <v>24968.12</v>
       </c>
       <c r="N414" s="7" t="n">
-        <v>45.04</v>
+        <v>48.27</v>
       </c>
       <c r="O414" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,12 +31798,14 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.1</v>
+        <v>5.11</v>
       </c>
       <c r="T414" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="U414" s="7" t="inlineStr"/>
+        <v>16.6</v>
+      </c>
+      <c r="U414" s="7" t="n">
+        <v>10</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="7" t="inlineStr"/>
     </row>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31757,34 +31757,34 @@
         <v>26507.07</v>
       </c>
       <c r="F414" t="n">
-        <v>26760.56</v>
+        <v>26702.86</v>
       </c>
       <c r="G414" t="n">
-        <v>4669711000</v>
+        <v>6898345000</v>
       </c>
       <c r="H414" s="6" t="n">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="I414" t="n">
         <v>2.6</v>
       </c>
       <c r="J414" t="n">
-        <v>26966.87</v>
+        <v>26963.98</v>
       </c>
       <c r="K414" t="n">
-        <v>26522.11</v>
+        <v>26521.15</v>
       </c>
       <c r="L414" t="n">
-        <v>26256.63</v>
+        <v>26256.15</v>
       </c>
       <c r="M414" t="n">
-        <v>24968.12</v>
+        <v>24967.83</v>
       </c>
       <c r="N414" s="7" t="n">
-        <v>48.27</v>
+        <v>47.32</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,16 +31798,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="T414" s="7" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="U414" s="7" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="7" t="inlineStr"/>
+      <c r="W414" s="7" t="n">
+        <v>150.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31760,7 +31760,7 @@
         <v>26702.86</v>
       </c>
       <c r="G414" t="n">
-        <v>6898345000</v>
+        <v>7818990000</v>
       </c>
       <c r="H414" s="6" t="n">
         <v>1.05</v>
@@ -31784,7 +31784,7 @@
         <v>47.32</v>
       </c>
       <c r="O414" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31784,7 +31784,7 @@
         <v>47.32</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31810,6 +31810,81 @@
       <c r="W414" s="7" t="n">
         <v>150.4</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>26308.41</v>
+      </c>
+      <c r="D415" t="n">
+        <v>26359.41</v>
+      </c>
+      <c r="E415" t="n">
+        <v>26287.88</v>
+      </c>
+      <c r="F415" t="n">
+        <v>26326.69</v>
+      </c>
+      <c r="G415" t="n">
+        <v>983392136</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J415" t="n">
+        <v>26933.35</v>
+      </c>
+      <c r="K415" t="n">
+        <v>26552.54</v>
+      </c>
+      <c r="L415" t="n">
+        <v>26266.25</v>
+      </c>
+      <c r="M415" t="n">
+        <v>24981.73</v>
+      </c>
+      <c r="N415" s="7" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="O415" t="n">
+        <v>28</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S415" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="T415" s="7" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="U415" s="7" t="inlineStr"/>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31784,7 +31784,7 @@
         <v>47.32</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31829,60 +31829,62 @@
         <v>26359.41</v>
       </c>
       <c r="E415" t="n">
-        <v>26287.88</v>
+        <v>25962.9</v>
       </c>
       <c r="F415" t="n">
-        <v>26326.69</v>
+        <v>26028.07</v>
       </c>
       <c r="G415" t="n">
-        <v>983392136</v>
+        <v>5126001000</v>
       </c>
       <c r="H415" s="5" t="n">
-        <v>-1.41</v>
+        <v>-2.53</v>
       </c>
       <c r="I415" t="n">
         <v>2.6</v>
       </c>
       <c r="J415" t="n">
-        <v>26933.35</v>
+        <v>26918.42</v>
       </c>
       <c r="K415" t="n">
-        <v>26552.54</v>
+        <v>26547.57</v>
       </c>
       <c r="L415" t="n">
-        <v>26266.25</v>
+        <v>26263.76</v>
       </c>
       <c r="M415" t="n">
-        <v>24981.73</v>
+        <v>24980.23</v>
       </c>
       <c r="N415" s="7" t="n">
-        <v>36.52</v>
+        <v>33.41</v>
       </c>
       <c r="O415" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>extreme fear</t>
         </is>
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>3x BUY</t>
         </is>
       </c>
       <c r="R415" t="inlineStr">
         <is>
-          <t>2nd: MA60, 50% cash, 5d</t>
+          <t>3rd: MA120, 50% cash, 5d</t>
         </is>
       </c>
       <c r="S415" t="n">
-        <v>5.04</v>
+        <v>4.95</v>
       </c>
       <c r="T415" s="7" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="U415" s="7" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="U415" s="7" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="7" t="inlineStr"/>
     </row>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31829,37 +31829,37 @@
         <v>26359.41</v>
       </c>
       <c r="E415" t="n">
-        <v>25962.9</v>
+        <v>25918.09</v>
       </c>
       <c r="F415" t="n">
-        <v>26028.07</v>
+        <v>26008.86</v>
       </c>
       <c r="G415" t="n">
-        <v>5126001000</v>
+        <v>7832683000</v>
       </c>
       <c r="H415" s="5" t="n">
-        <v>-2.53</v>
+        <v>-2.6</v>
       </c>
       <c r="I415" t="n">
         <v>2.6</v>
       </c>
       <c r="J415" t="n">
-        <v>26918.42</v>
+        <v>26917.46</v>
       </c>
       <c r="K415" t="n">
-        <v>26547.57</v>
+        <v>26547.25</v>
       </c>
       <c r="L415" t="n">
-        <v>26263.76</v>
+        <v>26263.6</v>
       </c>
       <c r="M415" t="n">
-        <v>24980.23</v>
+        <v>24980.14</v>
       </c>
       <c r="N415" s="7" t="n">
-        <v>33.41</v>
+        <v>33.23</v>
       </c>
       <c r="O415" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31880,13 +31880,15 @@
         <v>4.95</v>
       </c>
       <c r="T415" s="7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="U415" s="7" t="n">
-        <v>14.7</v>
+        <v>15.2</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="7" t="inlineStr"/>
+      <c r="W415" s="7" t="n">
+        <v>152.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>26008.86</v>
       </c>
       <c r="G415" t="n">
-        <v>7832683000</v>
+        <v>9012120000</v>
       </c>
       <c r="H415" s="5" t="n">
         <v>-2.6</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31859,7 +31859,7 @@
         <v>33.23</v>
       </c>
       <c r="O415" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31859,7 +31859,7 @@
         <v>33.23</v>
       </c>
       <c r="O415" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31889,6 +31889,79 @@
       <c r="W415" s="7" t="n">
         <v>152.4</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>25893.95</v>
+      </c>
+      <c r="D416" t="n">
+        <v>26111.62</v>
+      </c>
+      <c r="E416" t="n">
+        <v>25866.15</v>
+      </c>
+      <c r="F416" t="n">
+        <v>26005.18</v>
+      </c>
+      <c r="G416" t="n">
+        <v>3647802000</v>
+      </c>
+      <c r="H416" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I416" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J416" t="n">
+        <v>26864.28</v>
+      </c>
+      <c r="K416" t="n">
+        <v>26561.96</v>
+      </c>
+      <c r="L416" t="n">
+        <v>26271.42</v>
+      </c>
+      <c r="M416" t="n">
+        <v>24992.24</v>
+      </c>
+      <c r="N416" s="6" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="O416" t="n">
+        <v>20</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr"/>
+      <c r="S416" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="T416" s="7" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="U416" s="7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31911,34 +31911,34 @@
         <v>25866.15</v>
       </c>
       <c r="F416" t="n">
-        <v>26005.18</v>
+        <v>25955.34</v>
       </c>
       <c r="G416" t="n">
-        <v>3647802000</v>
+        <v>5728983000</v>
       </c>
       <c r="H416" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.21</v>
       </c>
       <c r="I416" t="n">
         <v>2.6</v>
       </c>
       <c r="J416" t="n">
-        <v>26864.28</v>
+        <v>26861.79</v>
       </c>
       <c r="K416" t="n">
-        <v>26561.96</v>
+        <v>26561.13</v>
       </c>
       <c r="L416" t="n">
-        <v>26271.42</v>
+        <v>26271</v>
       </c>
       <c r="M416" t="n">
-        <v>24992.24</v>
+        <v>24991.99</v>
       </c>
       <c r="N416" s="6" t="n">
-        <v>27.29</v>
+        <v>26.87</v>
       </c>
       <c r="O416" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
@@ -31952,16 +31952,18 @@
       </c>
       <c r="R416" t="inlineStr"/>
       <c r="S416" t="n">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
       <c r="T416" s="7" t="n">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
       <c r="U416" s="7" t="n">
-        <v>15.5</v>
+        <v>16.8</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" s="7" t="inlineStr"/>
+      <c r="W416" s="7" t="n">
+        <v>151.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31835,7 +31835,7 @@
         <v>25955.34</v>
       </c>
       <c r="G415" t="n">
-        <v>5728983000</v>
+        <v>6554790000</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-0.21</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2712,7 +2712,7 @@
         <v>2.6</v>
       </c>
       <c r="J29" t="n">
-        <v>17132.25</v>
+        <v>17132.26</v>
       </c>
       <c r="K29" t="n">
         <v>18472.28</v>
@@ -5728,7 +5728,7 @@
         <v>2.6</v>
       </c>
       <c r="J69" t="n">
-        <v>19240.32</v>
+        <v>19240.31</v>
       </c>
       <c r="K69" t="n">
         <v>17918.44</v>
@@ -31705,7 +31705,7 @@
         <v>26.87</v>
       </c>
       <c r="O413" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31731,6 +31731,79 @@
       <c r="W413" s="6" t="n">
         <v>151.8</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>26026.87</v>
+      </c>
+      <c r="D414" t="n">
+        <v>26306.82</v>
+      </c>
+      <c r="E414" t="n">
+        <v>25986.56</v>
+      </c>
+      <c r="F414" t="n">
+        <v>26208.23</v>
+      </c>
+      <c r="G414" t="n">
+        <v>3457312000</v>
+      </c>
+      <c r="H414" s="5" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J414" t="n">
+        <v>26831.18</v>
+      </c>
+      <c r="K414" t="n">
+        <v>26575.04</v>
+      </c>
+      <c r="L414" t="n">
+        <v>26278.35</v>
+      </c>
+      <c r="M414" t="n">
+        <v>25005.63</v>
+      </c>
+      <c r="N414" s="5" t="n">
+        <v>29.66</v>
+      </c>
+      <c r="O414" t="n">
+        <v>27</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="T414" s="6" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="U414" s="6" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -2712,7 +2712,7 @@
         <v>2.6</v>
       </c>
       <c r="J29" t="n">
-        <v>17132.26</v>
+        <v>17132.25</v>
       </c>
       <c r="K29" t="n">
         <v>18472.28</v>
@@ -5728,7 +5728,7 @@
         <v>2.6</v>
       </c>
       <c r="J69" t="n">
-        <v>19240.31</v>
+        <v>19240.32</v>
       </c>
       <c r="K69" t="n">
         <v>17918.44</v>
@@ -31753,31 +31753,31 @@
         <v>25986.56</v>
       </c>
       <c r="F414" t="n">
-        <v>26208.23</v>
+        <v>26169.38</v>
       </c>
       <c r="G414" t="n">
-        <v>3457312000</v>
+        <v>6492720000</v>
       </c>
       <c r="H414" s="5" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="I414" t="n">
         <v>2.6</v>
       </c>
       <c r="J414" t="n">
-        <v>26831.18</v>
+        <v>26829.24</v>
       </c>
       <c r="K414" t="n">
-        <v>26575.04</v>
+        <v>26574.39</v>
       </c>
       <c r="L414" t="n">
-        <v>26278.35</v>
+        <v>26278.03</v>
       </c>
       <c r="M414" t="n">
-        <v>25005.63</v>
+        <v>25005.44</v>
       </c>
       <c r="N414" s="5" t="n">
-        <v>29.66</v>
+        <v>28.85</v>
       </c>
       <c r="O414" t="n">
         <v>27</v>
@@ -31794,16 +31794,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="T414" s="6" t="n">
         <v>18.4</v>
       </c>
       <c r="U414" s="6" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="6" t="inlineStr"/>
+      <c r="W414" s="6" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31677,7 +31677,7 @@
         <v>26169.38</v>
       </c>
       <c r="G413" t="n">
-        <v>6508626000</v>
+        <v>7402660000</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>0.82</v>
@@ -31701,7 +31701,7 @@
         <v>28.85</v>
       </c>
       <c r="O413" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31701,7 +31701,7 @@
         <v>28.85</v>
       </c>
       <c r="O413" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31727,6 +31727,79 @@
       <c r="W413" s="2" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>26286.31</v>
+      </c>
+      <c r="D414" t="n">
+        <v>26372.21</v>
+      </c>
+      <c r="E414" t="n">
+        <v>26229.64</v>
+      </c>
+      <c r="F414" t="n">
+        <v>26254.31</v>
+      </c>
+      <c r="G414" t="n">
+        <v>1763767000</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J414" t="n">
+        <v>26802.07</v>
+      </c>
+      <c r="K414" t="n">
+        <v>26580.06</v>
+      </c>
+      <c r="L414" t="n">
+        <v>26281.49</v>
+      </c>
+      <c r="M414" t="n">
+        <v>25018.35</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="O414" t="n">
+        <v>32</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31743,40 +31743,40 @@
         <v>26286.31</v>
       </c>
       <c r="D414" t="n">
-        <v>26372.21</v>
+        <v>26540.81</v>
       </c>
       <c r="E414" t="n">
-        <v>26229.64</v>
+        <v>26219.31</v>
       </c>
       <c r="F414" t="n">
-        <v>26254.31</v>
+        <v>26483</v>
       </c>
       <c r="G414" t="n">
-        <v>1763767000</v>
+        <v>5843080000</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>0.32</v>
+        <v>1.2</v>
       </c>
       <c r="I414" t="n">
         <v>2.6</v>
       </c>
       <c r="J414" t="n">
-        <v>26802.07</v>
+        <v>26813.51</v>
       </c>
       <c r="K414" t="n">
-        <v>26580.06</v>
+        <v>26583.88</v>
       </c>
       <c r="L414" t="n">
-        <v>26281.49</v>
+        <v>26283.4</v>
       </c>
       <c r="M414" t="n">
-        <v>25018.35</v>
+        <v>25019.5</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>31.15</v>
+        <v>35.48</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31790,13 +31790,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -2633,7 +2633,7 @@
         <v>2.6</v>
       </c>
       <c r="J28" t="n">
-        <v>17132.25</v>
+        <v>17132.26</v>
       </c>
       <c r="K28" t="n">
         <v>18472.28</v>
@@ -5649,7 +5649,7 @@
         <v>2.6</v>
       </c>
       <c r="J68" t="n">
-        <v>19240.32</v>
+        <v>19240.31</v>
       </c>
       <c r="K68" t="n">
         <v>17918.44</v>
@@ -29431,7 +29431,7 @@
         <v>54.24</v>
       </c>
       <c r="O383" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P383" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>46.55</v>
       </c>
       <c r="O384" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P384" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>47.51</v>
       </c>
       <c r="O386" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P386" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>52.46</v>
       </c>
       <c r="O387" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P387" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>61.78</v>
       </c>
       <c r="O390" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P390" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>56.61</v>
       </c>
       <c r="O391" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P391" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>56.88</v>
       </c>
       <c r="O393" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P393" t="inlineStr">
         <is>
@@ -30264,7 +30264,7 @@
         <v>59.87</v>
       </c>
       <c r="O394" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P394" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>69.47</v>
       </c>
       <c r="O397" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P397" t="inlineStr">
         <is>
@@ -30564,7 +30564,7 @@
         <v>78.11</v>
       </c>
       <c r="O398" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P398" t="inlineStr">
         <is>
@@ -30714,7 +30714,7 @@
         <v>73.33</v>
       </c>
       <c r="O400" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P400" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>62.69</v>
       </c>
       <c r="O401" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P401" t="inlineStr">
         <is>
@@ -30864,11 +30864,11 @@
         <v>55.51</v>
       </c>
       <c r="O402" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P402" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q402" t="inlineStr">
@@ -30939,7 +30939,7 @@
         <v>50.04</v>
       </c>
       <c r="O403" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P403" t="inlineStr">
         <is>
@@ -31014,11 +31014,11 @@
         <v>56.89</v>
       </c>
       <c r="O404" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P404" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q404" t="inlineStr">
@@ -31089,7 +31089,7 @@
         <v>44.98</v>
       </c>
       <c r="O405" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P405" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>42.42</v>
       </c>
       <c r="O406" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P406" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>37.26</v>
       </c>
       <c r="O407" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P407" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>43.76</v>
       </c>
       <c r="O408" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P408" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>42.43</v>
       </c>
       <c r="O409" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P409" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>47.32</v>
       </c>
       <c r="O410" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P410" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>33.23</v>
       </c>
       <c r="O411" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P411" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>26.87</v>
       </c>
       <c r="O412" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>28.85</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31749,34 +31749,34 @@
         <v>26219.31</v>
       </c>
       <c r="F414" t="n">
-        <v>26483</v>
+        <v>26477.81</v>
       </c>
       <c r="G414" t="n">
-        <v>5843080000</v>
+        <v>7116359000</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="I414" t="n">
         <v>2.6</v>
       </c>
       <c r="J414" t="n">
-        <v>26813.51</v>
+        <v>26813.25</v>
       </c>
       <c r="K414" t="n">
-        <v>26583.88</v>
+        <v>26583.79</v>
       </c>
       <c r="L414" t="n">
-        <v>26283.4</v>
+        <v>26283.35</v>
       </c>
       <c r="M414" t="n">
-        <v>25019.5</v>
+        <v>25019.47</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>35.48</v>
+        <v>35.39</v>
       </c>
       <c r="O414" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31799,7 +31799,9 @@
         <v>12.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31697,7 +31697,7 @@
         <v>35.39</v>
       </c>
       <c r="O413" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31723,6 +31723,79 @@
       <c r="W413" s="7" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>26541.61</v>
+      </c>
+      <c r="D414" t="n">
+        <v>26582.01</v>
+      </c>
+      <c r="E414" t="n">
+        <v>26428.26</v>
+      </c>
+      <c r="F414" t="n">
+        <v>26475.67</v>
+      </c>
+      <c r="G414" t="n">
+        <v>4333394000</v>
+      </c>
+      <c r="H414" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I414" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J414" t="n">
+        <v>26793.98</v>
+      </c>
+      <c r="K414" t="n">
+        <v>26581.97</v>
+      </c>
+      <c r="L414" t="n">
+        <v>26288.93</v>
+      </c>
+      <c r="M414" t="n">
+        <v>25033.18</v>
+      </c>
+      <c r="N414" s="7" t="n">
+        <v>39.08</v>
+      </c>
+      <c r="O414" t="n">
+        <v>35</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="T414" s="7" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U414" s="7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -2554,7 +2554,7 @@
         <v>2.6</v>
       </c>
       <c r="J27" t="n">
-        <v>17132.26</v>
+        <v>17132.25</v>
       </c>
       <c r="K27" t="n">
         <v>18472.28</v>
@@ -5570,7 +5570,7 @@
         <v>2.6</v>
       </c>
       <c r="J67" t="n">
-        <v>19240.31</v>
+        <v>19240.32</v>
       </c>
       <c r="K67" t="n">
         <v>17918.44</v>
@@ -31739,40 +31739,40 @@
         <v>26541.61</v>
       </c>
       <c r="D414" t="n">
-        <v>26582.01</v>
+        <v>26587.34</v>
       </c>
       <c r="E414" t="n">
-        <v>26428.26</v>
+        <v>26414.92</v>
       </c>
       <c r="F414" t="n">
-        <v>26475.67</v>
+        <v>26549.85</v>
       </c>
       <c r="G414" t="n">
-        <v>4333394000</v>
-      </c>
-      <c r="H414" s="5" t="n">
-        <v>-0.01</v>
+        <v>7142936000</v>
+      </c>
+      <c r="H414" s="6" t="n">
+        <v>0.27</v>
       </c>
       <c r="I414" t="n">
         <v>2.6</v>
       </c>
       <c r="J414" t="n">
-        <v>26793.98</v>
+        <v>26797.69</v>
       </c>
       <c r="K414" t="n">
-        <v>26581.97</v>
+        <v>26583.2</v>
       </c>
       <c r="L414" t="n">
-        <v>26288.93</v>
+        <v>26289.55</v>
       </c>
       <c r="M414" t="n">
-        <v>25033.18</v>
+        <v>25033.55</v>
       </c>
       <c r="N414" s="7" t="n">
-        <v>39.08</v>
+        <v>40.41</v>
       </c>
       <c r="O414" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31786,16 +31786,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.02</v>
+        <v>5.05</v>
       </c>
       <c r="T414" s="7" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="U414" s="7" t="n">
-        <v>14.4</v>
+        <v>13.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="7" t="inlineStr"/>
+      <c r="W414" s="7" t="n">
+        <v>148.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31748,7 +31748,7 @@
         <v>26549.85</v>
       </c>
       <c r="G414" t="n">
-        <v>7142936000</v>
+        <v>7985070000</v>
       </c>
       <c r="H414" s="6" t="n">
         <v>0.27</v>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31772,7 +31772,7 @@
         <v>40.41</v>
       </c>
       <c r="O414" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31798,6 +31798,83 @@
       <c r="W414" s="7" t="n">
         <v>148.7</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>26201.82</v>
+      </c>
+      <c r="D415" t="n">
+        <v>26286.46</v>
+      </c>
+      <c r="E415" t="n">
+        <v>26053.16</v>
+      </c>
+      <c r="F415" t="n">
+        <v>26196.61</v>
+      </c>
+      <c r="G415" t="n">
+        <v>3302277000</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="I415" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J415" t="n">
+        <v>26763.94</v>
+      </c>
+      <c r="K415" t="n">
+        <v>26580.42</v>
+      </c>
+      <c r="L415" t="n">
+        <v>26289.13</v>
+      </c>
+      <c r="M415" t="n">
+        <v>25045.98</v>
+      </c>
+      <c r="N415" s="7" t="n">
+        <v>33.47</v>
+      </c>
+      <c r="O415" t="n">
+        <v>35</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>3rd: MA120, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" s="7" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="U415" s="7" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31820,31 +31820,31 @@
         <v>26053.16</v>
       </c>
       <c r="F415" t="n">
-        <v>26196.61</v>
+        <v>26184.72</v>
       </c>
       <c r="G415" t="n">
-        <v>3302277000</v>
+        <v>6506000000</v>
       </c>
       <c r="H415" s="5" t="n">
-        <v>-1.33</v>
+        <v>-1.38</v>
       </c>
       <c r="I415" t="n">
         <v>2.6</v>
       </c>
       <c r="J415" t="n">
-        <v>26763.94</v>
+        <v>26763.34</v>
       </c>
       <c r="K415" t="n">
-        <v>26580.42</v>
+        <v>26580.23</v>
       </c>
       <c r="L415" t="n">
-        <v>26289.13</v>
+        <v>26289.03</v>
       </c>
       <c r="M415" t="n">
-        <v>25045.98</v>
+        <v>25045.92</v>
       </c>
       <c r="N415" s="7" t="n">
-        <v>33.47</v>
+        <v>33.35</v>
       </c>
       <c r="O415" t="n">
         <v>35</v>
@@ -31865,16 +31865,18 @@
         </is>
       </c>
       <c r="S415" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T415" s="7" t="n">
-        <v>16.3</v>
+        <v>17.2</v>
       </c>
       <c r="U415" s="7" t="n">
-        <v>10.2</v>
+        <v>13.6</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="7" t="inlineStr"/>
+      <c r="W415" s="7" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31823,7 +31823,7 @@
         <v>26184.72</v>
       </c>
       <c r="G415" t="n">
-        <v>6506000000</v>
+        <v>7405880000</v>
       </c>
       <c r="H415" s="5" t="n">
         <v>-1.38</v>
@@ -31847,7 +31847,7 @@
         <v>33.35</v>
       </c>
       <c r="O415" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -31847,7 +31847,7 @@
         <v>33.35</v>
       </c>
       <c r="O415" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31877,6 +31877,79 @@
       <c r="W415" s="7" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>25592.49</v>
+      </c>
+      <c r="D416" t="n">
+        <v>25673</v>
+      </c>
+      <c r="E416" t="n">
+        <v>25478</v>
+      </c>
+      <c r="F416" t="n">
+        <v>25522.9</v>
+      </c>
+      <c r="G416" t="n">
+        <v>2905152000</v>
+      </c>
+      <c r="H416" s="5" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="I416" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J416" t="n">
+        <v>26679.95</v>
+      </c>
+      <c r="K416" t="n">
+        <v>26566.47</v>
+      </c>
+      <c r="L416" t="n">
+        <v>26282.77</v>
+      </c>
+      <c r="M416" t="n">
+        <v>25056.18</v>
+      </c>
+      <c r="N416" s="6" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="O416" t="n">
+        <v>27</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr"/>
+      <c r="S416" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T416" s="7" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="U416" s="7" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31879,77 +31879,77 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>^IXIC</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>^IXIC</t>
+        </is>
+      </c>
+      <c r="B416" s="1" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="C416" t="n">
+      <c r="C416" s="1" t="n">
         <v>25592.49</v>
       </c>
-      <c r="D416" t="n">
+      <c r="D416" s="1" t="n">
         <v>25673</v>
       </c>
-      <c r="E416" t="n">
-        <v>25478</v>
-      </c>
-      <c r="F416" t="n">
-        <v>25522.9</v>
-      </c>
-      <c r="G416" t="n">
-        <v>2905152000</v>
-      </c>
-      <c r="H416" s="5" t="n">
-        <v>-2.53</v>
-      </c>
-      <c r="I416" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J416" t="n">
-        <v>26679.95</v>
-      </c>
-      <c r="K416" t="n">
-        <v>26566.47</v>
-      </c>
-      <c r="L416" t="n">
-        <v>26282.77</v>
-      </c>
-      <c r="M416" t="n">
-        <v>25056.18</v>
-      </c>
-      <c r="N416" s="6" t="n">
-        <v>28.94</v>
-      </c>
-      <c r="O416" t="n">
-        <v>27</v>
-      </c>
-      <c r="P416" t="inlineStr">
+      <c r="E416" s="1" t="n">
+        <v>25177.33</v>
+      </c>
+      <c r="F416" s="1" t="n">
+        <v>25437</v>
+      </c>
+      <c r="G416" s="1" t="n">
+        <v>7565643000</v>
+      </c>
+      <c r="H416" s="2" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="I416" s="1" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J416" s="1" t="n">
+        <v>26675.65</v>
+      </c>
+      <c r="K416" s="1" t="n">
+        <v>26565.04</v>
+      </c>
+      <c r="L416" s="1" t="n">
+        <v>26282.05</v>
+      </c>
+      <c r="M416" s="1" t="n">
+        <v>25055.75</v>
+      </c>
+      <c r="N416" s="3" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="O416" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="P416" s="1" t="inlineStr">
         <is>
           <t>fear</t>
         </is>
       </c>
-      <c r="Q416" t="inlineStr">
+      <c r="Q416" s="1" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R416" t="inlineStr"/>
-      <c r="S416" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="T416" s="7" t="n">
+      <c r="R416" s="1" t="inlineStr"/>
+      <c r="S416" s="1" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="T416" s="4" t="n">
         <v>19.4</v>
       </c>
-      <c r="U416" s="7" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="V416" t="inlineStr"/>
-      <c r="W416" s="7" t="inlineStr"/>
+      <c r="U416" s="4" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="V416" s="1" t="inlineStr"/>
+      <c r="W416" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/NASDAQ_table.xlsx
+++ b/US_stock/NASDAQ_table.xlsx
@@ -31819,7 +31819,7 @@
         <v>25437</v>
       </c>
       <c r="G415" s="4" t="n">
-        <v>7710137000</v>
+        <v>9068930000</v>
       </c>
       <c r="H415" s="5" t="n">
         <v>-2.86</v>
